--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
@@ -89,6 +93,16 @@
       <i val="1"/>
       <color rgb="00FFFF99"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00222222"/>
+      <sz val="9"/>
     </font>
     <font>
       <i val="1"/>
@@ -116,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -190,6 +204,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -220,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -297,11 +316,8 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -309,7 +325,9 @@
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -334,11 +352,8 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -346,7 +361,9 @@
     <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -371,11 +388,8 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -383,7 +397,9 @@
     <xf numFmtId="164" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -429,11 +445,8 @@
     <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -441,15 +454,14 @@
     <xf numFmtId="164" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -457,59 +469,91 @@
     <xf numFmtId="164" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -877,31 +921,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PRJ13797 – JMUX Replacement  |  Vendor Cost Forecast 2026 &amp; 2027</t>
+          <t>PRJ13797 – JMUX Replacement  |  Vendor &amp; Internal Cost Forecast 2026 &amp; 2027</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: B&amp;M SOW v03 (Aug 2025) · Hawkeye Phase 2 SOW (Mar 2026) · Call minutes May 18 2026  |  Prepared: May 18 2026</t>
+          <t>Source: B&amp;M SOW v03 (Aug 2025)  ·  Hawkeye Phase 2 SOW (Mar 2026)  ·  Call minutes May 18 2026  |  Prepared: May 18 2026</t>
         </is>
       </c>
     </row>
@@ -928,12 +972,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Timing / Year</t>
+          <t>Timing</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>SOW Total ($)</t>
+          <t>SOW / Est. Total ($)</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -959,7 +1003,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="38" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -994,11 +1038,11 @@
       <c r="H5" s="9" t="inlineStr"/>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>$5,500/mo × 12 months. Static monthly invoiced cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+          <t>$5,500/mo × 12 months. Static monthly cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1006,8 +1050,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 Staging Support
-(Milestone 1 – carryover)</t>
+          <t>Phase 1 Staging Support  (Milestone 1 – carryover)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1034,11 +1077,11 @@
       <c r="H6" s="9" t="inlineStr"/>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Milestone 1: $57,300 fixed. Phase 1 staging test plan, card slotting, SFP install, connectivity/labelling docs. Invoiced 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+          <t>B&amp;M SOW Milestone 1: $57,300 fixed. Staging test plan, card slotting, SFP install.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1074,11 +1117,11 @@
       <c r="H7" s="16" t="inlineStr"/>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Milestone 2: $368,100 total ($61,350/mo). Aug 2025–Jan 2026. Mostly 2025. 2026 portion = ~1 month remaining if any.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+          <t>B&amp;M SOW Milestone 2: $368,100 total (~$61,350/mo). Aug 2025–Jan 2026. ~1 month in 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1086,8 +1129,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Substation Site Surveys – Phase 2
-(Milestone 3 – 36 sites)</t>
+          <t>Substation Site Surveys – Phase 2  (Milestone 3 – 36 sites)</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1102,7 +1144,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2026 (Jan–Feb)</t>
+          <t>2026 Jan–Feb</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
@@ -1114,11 +1156,11 @@
       <c r="H8" s="9" t="inlineStr"/>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Milestone 3: $86,040 fixed. Site surveys Jan 5–Feb 27 2026. COMPLETE per schedule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+          <t>B&amp;M SOW Milestone 3: $86,040 fixed. 36 sites × 3 weeks. Completed Feb 27 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1127,7 +1169,7 @@
       <c r="B9" s="6" t="inlineStr">
         <is>
           <t>MPLS Node Design – IFR
-36 sites × $16,695</t>
+36 sites × $16,695  =  $601,020</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -1142,7 +1184,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026 (Jan–Jun)</t>
+          <t>2026 Jan–Jun</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
@@ -1154,11 +1196,11 @@
       <c r="H9" s="9" t="inlineStr"/>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Appendix D: 36 × $16,695 = $601,020. IFRs rolling Jan–Jun 2026 per schedule. All IFRs due by Jun 29 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+          <t>B&amp;M Appendix D: 36 × $16,695. Rolling IFRs Jan–Jun 2026. All IFRs due Jun 29 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1167,7 +1209,7 @@
       <c r="B10" s="6" t="inlineStr">
         <is>
           <t>MPLS Node Design – IFC
-36 sites × $5,963</t>
+36 sites × $5,963  =  $214,668</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1182,7 +1224,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>2026 (Mar–Jul)</t>
+          <t>2026 Mar–Jul</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
@@ -1194,11 +1236,11 @@
       <c r="H10" s="9" t="inlineStr"/>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Appendix D: 36 × $5,963 = $214,668. IFCs rolling Mar–Jul 2026. All IFCs due by Jul 13 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+          <t>B&amp;M Appendix D: 36 × $5,963. Rolling IFCs Mar–Jul 2026. All IFCs due Jul 13 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1207,7 +1249,7 @@
       <c r="B11" s="13" t="inlineStr">
         <is>
           <t>MPLS Node Design – As-Built
-36 sites × $1,192</t>
+36 sites × $1,192  =  $42,912</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -1234,11 +1276,11 @@
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Appendix D: 36 × $1,192 = $42,912. As-Builts issued AFTER construction complete. Deferred to 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+          <t>B&amp;M Appendix D: 36 × $1,192. Issued AFTER construction complete. Deferred to 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="38" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1247,7 +1289,7 @@
       <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Phase 2 Construction Support Coordinator
-(Milestone 2 Phase 2 – monthly Aug–Dec 2026)</t>
+(Milestone 2 Ph2 – monthly Aug–Dec 2026)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1262,7 +1304,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2026 (Aug–Dec)</t>
+          <t>2026 Aug–Dec</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
@@ -1274,11 +1316,11 @@
       <c r="H12" s="9" t="inlineStr"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>B&amp;M SOW Milestone 2 (Phase 2): On-site coordinator up to 45 hrs/wk during Phase 2 construction. ~$61,350/mo × ~6 months. Invoiced monthly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t>B&amp;M SOW Milestone 2 (Phase 2): On-site coordinator up to 45 hrs/wk. ~$61,350/mo × ~6 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1287,8 +1329,7 @@
       <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Phase 3 Engineering – IFR + IFC
-31 sites × $22,658 (excl. As-Built)
-ACCELERATED from 2027→2026</t>
+31 sites × $22,658  (ACCELERATED from 2027→2026)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -1303,7 +1344,7 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>2026 START / 2027 complete</t>
+          <t>2026 start / 2027 complete</t>
         </is>
       </c>
       <c r="F13" s="23" t="n">
@@ -1317,11 +1358,11 @@
       </c>
       <c r="I13" s="25" t="inlineStr">
         <is>
-          <t>Vic/Jay agreed to accelerate Phase 3 engineering into 2026 to avoid 2028 schedule slip. Site surveys &amp; early IFRs start Aug 2026 during Phase 2 staging. Est. ~1/3 in 2026, ~2/3 in 2027. Confirms via B&amp;M meeting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t>Surveys + IFRs start Aug 2026 during Ph2 staging. ~1/3 in 2026, ~2/3 in 2027. Avoids 2028 schedule slip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>B&amp;M</t>
@@ -1330,7 +1371,7 @@
       <c r="B14" s="13" t="inlineStr">
         <is>
           <t>Phase 3 – As-Built
-31 sites × $1,192</t>
+31 sites × $1,192  =  $36,952</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1357,200 +1398,191 @@
       </c>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>31 Phase 3 As-Builts post Phase 3 construction. All 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
+          <t>31 As-Builts post Phase 3 construction. All 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>B&amp;M TOTAL  (excl. Phase 1 constr. support already paid in 2025)</t>
-        </is>
-      </c>
-      <c r="F15" s="28" t="n">
+          <t xml:space="preserve">  SUBTOTAL — B&amp;M TOTAL</t>
+        </is>
+      </c>
+      <c r="F15" s="27" t="n">
         <v>2158962</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="28" t="n">
         <v>1683202</v>
       </c>
-      <c r="H15" s="29" t="n">
+      <c r="H15" s="28" t="n">
         <v>567262</v>
       </c>
-      <c r="I15" s="30" t="n"/>
+      <c r="I15" s="29" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HAWKEYE CONSTRUCTION (ELECNOR HAWKEYE LLC)  —  SOW Fixed Price: $400,680  |  Targeted completion: Dec 31 2026</t>
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HAWKEYE CONSTRUCTION (ELECNOR HAWKEYE LLC)  —  SOW Fixed Price: $400,680  |  Target completion: Dec 31 2026</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Hawkeye</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>Milestone Phase 0:
-Equipment Staging &amp; Assembly
-Receive, rack, card-install, burn-in &amp; test all 36 Phase 2 Nokia nodes at lab</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Milestone Ph0:  Equipment Staging &amp; Assembly
+Receive, rack, load firmware, burn-in &amp; test all 36 Phase 2 Nokia nodes at Hawkeye lab</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>PO7000002099</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D18" s="34" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
-        <is>
-          <t>2026 (Jun–Aug)</t>
-        </is>
-      </c>
-      <c r="F18" s="36" t="n">
+      <c r="E18" s="34" t="inlineStr">
+        <is>
+          <t>2026 Jun–Aug</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="n">
         <v>100170</v>
       </c>
-      <c r="G18" s="37" t="n">
+      <c r="G18" s="36" t="n">
         <v>100170</v>
       </c>
-      <c r="H18" s="36" t="inlineStr"/>
-      <c r="I18" s="38" t="inlineStr">
-        <is>
-          <t>Hawkeye SOW Milestone Phase 0: $100,170 (25% of $400,680). Assemble Nokia SAR-8, load firmware, burn-in test at Hawkeye lab before shipping to substations.</t>
+      <c r="H18" s="35" t="inlineStr"/>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW Milestone Ph0: $100,170 (25% of $400,680). Lab assembly before site shipment.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Hawkeye</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>Milestone 1:
-Design/Site Survey Complete
-On-site pre-construction surveys: cable types, power, rack space per IFC</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 1:  Site Surveys (pre-construction)
+On-site: cable types, power verification, rack space per IFC</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>PO7000002099</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
-        <is>
-          <t>2026 (May–Jul)</t>
-        </is>
-      </c>
-      <c r="F19" s="36" t="n">
+      <c r="E19" s="34" t="inlineStr">
+        <is>
+          <t>2026 May–Jul</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="n">
         <v>100170</v>
       </c>
-      <c r="G19" s="37" t="n">
+      <c r="G19" s="36" t="n">
         <v>100170</v>
       </c>
-      <c r="H19" s="36" t="inlineStr"/>
-      <c r="I19" s="38" t="inlineStr">
-        <is>
-          <t>Hawkeye SOW Milestone 1: $100,170 (25%). 3 mobilisations per site. Survey verifies IFC cable/connector requirements. Vinny started week of May 18 2026.</t>
+      <c r="H19" s="35" t="inlineStr"/>
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW Milestone 1: $100,170 (25%). 3 mobilisations/site. Vinny started week of May 18 2026.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Hawkeye</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>Milestone 2:
-Installation Complete – All 36 sites
-Install Nokia SAR-8, CWDM, Eltek PSU, RS-232 patch panel, fiber, CAT6, 4-wire VF. Energize &amp; basic test.</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 2:  Installation Complete – All 36 Sites
+Install Nokia SAR-8, CWDM, Eltek PSU, RS-232 patch panel, fiber, CAT6, 4-wire VF. Energize &amp; test.</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>PO7000002099</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="34" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
-        <is>
-          <t>2026 (Aug–Sep)</t>
-        </is>
-      </c>
-      <c r="F20" s="36" t="n">
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>2026 Aug–Sep</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="n">
         <v>80136</v>
       </c>
-      <c r="G20" s="37" t="n">
+      <c r="G20" s="36" t="n">
         <v>80136</v>
       </c>
-      <c r="H20" s="36" t="inlineStr"/>
-      <c r="I20" s="38" t="inlineStr">
-        <is>
-          <t>Hawkeye SOW Milestone 2: $80,136 (20%). 36 Phase 2 substations. Install per approved IFC. Notify PSEG Relay when site ready for service migration. Construction start: Aug 5 2026.</t>
+      <c r="H20" s="35" t="inlineStr"/>
+      <c r="I20" s="37" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW Milestone 2: $80,136 (20%). Construction start Aug 5 2026. Notify PSEG Relay when ready for migration.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Hawkeye</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Milestone 4:
-Project Ready for Go-Live
-(all sites installed, tested, relay migration complete)</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Milestone 4:  Project Ready for Go-Live
+All 36 sites installed, tested, relay migration complete, PSEG sign-off</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>PO7000002099</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
-        <is>
-          <t>2026 (Sep–Oct)</t>
-        </is>
-      </c>
-      <c r="F21" s="36" t="n">
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>2026 Sep–Oct</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="n">
         <v>80136</v>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G21" s="36" t="n">
         <v>80136</v>
       </c>
-      <c r="H21" s="36" t="inlineStr"/>
-      <c r="I21" s="38" t="inlineStr">
-        <is>
-          <t>Hawkeye SOW Milestone 4: $80,136 (20%). All 36 sites installed and signed off. PSEG Relay has completed service migration to Nokia. Go-live approval from Vic/PSEG.</t>
+      <c r="H21" s="35" t="inlineStr"/>
+      <c r="I21" s="37" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW Milestone 4: $80,136 (20%). Go-live approval from Vic/PSEG.</t>
         </is>
       </c>
     </row>
@@ -1562,9 +1594,8 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>Milestone 6:
-Decommissioning – Remove &amp; Ship JMUX
-Power down JMUX, dismantle, box, ship to designated location. All 36 Phase 2 sites.</t>
+          <t>Milestone 6:  Decommissioning
+Power down JMUX, dismantle, box &amp; ship to designated location – All 36 Phase 2 sites</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -1591,40 +1622,35 @@
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>Hawkeye SOW Milestone 6: $40,068 (10%). Cannot start until ALL circuits migrated off JMUX by relay team. Likely 2027 after Phase 2+3 cutovers complete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>HAWKEYE TOTAL  (SOW $400,680 = 5 milestones)</t>
-        </is>
-      </c>
-      <c r="F23" s="41" t="n">
+          <t>Hawkeye SOW Milestone 6: $40,068 (10%). Cannot start until ALL circuits migrated off JMUX by relay team. Likely 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUBTOTAL — HAWKEYE TOTAL  (SOW $400,680)</t>
+        </is>
+      </c>
+      <c r="F23" s="39" t="n">
         <v>400680</v>
       </c>
-      <c r="G23" s="42" t="n">
+      <c r="G23" s="40" t="n">
         <v>360612</v>
       </c>
-      <c r="H23" s="42" t="n">
+      <c r="H23" s="40" t="n">
         <v>40068</v>
       </c>
-      <c r="I23" s="43" t="n"/>
+      <c r="I23" s="41" t="inlineStr"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOKIA &amp; EQUIPMENT  —  Master PO: $1,899,000  |  Phase 2 paid: $733,293  |  Phase 3 remaining: ~$395,000</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="40" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Nokia</t>
@@ -1633,13 +1659,12 @@
       <c r="B26" s="13" t="inlineStr">
         <is>
           <t>Phase 2 Equipment
-36 Nokia 7705 SAR nodes + cards + SFPs
-[DELIVERED &amp; PAID]</t>
+36 Nokia 7705 SAR nodes + cards + SFPs  [DELIVERED &amp; PAID]</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>PO7000001811 / 2119 / 1841 / 1767</t>
+          <t>PO7000001811/2119/1841/1767</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -1659,316 +1684,301 @@
       <c r="H26" s="16" t="inlineStr"/>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>ALL Phase 2 equipment delivered and paid ($733,293). No further 2026 Nokia Phase 2 cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="45" t="inlineStr">
+          <t>ALL Phase 2 equipment delivered and paid. No further 2026 Nokia Phase 2 cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>Phase 3 Equipment
-31 Nokia 7705 SAR nodes + cards
-[ORDER ~Q3 2026, DELIVER 2027]</t>
-        </is>
-      </c>
-      <c r="C27" s="47" t="inlineStr">
+31 Nokia 7705 SAR nodes + cards  [ORDER ~Q3 2026, DELIVER 2027]</t>
+        </is>
+      </c>
+      <c r="C27" s="45" t="inlineStr">
         <is>
           <t>TBD – Ph3 PO</t>
         </is>
       </c>
-      <c r="D27" s="48" t="inlineStr">
+      <c r="D27" s="46" t="inlineStr">
         <is>
           <t>Ph3</t>
         </is>
       </c>
-      <c r="E27" s="48" t="inlineStr">
+      <c r="E27" s="46" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="47" t="n">
         <v>395000</v>
       </c>
-      <c r="G27" s="49" t="inlineStr"/>
-      <c r="H27" s="50" t="n">
+      <c r="G27" s="47" t="inlineStr"/>
+      <c r="H27" s="48" t="n">
         <v>395000</v>
       </c>
-      <c r="I27" s="51" t="inlineStr">
-        <is>
-          <t>Remaining $395K on master $1.899M PO. Confirm Phase 3 BOM with Ethan/Tim before ordering. Lead time ~8-12 wks. Target order Q3 2026, delivery Q1 2027.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="I27" s="49" t="inlineStr">
+        <is>
+          <t>Remaining $395K on master $1.899M PO. Confirm BOM with Ethan/Tim. Lead time ~8-12 wks. Order Q3 2026, deliver Q1 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>Presidio</t>
         </is>
       </c>
-      <c r="B28" s="46" t="inlineStr">
-        <is>
-          <t>CWDM Cards
-(Phase 2: ~8-10 additional cards)
-(Phase 3: TBD with Ethan/Tim)</t>
-        </is>
-      </c>
-      <c r="C28" s="47" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>CWDM Cards  (Phase 2: ~8-10 additional  |  Phase 3: TBD)</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>TBD – Presidio PO</t>
         </is>
       </c>
-      <c r="D28" s="48" t="inlineStr">
+      <c r="D28" s="46" t="inlineStr">
         <is>
           <t>Ph2+3</t>
         </is>
       </c>
-      <c r="E28" s="48" t="inlineStr">
+      <c r="E28" s="46" t="inlineStr">
         <is>
           <t>2026 / 2027</t>
         </is>
       </c>
-      <c r="F28" s="49" t="n">
+      <c r="F28" s="47" t="n">
         <v>35000</v>
       </c>
-      <c r="G28" s="50" t="n">
+      <c r="G28" s="48" t="n">
         <v>15000</v>
       </c>
-      <c r="H28" s="50" t="n">
+      <c r="H28" s="48" t="n">
         <v>20000</v>
       </c>
-      <c r="I28" s="51" t="inlineStr">
-        <is>
-          <t>Graybar closed. Source from Presidio. ~$1,500-2,000/card. Phase 2 count to confirm with Ethan. Phase 3 count TBD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="I28" s="49" t="inlineStr">
+        <is>
+          <t>Graybar closed. Presidio source. ~$1,500-2,000/card. Count to confirm with Ethan/Tim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>Presidio</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
-        <is>
-          <t>Power Supplies + Accessories
-(Phase 2+3)</t>
-        </is>
-      </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>Power Supplies + Accessories  (Phase 2+3)</t>
+        </is>
+      </c>
+      <c r="C29" s="45" t="inlineStr">
         <is>
           <t>TBD – Presidio PO</t>
         </is>
       </c>
-      <c r="D29" s="48" t="inlineStr">
+      <c r="D29" s="46" t="inlineStr">
         <is>
           <t>Ph2+3</t>
         </is>
       </c>
-      <c r="E29" s="48" t="inlineStr">
+      <c r="E29" s="46" t="inlineStr">
         <is>
           <t>2026 / 2027</t>
         </is>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F29" s="47" t="n">
         <v>20000</v>
       </c>
-      <c r="G29" s="50" t="n">
+      <c r="G29" s="48" t="n">
         <v>10000</v>
       </c>
-      <c r="H29" s="50" t="n">
+      <c r="H29" s="48" t="n">
         <v>10000</v>
       </c>
-      <c r="I29" s="51" t="inlineStr">
-        <is>
-          <t>Eltek power converters ~$2K each. 8-10 more needed. Phase 3 accessories TBD. Source from Presidio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="52" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B30" s="53" t="inlineStr">
-        <is>
-          <t>NOKIA / EQUIPMENT TOTAL  (excl. Phase 2 already paid)</t>
-        </is>
-      </c>
-      <c r="F30" s="54" t="n">
+      <c r="I29" s="49" t="inlineStr">
+        <is>
+          <t>Eltek converters ~$2K each. 8-10 more needed. Phase 3 BOM TBD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUBTOTAL — NOKIA / EQUIPMENT TOTAL  (excl. Phase 2 already paid)</t>
+        </is>
+      </c>
+      <c r="F30" s="51" t="n">
         <v>450000</v>
       </c>
-      <c r="G30" s="55" t="n">
+      <c r="G30" s="52" t="n">
         <v>25000</v>
       </c>
-      <c r="H30" s="55" t="n">
+      <c r="H30" s="52" t="n">
         <v>425000</v>
       </c>
-      <c r="I30" s="56" t="n"/>
+      <c r="I30" s="53" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAR (PHASE ANGLE REGULATOR) — NEW SCOPE  |  6 Sites: Northport, Hicksville, Melville, Lindenhurst, Far Rockaway, Hewlett  |  All 2026</t>
+      <c r="A32" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAR (PHASE ANGLE REGULATOR) — NEW SCOPE  |  6 Sites: Northport · 5HK · Melville · 7Z Lindenhurst · 2H Far Rockaway · 2R Hewlett  |  All 2026</t>
         </is>
       </c>
     </row>
     <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="58" t="inlineStr">
+      <c r="A33" s="55" t="inlineStr">
         <is>
           <t>PAR – Material</t>
         </is>
       </c>
-      <c r="B33" s="59" t="inlineStr">
-        <is>
-          <t>Iniven RC-30 Equipment
-6 sites – converts direct contact → C37.94
-[PO CONFIRMED]</t>
-        </is>
-      </c>
-      <c r="C33" s="60" t="inlineStr">
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>Iniven RC-30 Equipment  [PO CONFIRMED]
+EO#7000002695 – 6 sites
+Converts direct contact → C37.94</t>
+        </is>
+      </c>
+      <c r="C33" s="57" t="inlineStr">
         <is>
           <t>EO#7000002695</t>
         </is>
       </c>
-      <c r="D33" s="61" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E33" s="61" t="inlineStr">
+      <c r="E33" s="58" t="inlineStr">
         <is>
           <t>2026 (ordered)</t>
         </is>
       </c>
-      <c r="F33" s="62" t="n">
+      <c r="F33" s="59" t="n">
         <v>52500</v>
       </c>
-      <c r="G33" s="63" t="n">
+      <c r="G33" s="60" t="n">
         <v>52500</v>
       </c>
-      <c r="H33" s="62" t="inlineStr"/>
-      <c r="I33" s="64" t="inlineStr">
-        <is>
-          <t>Approved $52,500. PO placed (Chakrapani). Iniven (I-N-I-V-E-N). 8-wk lead time. NOT a programmable device – no NERC CIP issue.</t>
+      <c r="H33" s="59" t="inlineStr"/>
+      <c r="I33" s="61" t="inlineStr">
+        <is>
+          <t>Approved $52,500. Iniven (I-N-I-V-E-N). 8-wk lead time. NOT a programmable device – no NERC CIP issue.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="65" t="inlineStr">
+      <c r="A34" s="62" t="inlineStr">
         <is>
           <t>PAR – Engineering</t>
         </is>
       </c>
-      <c r="B34" s="66" t="inlineStr">
+      <c r="B34" s="63" t="inlineStr">
         <is>
           <t>Relay Engineering – Chakrapani (Chok) team
-Design, procurement, test
-[FORECAST ONLY – actuals far lower]</t>
-        </is>
-      </c>
-      <c r="C34" s="67" t="inlineStr">
+Design, procurement, test  [FORECAST ONLY – actuals far lower]
+Valk + Samir</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
         <is>
           <t>Internal – Chok team</t>
         </is>
       </c>
-      <c r="D34" s="68" t="inlineStr">
+      <c r="D34" s="65" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E34" s="68" t="inlineStr">
-        <is>
-          <t>2026 (May–Sep)</t>
-        </is>
-      </c>
-      <c r="F34" s="69" t="n">
+      <c r="E34" s="65" t="inlineStr">
+        <is>
+          <t>2026 May–Sep</t>
+        </is>
+      </c>
+      <c r="F34" s="66" t="n">
         <v>240000</v>
       </c>
-      <c r="G34" s="70" t="n">
+      <c r="G34" s="67" t="n">
         <v>240000</v>
       </c>
-      <c r="H34" s="69" t="inlineStr"/>
-      <c r="I34" s="71" t="inlineStr">
-        <is>
-          <t>ORIGINAL FORECAST: 1,200 hrs × $200/hr = $240,000. ACTUAL TO DATE: ~$5,000 only (Valk @$65/hr + Samir @$150/hr). Expect MAJOR downward revision. Meeting being set with Chok + Locke + Samir this week to get real monthly forecast.</t>
+      <c r="H34" s="66" t="inlineStr"/>
+      <c r="I34" s="68" t="inlineStr">
+        <is>
+          <t>⚠ FORECAST ONLY: 1,200 hrs × $200 = $240K. ACTUAL TO DATE: ~$5K (Valk @$65 + Samir @$150/hr). Meeting with Chok + Locke + Samir this week – expect major downward revision.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="58" t="inlineStr">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>PAR – Install</t>
         </is>
       </c>
-      <c r="B35" s="59" t="inlineStr">
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>Relay Support – Steven Bradley / Johnny team
-Installation &amp; final testing at 6 sites
-[REVISED per email Mar 23 2026]</t>
-        </is>
-      </c>
-      <c r="C35" s="60" t="inlineStr">
+Installation &amp; final testing – 6 sites  [REVISED Mar 23 2026 email]</t>
+        </is>
+      </c>
+      <c r="C35" s="57" t="inlineStr">
         <is>
           <t>Internal – Steven's team</t>
         </is>
       </c>
-      <c r="D35" s="61" t="inlineStr">
+      <c r="D35" s="58" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E35" s="61" t="inlineStr">
-        <is>
-          <t>2026 (Aug–Dec)</t>
-        </is>
-      </c>
-      <c r="F35" s="62" t="n">
+      <c r="E35" s="58" t="inlineStr">
+        <is>
+          <t>2026 Aug–Dec</t>
+        </is>
+      </c>
+      <c r="F35" s="59" t="n">
         <v>195600</v>
       </c>
-      <c r="G35" s="63" t="n">
+      <c r="G35" s="60" t="n">
         <v>195600</v>
       </c>
-      <c r="H35" s="62" t="inlineStr"/>
-      <c r="I35" s="64" t="inlineStr">
-        <is>
-          <t>REVISED: 144 hrs/site × 5 sites = 720 hrs + supervision = 1,056 man-hours. ~$185/hr avg = $195,600. DOWN from original $494K. CIO Greg also confirmed $494K impossible. Meeting being set to confirm resource names &amp; monthly breakdown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="72" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B36" s="73" t="inlineStr">
-        <is>
-          <t>PAR TOTAL  (Chok $240K is inflated — expect ~$50-80K actual)</t>
-        </is>
-      </c>
-      <c r="F36" s="74" t="n">
+      <c r="H35" s="59" t="inlineStr"/>
+      <c r="I35" s="61" t="inlineStr">
+        <is>
+          <t>REVISED: 144 hrs/site × 5 sites = 720 hrs + supervision = 1,056 hrs. ~$185/hr avg = $195,600. Down from $494K. Meeting to confirm resource names &amp; monthly breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUBTOTAL — PAR TOTAL  (Chok $240K inflated — expect ~$50-80K actual after meeting)</t>
+        </is>
+      </c>
+      <c r="F36" s="70" t="n">
         <v>488100</v>
       </c>
-      <c r="G36" s="75" t="n">
+      <c r="G36" s="71" t="n">
         <v>488100</v>
       </c>
-      <c r="H36" s="75" t="inlineStr"/>
-      <c r="I36" s="76" t="n"/>
+      <c r="H36" s="71" t="inlineStr"/>
+      <c r="I36" s="72" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  INTERNAL PSEG / PROJECT MANAGEMENT COSTS  (Vic's framework – May 18 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+      <c r="A38" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNAL PSEG / PROJECT MANAGEMENT — Named Resources</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="38" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Internal – PM</t>
@@ -1976,10 +1986,15 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>PM – Jaya Gunaratne</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr"/>
+          <t>Jaya Gunaratne
+Project Manager – PRJ13797</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
           <t>Ph2+3</t>
@@ -2001,22 +2016,27 @@
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
-          <t>Full-time through project. PSEG internal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
+          <t>Full-time PM through project completion (Phase 2 + 3). PSEG internal charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="38" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal – Finance</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Controller – Chad</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr"/>
+          <t>Chad (Controller)
+Project Financial Controller</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
           <t>Ph2+3</t>
@@ -2038,22 +2058,27 @@
       </c>
       <c r="I40" s="18" t="inlineStr">
         <is>
-          <t>Internal financial controller.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
+          <t>Internal financial controller. SAP extract, monthly forecast, variance reporting, URB prep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="38" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal – Scheduling</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>Scheduler</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr"/>
+          <t>Umair (Scheduler)
+Project Scheduler</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Ph2+3</t>
@@ -2075,22 +2100,27 @@
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
-          <t>Internal schedule resource.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
+          <t>Internal schedule resource. Maintains Phase 2 + 3 project plans, updates milestones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="38" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal – Ops</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>Internal Labor (Raheem, Brianna et al.)</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr"/>
+          <t>Rahiq
+Internal Operations / Deployment Support</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Ph2+3</t>
@@ -2102,32 +2132,37 @@
         </is>
       </c>
       <c r="F42" s="16" t="n">
-        <v>260000</v>
+        <v>130000</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>140000</v>
+        <v>70000</v>
       </c>
       <c r="H42" s="17" t="n">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="I42" s="18" t="inlineStr">
         <is>
-          <t>PSEG internal ops/deployment support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
+          <t>PSEG internal deployment support. On-site coordination, change management, RTU migration ops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="38" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Internal – Ops</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>PQA / Assessments (3.5% cap)</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr"/>
+          <t>Brianna
+Internal Operations / Deployment Support</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Ph2+3</t>
@@ -2139,21 +2174,21 @@
         </is>
       </c>
       <c r="F43" s="16" t="n">
-        <v>220000</v>
+        <v>130000</v>
       </c>
       <c r="G43" s="17" t="n">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="H43" s="17" t="n">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
-          <t>Capped at 3.5% total budget. Joe Jekyll PCR cards for variances. PQA audit rates negotiated down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
+          <t>PSEG internal deployment support. On-site coordination, change management, RTU migration ops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="38" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
           <t>Cognizant</t>
@@ -2161,10 +2196,15 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>O/S Sr. Engineer – Lee Blackman</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr"/>
+          <t>Lee Blackman
+O/S Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Outside Services</t>
+        </is>
+      </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
           <t>Ph2+3</t>
@@ -2186,106 +2226,212 @@
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>$7,200/month through Phase 2 completion. Engineering oversight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+          <t>$7,200/month through Phase 2 completion. Engineering oversight, IP addressing, BGP design, IFR review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="38" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Relay Team Support – RTU Cutovers (John's team)
-[SEPARATE FROM PAR]</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr"/>
-      <c r="D45" s="22" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>PQA / Assessments  (capped at 3.5%)
+Process &amp; Quality Assurance overhead</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Ph2+3</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>2026 + 2027</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>220000</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>Capped at 3.5% total budget. Joe Jekyll agreed: PCR cards for budget variances. PQA audit rates negotiated down (Marge/PQA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="38" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>Internal – Relay</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Relay Team Support – John's team
+RTU Circuit Cutovers  [SEPARATE FROM PAR]</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
         <is>
           <t>Ph2</t>
         </is>
       </c>
-      <c r="E45" s="22" t="inlineStr">
+      <c r="E46" s="22" t="inlineStr">
         <is>
           <t>2026 + 2027</t>
         </is>
       </c>
-      <c r="F45" s="23" t="n">
+      <c r="F46" s="23" t="n">
         <v>500000</v>
       </c>
-      <c r="G45" s="24" t="n">
+      <c r="G46" s="24" t="n">
         <v>400000</v>
       </c>
-      <c r="H45" s="24" t="n">
+      <c r="H46" s="24" t="n">
         <v>100000</v>
       </c>
-      <c r="I45" s="25" t="inlineStr">
-        <is>
-          <t>Internal PSEG relay team for RTU circuit cutovers. Actual rate ~$65-$150/hr. Original $494K being validated against actuals — likely similar range for cutovers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="78" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="B46" s="79" t="inlineStr">
-        <is>
-          <t>INTERNAL / PM TOTAL</t>
-        </is>
-      </c>
-      <c r="F46" s="80" t="n">
+      <c r="I46" s="25" t="inlineStr">
+        <is>
+          <t>Internal PSEG relay team for RTU circuit cutovers at all Phase 2 sites. Actual rate ~$65-$150/hr. Distinct from PAR installation (Steve Bradley). Validate actuals per site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUBTOTAL — INTERNAL / PM TOTAL</t>
+        </is>
+      </c>
+      <c r="F47" s="75" t="n">
         <v>1810000</v>
       </c>
-      <c r="G46" s="81" t="n">
+      <c r="G47" s="76" t="n">
         <v>1250000</v>
       </c>
-      <c r="H46" s="81" t="n">
+      <c r="H47" s="76" t="n">
         <v>860000</v>
       </c>
-      <c r="I46" s="82" t="n"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="83" t="inlineStr">
+      <c r="I47" s="77" t="inlineStr"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="78" t="inlineStr">
         <is>
           <t xml:space="preserve">  GRAND TOTAL — ALL VENDORS + INTERNAL + PAR</t>
         </is>
       </c>
-      <c r="F48" s="84" t="n">
+      <c r="F49" s="79" t="n">
         <v>5307742</v>
       </c>
-      <c r="G48" s="85" t="n">
+      <c r="G49" s="80" t="n">
         <v>3806914</v>
       </c>
-      <c r="H48" s="85" t="n">
+      <c r="H49" s="80" t="n">
         <v>1892330</v>
       </c>
-      <c r="I48" s="86" t="inlineStr">
-        <is>
-          <t>⚠ Chok PAR engineering $240K is heavily inflated (actual ~$5K to date). Relay RTU cutovers to confirm. Phase 3 Nokia $395K is 2027. Decommissioning $40K is 2027.</t>
+      <c r="I49" s="81" t="inlineStr">
+        <is>
+          <t>⚠ Chok PAR engineering $240K is inflated (actual ~$5K). Relay RTU cutovers to confirm. Phase 3 Nokia $395K = 2027. Hawkeye decommissioning $40K = 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1"/>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  COLOUR LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   B&amp;M – Fixed price per SOW Appendix D ($23,850/site: IFR $16,695 + IFC $5,963 + As-Built $1,192)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Hawkeye – Fixed price $400,680 for Phase 2 (5 milestones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Costs split / accelerated across 2026 &amp; 2027 based on schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PAR costs – new scope not in original budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PAR Chok engineering – FORECAST ONLY. Actual ~$5K to date. Expect major downward revision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Internal PSEG named resources + deferred items (As-Builts, decommissioning, Nokia Ph3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Nokia/Presidio equipment costs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A32:J32"/>
+  <mergeCells count="21">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A59:I59"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2302,7 +2448,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -2311,63 +2457,63 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="87" t="inlineStr">
-        <is>
-          <t>B&amp;M – MPLS Node Design Cost by Site (Appendix D, SOW v03)  |  36 Phase 2 Sites  |  Total: $858,600</t>
+      <c r="A1" s="90" t="inlineStr">
+        <is>
+          <t>B&amp;M – MPLS Node Design Cost by Site  |  Appendix D, SOW v03  |  36 Phase 2 Sites  |  Total: $858,600</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="88" t="inlineStr">
-        <is>
-          <t>Per site: IFR $16,695  |  IFC $5,963  |  As-Built $1,192  |  Total per site $23,850  |  All IFRs/IFCs = 2026  |  As-Builts = 2027</t>
+      <c r="A2" s="91" t="inlineStr">
+        <is>
+          <t>Per site: IFR $16,695  |  IFC $5,963  |  As-Built $1,192  |  Total $23,850  ||  IFR + IFC = 2026  |  As-Builts = 2027</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="89" t="inlineStr">
+      <c r="A3" s="92" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B3" s="89" t="inlineStr">
+      <c r="B3" s="92" t="inlineStr">
         <is>
           <t>Site Name</t>
         </is>
       </c>
-      <c r="C3" s="89" t="inlineStr">
-        <is>
-          <t>IFR Year</t>
-        </is>
-      </c>
-      <c r="D3" s="89" t="inlineStr">
-        <is>
-          <t>IFR Cost ($)</t>
-        </is>
-      </c>
-      <c r="E3" s="89" t="inlineStr">
-        <is>
-          <t>IFC Cost ($)</t>
-        </is>
-      </c>
-      <c r="F3" s="89" t="inlineStr">
+      <c r="C3" s="92" t="inlineStr">
+        <is>
+          <t>IFR Schedule</t>
+        </is>
+      </c>
+      <c r="D3" s="92" t="inlineStr">
+        <is>
+          <t>IFR ($)</t>
+        </is>
+      </c>
+      <c r="E3" s="92" t="inlineStr">
+        <is>
+          <t>IFC ($)</t>
+        </is>
+      </c>
+      <c r="F3" s="92" t="inlineStr">
         <is>
           <t>As-Built ($)</t>
         </is>
       </c>
-      <c r="G3" s="89" t="inlineStr">
+      <c r="G3" s="92" t="inlineStr">
         <is>
           <t>Total ($)</t>
         </is>
       </c>
-      <c r="H3" s="89" t="inlineStr">
-        <is>
-          <t>Schedule (from SOW)</t>
+      <c r="H3" s="92" t="inlineStr">
+        <is>
+          <t>IFC Schedule / Notes</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="90" t="inlineStr">
+      <c r="A4" s="93" t="inlineStr">
         <is>
           <t>2H</t>
         </is>
@@ -2377,9 +2523,9 @@
           <t>Far Rockaway</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>2026 Jan–Feb</t>
+      <c r="C4" s="94" t="inlineStr">
+        <is>
+          <t>Jan 27 – Feb 23</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
@@ -2388,7 +2534,7 @@
       <c r="E4" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F4" s="91" t="n">
+      <c r="F4" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G4" s="10" t="n">
@@ -2396,46 +2542,46 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Jan–Feb  |  IFC: 2026 Mar  |  As-Built: 2027</t>
+          <t>IFC: Mar 10 – Mar 23  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="92" t="inlineStr">
+      <c r="A5" s="96" t="inlineStr">
         <is>
           <t>2K</t>
         </is>
       </c>
-      <c r="B5" s="93" t="inlineStr">
+      <c r="B5" s="97" t="inlineStr">
         <is>
           <t>Valley Stream</t>
         </is>
       </c>
-      <c r="C5" s="94" t="inlineStr">
-        <is>
-          <t>2026 Jan–Feb</t>
-        </is>
-      </c>
-      <c r="D5" s="95" t="n">
+      <c r="C5" s="98" t="inlineStr">
+        <is>
+          <t>Jan 27 – Feb 23</t>
+        </is>
+      </c>
+      <c r="D5" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E5" s="95" t="n">
+      <c r="E5" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F5" s="96" t="n">
+      <c r="F5" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G5" s="97" t="n">
+      <c r="G5" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H5" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Jan–Feb  |  IFC: 2026 Mar  |  As-Built: 2027</t>
+      <c r="H5" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Mar 10 – Mar 23  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="90" t="inlineStr">
+      <c r="A6" s="93" t="inlineStr">
         <is>
           <t>2KB</t>
         </is>
@@ -2445,9 +2591,9 @@
           <t>Cedarhurst</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>2026 Jan–Feb</t>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>Jan 27 – Feb 23</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
@@ -2456,7 +2602,7 @@
       <c r="E6" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F6" s="91" t="n">
+      <c r="F6" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -2464,46 +2610,46 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Jan–Feb  |  IFC: 2026 Mar  |  As-Built: 2027</t>
+          <t>IFC: Mar 10 – Mar 23  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="92" t="inlineStr">
+      <c r="A7" s="96" t="inlineStr">
         <is>
           <t>2R</t>
         </is>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="97" t="inlineStr">
         <is>
           <t>Hewlett</t>
         </is>
       </c>
-      <c r="C7" s="94" t="inlineStr">
-        <is>
-          <t>2026 Feb–Mar</t>
-        </is>
-      </c>
-      <c r="D7" s="95" t="n">
+      <c r="C7" s="98" t="inlineStr">
+        <is>
+          <t>Feb 17 – Mar 16</t>
+        </is>
+      </c>
+      <c r="D7" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E7" s="95" t="n">
+      <c r="E7" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F7" s="96" t="n">
+      <c r="F7" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G7" s="97" t="n">
+      <c r="G7" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H7" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Feb–Mar  |  IFC: 2026 Apr  |  As-Built: 2027</t>
+      <c r="H7" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Mar 31 – Apr 13  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="90" t="inlineStr">
+      <c r="A8" s="93" t="inlineStr">
         <is>
           <t>2R1</t>
         </is>
@@ -2513,9 +2659,9 @@
           <t>Hewlett Shelter</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>2026 Feb–Mar</t>
+      <c r="C8" s="94" t="inlineStr">
+        <is>
+          <t>Feb 17 – Mar 16</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
@@ -2524,7 +2670,7 @@
       <c r="E8" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F8" s="91" t="n">
+      <c r="F8" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -2532,46 +2678,46 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Feb–Mar  |  IFC: 2026 Apr  |  As-Built: 2027</t>
+          <t>IFC: Mar 31 – Apr 13  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="92" t="inlineStr">
+      <c r="A9" s="96" t="inlineStr">
         <is>
           <t>2RB</t>
         </is>
       </c>
-      <c r="B9" s="93" t="inlineStr">
+      <c r="B9" s="97" t="inlineStr">
         <is>
           <t>Green Acres</t>
         </is>
       </c>
-      <c r="C9" s="94" t="inlineStr">
-        <is>
-          <t>2026 Mar</t>
-        </is>
-      </c>
-      <c r="D9" s="95" t="n">
+      <c r="C9" s="98" t="inlineStr">
+        <is>
+          <t>Mar 3 – Mar 30</t>
+        </is>
+      </c>
+      <c r="D9" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E9" s="95" t="n">
+      <c r="E9" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F9" s="96" t="n">
+      <c r="F9" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G9" s="97" t="n">
+      <c r="G9" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H9" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Mar  |  IFC: 2026 Apr  |  As-Built: 2027</t>
+      <c r="H9" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Apr 14 – Apr 27  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="93" t="inlineStr">
         <is>
           <t>2WB</t>
         </is>
@@ -2581,9 +2727,9 @@
           <t>Barrett Power Plant</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>2026 Mar</t>
+      <c r="C10" s="94" t="inlineStr">
+        <is>
+          <t>Mar 3 – Mar 30</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
@@ -2592,7 +2738,7 @@
       <c r="E10" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F10" s="91" t="n">
+      <c r="F10" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -2600,46 +2746,46 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Mar  |  IFC: 2026 Apr  |  As-Built: 2027</t>
+          <t>IFC: Apr 14 – Apr 27  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="92" t="inlineStr">
+      <c r="A11" s="96" t="inlineStr">
         <is>
           <t>2ZB</t>
         </is>
       </c>
-      <c r="B11" s="93" t="inlineStr">
+      <c r="B11" s="97" t="inlineStr">
         <is>
           <t>Barrett PS (EF Barrett)</t>
         </is>
       </c>
-      <c r="C11" s="94" t="inlineStr">
-        <is>
-          <t>2026 Mar–Apr</t>
-        </is>
-      </c>
-      <c r="D11" s="95" t="n">
+      <c r="C11" s="98" t="inlineStr">
+        <is>
+          <t>Mar 17 – Apr 13</t>
+        </is>
+      </c>
+      <c r="D11" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E11" s="95" t="n">
+      <c r="E11" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F11" s="96" t="n">
+      <c r="F11" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G11" s="97" t="n">
+      <c r="G11" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H11" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Mar–Apr  |  IFC: 2026 May  |  As-Built: 2027</t>
+      <c r="H11" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Apr 28 – May 11  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="90" t="inlineStr">
+      <c r="A12" s="93" t="inlineStr">
         <is>
           <t>3J</t>
         </is>
@@ -2649,9 +2795,9 @@
           <t>Whiteside</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>2026 Mar–Apr</t>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>Mar 31 – Apr 27</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
@@ -2660,7 +2806,7 @@
       <c r="E12" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F12" s="91" t="n">
+      <c r="F12" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -2668,46 +2814,46 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Mar–Apr  |  IFC: 2026 May  |  As-Built: 2027</t>
+          <t>IFC: May 12 – May 26  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="92" t="inlineStr">
+      <c r="A13" s="96" t="inlineStr">
         <is>
           <t>4M</t>
         </is>
       </c>
-      <c r="B13" s="93" t="inlineStr">
+      <c r="B13" s="97" t="inlineStr">
         <is>
           <t>Baldwin</t>
         </is>
       </c>
-      <c r="C13" s="94" t="inlineStr">
-        <is>
-          <t>2026 Apr</t>
-        </is>
-      </c>
-      <c r="D13" s="95" t="n">
+      <c r="C13" s="98" t="inlineStr">
+        <is>
+          <t>Apr 7 – May 4</t>
+        </is>
+      </c>
+      <c r="D13" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E13" s="95" t="n">
+      <c r="E13" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F13" s="96" t="n">
+      <c r="F13" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G13" s="97" t="n">
+      <c r="G13" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H13" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Apr  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+      <c r="H13" s="102" t="inlineStr">
+        <is>
+          <t>IFC: May 19 – Jun 2  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="90" t="inlineStr">
+      <c r="A14" s="93" t="inlineStr">
         <is>
           <t>4M1</t>
         </is>
@@ -2717,9 +2863,9 @@
           <t>Baldwin Shelter</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>2026 Apr</t>
+      <c r="C14" s="94" t="inlineStr">
+        <is>
+          <t>Apr 7 – May 4</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
@@ -2728,7 +2874,7 @@
       <c r="E14" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F14" s="91" t="n">
+      <c r="F14" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G14" s="10" t="n">
@@ -2736,46 +2882,46 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Apr  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+          <t>IFC: May 19 – Jun 2  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="92" t="inlineStr">
+      <c r="A15" s="96" t="inlineStr">
         <is>
           <t>6H</t>
         </is>
       </c>
-      <c r="B15" s="93" t="inlineStr">
+      <c r="B15" s="97" t="inlineStr">
         <is>
           <t>Hauppauge</t>
         </is>
       </c>
-      <c r="C15" s="94" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
-        </is>
-      </c>
-      <c r="D15" s="95" t="n">
+      <c r="C15" s="98" t="inlineStr">
+        <is>
+          <t>Apr 14 – May 11</t>
+        </is>
+      </c>
+      <c r="D15" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E15" s="95" t="n">
+      <c r="E15" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F15" s="96" t="n">
+      <c r="F15" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G15" s="97" t="n">
+      <c r="G15" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H15" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+      <c r="H15" s="102" t="inlineStr">
+        <is>
+          <t>IFC: May 27 – Jun 9  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="90" t="inlineStr">
+      <c r="A16" s="93" t="inlineStr">
         <is>
           <t>6H1</t>
         </is>
@@ -2785,9 +2931,9 @@
           <t>Hauppauge Tower Shelter</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
+      <c r="C16" s="94" t="inlineStr">
+        <is>
+          <t>Apr 14 – May 11</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
@@ -2796,7 +2942,7 @@
       <c r="E16" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F16" s="91" t="n">
+      <c r="F16" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G16" s="10" t="n">
@@ -2804,46 +2950,46 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+          <t>IFC: May 27 – Jun 9  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="92" t="inlineStr">
+      <c r="A17" s="96" t="inlineStr">
         <is>
           <t>6K</t>
         </is>
       </c>
-      <c r="B17" s="93" t="inlineStr">
+      <c r="B17" s="97" t="inlineStr">
         <is>
           <t>State School</t>
         </is>
       </c>
-      <c r="C17" s="94" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
-        </is>
-      </c>
-      <c r="D17" s="95" t="n">
+      <c r="C17" s="98" t="inlineStr">
+        <is>
+          <t>Apr 14 – May 11</t>
+        </is>
+      </c>
+      <c r="D17" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E17" s="95" t="n">
+      <c r="E17" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F17" s="96" t="n">
+      <c r="F17" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G17" s="97" t="n">
+      <c r="G17" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H17" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+      <c r="H17" s="102" t="inlineStr">
+        <is>
+          <t>IFC: May 27 – Jun 9  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="90" t="inlineStr">
+      <c r="A18" s="93" t="inlineStr">
         <is>
           <t>6S</t>
         </is>
@@ -2853,9 +2999,9 @@
           <t>Kings Hwy</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
+      <c r="C18" s="94" t="inlineStr">
+        <is>
+          <t>Apr 21 – May 18</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
@@ -2864,7 +3010,7 @@
       <c r="E18" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F18" s="91" t="n">
+      <c r="F18" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G18" s="10" t="n">
@@ -2872,46 +3018,46 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+          <t>IFC: Jun 3 – Jun 16  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="92" t="inlineStr">
+      <c r="A19" s="96" t="inlineStr">
         <is>
           <t>7BH</t>
         </is>
       </c>
-      <c r="B19" s="93" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>Bohemia</t>
         </is>
       </c>
-      <c r="C19" s="94" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
-        </is>
-      </c>
-      <c r="D19" s="95" t="n">
+      <c r="C19" s="98" t="inlineStr">
+        <is>
+          <t>Apr 21 – May 18</t>
+        </is>
+      </c>
+      <c r="D19" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E19" s="95" t="n">
+      <c r="E19" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F19" s="96" t="n">
+      <c r="F19" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G19" s="97" t="n">
+      <c r="G19" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H19" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+      <c r="H19" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 3 – Jun 16  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="90" t="inlineStr">
+      <c r="A20" s="93" t="inlineStr">
         <is>
           <t>7D</t>
         </is>
@@ -2921,9 +3067,9 @@
           <t>West Babylon</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
+      <c r="C20" s="94" t="inlineStr">
+        <is>
+          <t>Apr 28 – May 26</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
@@ -2932,7 +3078,7 @@
       <c r="E20" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F20" s="91" t="n">
+      <c r="F20" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G20" s="10" t="n">
@@ -2940,46 +3086,46 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+          <t>IFC: Jun 10 – Jun 23  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>7D1</t>
         </is>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>West Babylon Shelter</t>
         </is>
       </c>
-      <c r="C21" s="94" t="inlineStr">
-        <is>
-          <t>2026 Apr–May</t>
-        </is>
-      </c>
-      <c r="D21" s="95" t="n">
+      <c r="C21" s="98" t="inlineStr">
+        <is>
+          <t>Apr 28 – May 26</t>
+        </is>
+      </c>
+      <c r="D21" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E21" s="95" t="n">
+      <c r="E21" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F21" s="96" t="n">
+      <c r="F21" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G21" s="97" t="n">
+      <c r="G21" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H21" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Apr–May  |  IFC: 2026 Jun  |  As-Built: 2027</t>
+      <c r="H21" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 10 – Jun 23  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="90" t="inlineStr">
+      <c r="A22" s="93" t="inlineStr">
         <is>
           <t>7H</t>
         </is>
@@ -2989,9 +3135,9 @@
           <t>Babylon</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
+      <c r="C22" s="94" t="inlineStr">
+        <is>
+          <t>May 5 – Jun 2</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
@@ -3000,7 +3146,7 @@
       <c r="E22" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F22" s="91" t="n">
+      <c r="F22" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G22" s="10" t="n">
@@ -3008,46 +3154,46 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 17 – Jun 30  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="92" t="inlineStr">
+      <c r="A23" s="96" t="inlineStr">
         <is>
           <t>7H1</t>
         </is>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>Babylon Shelter</t>
         </is>
       </c>
-      <c r="C23" s="94" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
-        </is>
-      </c>
-      <c r="D23" s="95" t="n">
+      <c r="C23" s="98" t="inlineStr">
+        <is>
+          <t>May 5 – Jun 2</t>
+        </is>
+      </c>
+      <c r="D23" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E23" s="95" t="n">
+      <c r="E23" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F23" s="96" t="n">
+      <c r="F23" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G23" s="97" t="n">
+      <c r="G23" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H23" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+      <c r="H23" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 17 – Jun 30  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="90" t="inlineStr">
+      <c r="A24" s="93" t="inlineStr">
         <is>
           <t>7J</t>
         </is>
@@ -3057,9 +3203,9 @@
           <t>Sterling</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
+      <c r="C24" s="94" t="inlineStr">
+        <is>
+          <t>May 5 – Jun 2</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
@@ -3068,7 +3214,7 @@
       <c r="E24" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F24" s="91" t="n">
+      <c r="F24" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G24" s="10" t="n">
@@ -3076,46 +3222,46 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 17 – Jun 30  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="92" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>7M</t>
         </is>
       </c>
-      <c r="B25" s="93" t="inlineStr">
+      <c r="B25" s="97" t="inlineStr">
         <is>
           <t>MacArthur</t>
         </is>
       </c>
-      <c r="C25" s="94" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
-        </is>
-      </c>
-      <c r="D25" s="95" t="n">
+      <c r="C25" s="98" t="inlineStr">
+        <is>
+          <t>May 12 – Jun 9</t>
+        </is>
+      </c>
+      <c r="D25" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E25" s="95" t="n">
+      <c r="E25" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F25" s="96" t="n">
+      <c r="F25" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G25" s="97" t="n">
+      <c r="G25" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H25" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+      <c r="H25" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="90" t="inlineStr">
+      <c r="A26" s="93" t="inlineStr">
         <is>
           <t>7R</t>
         </is>
@@ -3125,9 +3271,9 @@
           <t>Sayville</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
+      <c r="C26" s="94" t="inlineStr">
+        <is>
+          <t>May 12 – Jun 9</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
@@ -3136,7 +3282,7 @@
       <c r="E26" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F26" s="91" t="n">
+      <c r="F26" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G26" s="10" t="n">
@@ -3144,46 +3290,46 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="92" t="inlineStr">
+      <c r="A27" s="96" t="inlineStr">
         <is>
           <t>7RM</t>
         </is>
       </c>
-      <c r="B27" s="93" t="inlineStr">
+      <c r="B27" s="97" t="inlineStr">
         <is>
           <t>Bayport</t>
         </is>
       </c>
-      <c r="C27" s="94" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
-        </is>
-      </c>
-      <c r="D27" s="95" t="n">
+      <c r="C27" s="98" t="inlineStr">
+        <is>
+          <t>May 12 – Jun 9</t>
+        </is>
+      </c>
+      <c r="D27" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E27" s="95" t="n">
+      <c r="E27" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F27" s="96" t="n">
+      <c r="F27" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G27" s="97" t="n">
+      <c r="G27" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H27" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+      <c r="H27" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="90" t="inlineStr">
+      <c r="A28" s="93" t="inlineStr">
         <is>
           <t>7UM</t>
         </is>
@@ -3193,9 +3339,9 @@
           <t>South Farmingdale</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
+      <c r="C28" s="94" t="inlineStr">
+        <is>
+          <t>May 12 – Jun 9</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
@@ -3204,7 +3350,7 @@
       <c r="E28" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F28" s="91" t="n">
+      <c r="F28" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G28" s="10" t="n">
@@ -3212,46 +3358,46 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jun–Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="92" t="inlineStr">
+      <c r="A29" s="96" t="inlineStr">
         <is>
           <t>7W</t>
         </is>
       </c>
-      <c r="B29" s="93" t="inlineStr">
+      <c r="B29" s="97" t="inlineStr">
         <is>
           <t>Berry St.</t>
         </is>
       </c>
-      <c r="C29" s="94" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
-        </is>
-      </c>
-      <c r="D29" s="95" t="n">
+      <c r="C29" s="98" t="inlineStr">
+        <is>
+          <t>May 19 – Jun 16</t>
+        </is>
+      </c>
+      <c r="D29" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E29" s="95" t="n">
+      <c r="E29" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F29" s="96" t="n">
+      <c r="F29" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G29" s="97" t="n">
+      <c r="G29" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H29" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+      <c r="H29" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="93" t="inlineStr">
         <is>
           <t>7XM</t>
         </is>
@@ -3261,9 +3407,9 @@
           <t>Great River</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
+      <c r="C30" s="94" t="inlineStr">
+        <is>
+          <t>May 19 – Jun 16</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
@@ -3272,7 +3418,7 @@
       <c r="E30" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F30" s="91" t="n">
+      <c r="F30" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G30" s="10" t="n">
@@ -3280,46 +3426,46 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="92" t="inlineStr">
+      <c r="A31" s="96" t="inlineStr">
         <is>
           <t>7XM1</t>
         </is>
       </c>
-      <c r="B31" s="93" t="inlineStr">
+      <c r="B31" s="97" t="inlineStr">
         <is>
           <t>Great River Shelter</t>
         </is>
       </c>
-      <c r="C31" s="94" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
-        </is>
-      </c>
-      <c r="D31" s="95" t="n">
+      <c r="C31" s="98" t="inlineStr">
+        <is>
+          <t>May 19 – Jun 16</t>
+        </is>
+      </c>
+      <c r="D31" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E31" s="95" t="n">
+      <c r="E31" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F31" s="96" t="n">
+      <c r="F31" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G31" s="97" t="n">
+      <c r="G31" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H31" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+      <c r="H31" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="90" t="inlineStr">
+      <c r="A32" s="93" t="inlineStr">
         <is>
           <t>7Z</t>
         </is>
@@ -3329,9 +3475,9 @@
           <t>Lindenhurst</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
+      <c r="C32" s="94" t="inlineStr">
+        <is>
+          <t>May 19 – Jun 16</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
@@ -3340,7 +3486,7 @@
       <c r="E32" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F32" s="91" t="n">
+      <c r="F32" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G32" s="10" t="n">
@@ -3348,46 +3494,46 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="92" t="inlineStr">
+      <c r="A33" s="96" t="inlineStr">
         <is>
           <t>8AX</t>
         </is>
       </c>
-      <c r="B33" s="93" t="inlineStr">
+      <c r="B33" s="97" t="inlineStr">
         <is>
           <t>Patchogue</t>
         </is>
       </c>
-      <c r="C33" s="94" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
-        </is>
-      </c>
-      <c r="D33" s="95" t="n">
+      <c r="C33" s="98" t="inlineStr">
+        <is>
+          <t>May 19 – Jun 16</t>
+        </is>
+      </c>
+      <c r="D33" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E33" s="95" t="n">
+      <c r="E33" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F33" s="96" t="n">
+      <c r="F33" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G33" s="97" t="n">
+      <c r="G33" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H33" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+      <c r="H33" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="90" t="inlineStr">
+      <c r="A34" s="93" t="inlineStr">
         <is>
           <t>8AX1</t>
         </is>
@@ -3397,9 +3543,9 @@
           <t>Patchogue Shelter</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
+      <c r="C34" s="94" t="inlineStr">
+        <is>
+          <t>May 19 – Jun 16</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
@@ -3408,7 +3554,7 @@
       <c r="E34" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F34" s="91" t="n">
+      <c r="F34" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G34" s="10" t="n">
@@ -3416,46 +3562,46 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+          <t>IFC: Jun 24 – Jul 8  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="92" t="inlineStr">
+      <c r="A35" s="96" t="inlineStr">
         <is>
           <t>D.O.</t>
         </is>
       </c>
-      <c r="B35" s="93" t="inlineStr">
+      <c r="B35" s="97" t="inlineStr">
         <is>
           <t>Brentwood D.O.</t>
         </is>
       </c>
-      <c r="C35" s="94" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
-        </is>
-      </c>
-      <c r="D35" s="95" t="n">
+      <c r="C35" s="98" t="inlineStr">
+        <is>
+          <t>May 27 – Jun 23</t>
+        </is>
+      </c>
+      <c r="D35" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E35" s="95" t="n">
+      <c r="E35" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F35" s="96" t="n">
+      <c r="F35" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G35" s="97" t="n">
+      <c r="G35" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H35" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+      <c r="H35" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jul 9 – Jul 22  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="90" t="inlineStr">
+      <c r="A36" s="93" t="inlineStr">
         <is>
           <t>D.O.</t>
         </is>
@@ -3465,9 +3611,9 @@
           <t>Hewlett Headquarters</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
+      <c r="C36" s="94" t="inlineStr">
+        <is>
+          <t>May 27 – Jun 23</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
@@ -3476,7 +3622,7 @@
       <c r="E36" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F36" s="91" t="n">
+      <c r="F36" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G36" s="10" t="n">
@@ -3484,46 +3630,46 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+          <t>IFC: Jul 9 – Jul 22  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="92" t="inlineStr">
+      <c r="A37" s="96" t="inlineStr">
         <is>
           <t>5HK</t>
         </is>
       </c>
-      <c r="B37" s="93" t="inlineStr">
+      <c r="B37" s="97" t="inlineStr">
         <is>
           <t>Hicksville Primary</t>
         </is>
       </c>
-      <c r="C37" s="94" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
-        </is>
-      </c>
-      <c r="D37" s="95" t="n">
+      <c r="C37" s="98" t="inlineStr">
+        <is>
+          <t>May 27 – Jun 23</t>
+        </is>
+      </c>
+      <c r="D37" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E37" s="95" t="n">
+      <c r="E37" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F37" s="96" t="n">
+      <c r="F37" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G37" s="97" t="n">
+      <c r="G37" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H37" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+      <c r="H37" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jul 9 – Jul 22  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="90" t="inlineStr">
+      <c r="A38" s="93" t="inlineStr">
         <is>
           <t>6U</t>
         </is>
@@ -3533,9 +3679,9 @@
           <t>Ruland Road</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>2026 May–Jun</t>
+      <c r="C38" s="94" t="inlineStr">
+        <is>
+          <t>May 27 – Jun 23</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
@@ -3544,7 +3690,7 @@
       <c r="E38" s="9" t="n">
         <v>5963</v>
       </c>
-      <c r="F38" s="91" t="n">
+      <c r="F38" s="95" t="n">
         <v>1192</v>
       </c>
       <c r="G38" s="10" t="n">
@@ -3552,75 +3698,75 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>IFR: 2026 May–Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+          <t>IFC: Jul 9 – Jul 22  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="92" t="inlineStr">
+      <c r="A39" s="96" t="inlineStr">
         <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="B39" s="93" t="inlineStr">
+      <c r="B39" s="97" t="inlineStr">
         <is>
           <t>ACC</t>
         </is>
       </c>
-      <c r="C39" s="94" t="inlineStr">
-        <is>
-          <t>2026 Jun</t>
-        </is>
-      </c>
-      <c r="D39" s="95" t="n">
+      <c r="C39" s="98" t="inlineStr">
+        <is>
+          <t>Jun 3 – Jun 30</t>
+        </is>
+      </c>
+      <c r="D39" s="99" t="n">
         <v>16695</v>
       </c>
-      <c r="E39" s="95" t="n">
+      <c r="E39" s="99" t="n">
         <v>5963</v>
       </c>
-      <c r="F39" s="96" t="n">
+      <c r="F39" s="100" t="n">
         <v>1192</v>
       </c>
-      <c r="G39" s="97" t="n">
+      <c r="G39" s="101" t="n">
         <v>23850</v>
       </c>
-      <c r="H39" s="98" t="inlineStr">
-        <is>
-          <t>IFR: 2026 Jun  |  IFC: 2026 Jul  |  As-Built: 2027</t>
+      <c r="H39" s="102" t="inlineStr">
+        <is>
+          <t>IFC: Jul 16 – Jul 29  |  As-Built: 2027</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="103" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="103" t="inlineStr">
         <is>
           <t>36 sites</t>
         </is>
       </c>
-      <c r="C40" s="89" t="inlineStr">
+      <c r="C40" s="92" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="28" t="n">
         <v>601020</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="28" t="n">
         <v>214668</v>
       </c>
-      <c r="F40" s="99" t="n">
+      <c r="F40" s="104" t="n">
         <v>42912</v>
       </c>
-      <c r="G40" s="29" t="n">
+      <c r="G40" s="28" t="n">
         <v>858600</v>
       </c>
-      <c r="H40" s="100" t="inlineStr">
-        <is>
-          <t>IFR+IFC = 2026 ($815,688)  |  As-Builts = 2027 ($42,912)</t>
+      <c r="H40" s="105" t="inlineStr">
+        <is>
+          <t>IFR + IFC = 2026 ($815,688)  |  As-Builts = 2027 ($42,912)</t>
         </is>
       </c>
     </row>

--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="B&amp;M Site Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nokia Ph3 Equipment" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="51">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +129,158 @@
     </font>
     <font>
       <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <strike val="0"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <strike val="0"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <strike val="0"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <strike val="0"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <strike val="1"/>
+      <color rgb="00AA0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <strike val="1"/>
+      <color rgb="00AA0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <strike val="1"/>
+      <color rgb="00AA0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <strike val="1"/>
+      <color rgb="00AA0000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="001E5631"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="001E5631"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <strike val="0"/>
+      <color rgb="001E5631"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <strike val="0"/>
+      <color rgb="001E5631"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00AA0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00AA0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001E5631"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E5631"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="00AA0000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00AA0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="00C55A11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00C55A11"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="001E5631"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001E5631"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="007F6000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="007F6000"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -239,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -554,6 +708,151 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="39" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="41" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3777,4 +4076,866 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="106" t="inlineStr">
+        <is>
+          <t>PRJ13797 – JMUX Replacement  |  Nokia Phase 3 Equipment Order  |  Sales Doc. 14937998  |  Prepared: May 18 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="107" t="inlineStr">
+        <is>
+          <t>Changes per Ethan Koch (B&amp;M), May 12 2026:  ① Remove 4W E&amp;M cards (Item 100) — may have enough remaining from Phase 2  ② NSP IP Control licenses already removed (RMA'd)  ③ Add 4× 10G SFP+ CWDM 1491nm optics (new line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="108" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C3" s="108" t="inlineStr">
+        <is>
+          <t>Material #</t>
+        </is>
+      </c>
+      <c r="D3" s="108" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E3" s="108" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="F3" s="108" t="inlineStr">
+        <is>
+          <t>Unit Price ($)</t>
+        </is>
+      </c>
+      <c r="G3" s="108" t="inlineStr">
+        <is>
+          <t>Net Value ($)</t>
+        </is>
+      </c>
+      <c r="H3" s="108" t="inlineStr">
+        <is>
+          <t>Tax ($)</t>
+        </is>
+      </c>
+      <c r="I3" s="108" t="inlineStr">
+        <is>
+          <t>Revised Net ($)</t>
+        </is>
+      </c>
+      <c r="J3" s="108" t="inlineStr">
+        <is>
+          <t>Status / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="109" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>3HE00062CB</t>
+        </is>
+      </c>
+      <c r="D4" s="111" t="inlineStr">
+        <is>
+          <t>SFP - GIGE BASE-T RJ45 R6/6 DDM -40/85C</t>
+        </is>
+      </c>
+      <c r="E4" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" s="113" t="n">
+        <v>106.26</v>
+      </c>
+      <c r="G4" s="113" t="n">
+        <v>1487.64</v>
+      </c>
+      <c r="H4" s="114" t="n">
+        <v>130.17</v>
+      </c>
+      <c r="I4" s="115" t="n">
+        <v>1487.64</v>
+      </c>
+      <c r="J4" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="117" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="118" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C5" s="119" t="inlineStr">
+        <is>
+          <t>3HE00028CA</t>
+        </is>
+      </c>
+      <c r="D5" s="119" t="inlineStr">
+        <is>
+          <t>SFP - GIGE LX - LC ROHS 6/6 DDM -40/85C</t>
+        </is>
+      </c>
+      <c r="E5" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="121" t="n">
+        <v>111.44</v>
+      </c>
+      <c r="G5" s="121" t="n">
+        <v>1560.16</v>
+      </c>
+      <c r="H5" s="122" t="n">
+        <v>136.51</v>
+      </c>
+      <c r="I5" s="123" t="n">
+        <v>1560.16</v>
+      </c>
+      <c r="J5" s="124" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="109" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="110" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>3HE12410AA</t>
+        </is>
+      </c>
+      <c r="D6" s="111" t="inlineStr">
+        <is>
+          <t>DCE CABLE for SDI V3</t>
+        </is>
+      </c>
+      <c r="E6" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="113" t="n">
+        <v>245</v>
+      </c>
+      <c r="G6" s="113" t="n">
+        <v>3430</v>
+      </c>
+      <c r="H6" s="114" t="n">
+        <v>300.12</v>
+      </c>
+      <c r="I6" s="115" t="n">
+        <v>3430</v>
+      </c>
+      <c r="J6" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="117" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="118" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C7" s="119" t="inlineStr">
+        <is>
+          <t>3HE02784UA</t>
+        </is>
+      </c>
+      <c r="D7" s="119" t="inlineStr">
+        <is>
+          <t>SAR RELEASE 24.x BASIC OS LICENSE</t>
+        </is>
+      </c>
+      <c r="E7" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" s="121" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="G7" s="121" t="n">
+        <v>4165</v>
+      </c>
+      <c r="H7" s="122" t="n">
+        <v>364.44</v>
+      </c>
+      <c r="I7" s="123" t="n">
+        <v>4165</v>
+      </c>
+      <c r="J7" s="124" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="125" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="126" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C8" s="127" t="inlineStr">
+        <is>
+          <t>3HE16016AA</t>
+        </is>
+      </c>
+      <c r="D8" s="127" t="inlineStr">
+        <is>
+          <t>NSP IP CONTROL CLASS 1 NODE</t>
+        </is>
+      </c>
+      <c r="E8" s="125" t="n">
+        <v>56</v>
+      </c>
+      <c r="F8" s="128" t="n">
+        <v>140</v>
+      </c>
+      <c r="G8" s="128" t="n">
+        <v>7840</v>
+      </c>
+      <c r="H8" s="129" t="n">
+        <v>686</v>
+      </c>
+      <c r="I8" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="130" t="inlineStr">
+        <is>
+          <t>REMOVED – RMA'd</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="117" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="118" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C9" s="119" t="inlineStr">
+        <is>
+          <t>3HE12442AA</t>
+        </is>
+      </c>
+      <c r="D9" s="119" t="inlineStr">
+        <is>
+          <t>4 PORT RS232 DIST PANEL, SDIv3 ONLY</t>
+        </is>
+      </c>
+      <c r="E9" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" s="121" t="n">
+        <v>595</v>
+      </c>
+      <c r="G9" s="121" t="n">
+        <v>8330</v>
+      </c>
+      <c r="H9" s="122" t="n">
+        <v>728.88</v>
+      </c>
+      <c r="I9" s="123" t="n">
+        <v>8330</v>
+      </c>
+      <c r="J9" s="124" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="109" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="110" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>3HE06792FA</t>
+        </is>
+      </c>
+      <c r="D10" s="111" t="inlineStr">
+        <is>
+          <t>FAN/ALARM MODULE SAR-8 V2 -48/+24VDC cc</t>
+        </is>
+      </c>
+      <c r="E10" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="F10" s="113" t="n">
+        <v>630</v>
+      </c>
+      <c r="G10" s="113" t="n">
+        <v>8820</v>
+      </c>
+      <c r="H10" s="114" t="n">
+        <v>771.75</v>
+      </c>
+      <c r="I10" s="115" t="n">
+        <v>8820</v>
+      </c>
+      <c r="J10" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="117" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="118" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C11" s="119" t="inlineStr">
+        <is>
+          <t>3HE07354AH</t>
+        </is>
+      </c>
+      <c r="D11" s="119" t="inlineStr">
+        <is>
+          <t>RTU - MDDB LICENSE (ADDITIONAL NODES)</t>
+        </is>
+      </c>
+      <c r="E11" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="121" t="n">
+        <v>700</v>
+      </c>
+      <c r="G11" s="121" t="n">
+        <v>9800</v>
+      </c>
+      <c r="H11" s="122" t="n">
+        <v>857.5</v>
+      </c>
+      <c r="I11" s="123" t="n">
+        <v>9800</v>
+      </c>
+      <c r="J11" s="124" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="109" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="110" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>3HE06791BA</t>
+        </is>
+      </c>
+      <c r="D12" s="111" t="inlineStr">
+        <is>
+          <t>SAR-8 SHELF V2/CONFORMAL COATED</t>
+        </is>
+      </c>
+      <c r="E12" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="113" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G12" s="113" t="n">
+        <v>14700</v>
+      </c>
+      <c r="H12" s="114" t="n">
+        <v>1286.25</v>
+      </c>
+      <c r="I12" s="115" t="n">
+        <v>14700</v>
+      </c>
+      <c r="J12" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="125" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="126" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C13" s="127" t="inlineStr">
+        <is>
+          <t>3HE03126BA</t>
+        </is>
+      </c>
+      <c r="D13" s="127" t="inlineStr">
+        <is>
+          <t>6P E AND M CARD cc  (4W E&amp;M)</t>
+        </is>
+      </c>
+      <c r="E13" s="125" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="128" t="n">
+        <v>1662.5</v>
+      </c>
+      <c r="G13" s="128" t="n">
+        <v>23275</v>
+      </c>
+      <c r="H13" s="129" t="n">
+        <v>2036.56</v>
+      </c>
+      <c r="I13" s="128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="130" t="inlineStr">
+        <is>
+          <t>REMOVED – Ethan: may have enough from Phase 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="109" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="110" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>3HE07942BA</t>
+        </is>
+      </c>
+      <c r="D14" s="111" t="inlineStr">
+        <is>
+          <t>INTEGRATED SERVICES CARD (ISC) cc</t>
+        </is>
+      </c>
+      <c r="E14" s="112" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" s="113" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G14" s="113" t="n">
+        <v>29400</v>
+      </c>
+      <c r="H14" s="114" t="n">
+        <v>2572.5</v>
+      </c>
+      <c r="I14" s="115" t="n">
+        <v>29400</v>
+      </c>
+      <c r="J14" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="117" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="118" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C15" s="119" t="inlineStr">
+        <is>
+          <t>3HE07161CA</t>
+        </is>
+      </c>
+      <c r="D15" s="119" t="inlineStr">
+        <is>
+          <t>SFP+ 10GE CWDM 1471nm 40km R6/6 DDM 0/70C</t>
+        </is>
+      </c>
+      <c r="E15" s="120" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" s="121" t="n">
+        <v>1175.51</v>
+      </c>
+      <c r="G15" s="121" t="n">
+        <v>32914.28</v>
+      </c>
+      <c r="H15" s="122" t="n">
+        <v>2880</v>
+      </c>
+      <c r="I15" s="123" t="n">
+        <v>32914.28</v>
+      </c>
+      <c r="J15" s="124" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="109" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="110" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>3HE02774CB</t>
+        </is>
+      </c>
+      <c r="D16" s="111" t="inlineStr">
+        <is>
+          <t>CTL SWITCH MODULE V2  -48/+24VDC cc</t>
+        </is>
+      </c>
+      <c r="E16" s="112" t="n">
+        <v>28</v>
+      </c>
+      <c r="F16" s="113" t="n">
+        <v>1417.5</v>
+      </c>
+      <c r="G16" s="113" t="n">
+        <v>39690</v>
+      </c>
+      <c r="H16" s="114" t="n">
+        <v>3472.88</v>
+      </c>
+      <c r="I16" s="115" t="n">
+        <v>39690</v>
+      </c>
+      <c r="J16" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="117" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="118" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C17" s="119" t="inlineStr">
+        <is>
+          <t>3HE03391BC</t>
+        </is>
+      </c>
+      <c r="D17" s="119" t="inlineStr">
+        <is>
+          <t>12P SERIAL DATA CARD V3 -48/+24VDC cc</t>
+        </is>
+      </c>
+      <c r="E17" s="120" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="121" t="n">
+        <v>3780</v>
+      </c>
+      <c r="G17" s="121" t="n">
+        <v>52920</v>
+      </c>
+      <c r="H17" s="122" t="n">
+        <v>4630.5</v>
+      </c>
+      <c r="I17" s="123" t="n">
+        <v>52920</v>
+      </c>
+      <c r="J17" s="124" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="109" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="110" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>3HE07943BA</t>
+        </is>
+      </c>
+      <c r="D18" s="111" t="inlineStr">
+        <is>
+          <t>6P 2×10GE, 4×1GE 10G CARD CC</t>
+        </is>
+      </c>
+      <c r="E18" s="112" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" s="113" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G18" s="113" t="n">
+        <v>156800</v>
+      </c>
+      <c r="H18" s="114" t="n">
+        <v>13720</v>
+      </c>
+      <c r="I18" s="115" t="n">
+        <v>156800</v>
+      </c>
+      <c r="J18" s="116" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="131" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="132" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="C19" s="133" t="inlineStr">
+        <is>
+          <t>3HE07161BA</t>
+        </is>
+      </c>
+      <c r="D19" s="133" t="inlineStr">
+        <is>
+          <t>SFP+ 10GE CWDM 1491nm 40km R6/6 DDM 0/70C  ★ ADDED per Ethan Koch</t>
+        </is>
+      </c>
+      <c r="E19" s="131" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="134" t="n">
+        <v>1175.51</v>
+      </c>
+      <c r="G19" s="134" t="n">
+        <v>4702.04</v>
+      </c>
+      <c r="H19" s="135" t="n">
+        <v>411.43</v>
+      </c>
+      <c r="I19" s="134" t="n">
+        <v>4702.04</v>
+      </c>
+      <c r="J19" s="136" t="inlineStr">
+        <is>
+          <t>NEW – Added per Ethan email May 12 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Original Order Total (Sales Doc. 14937998)</t>
+        </is>
+      </c>
+      <c r="I21" s="138" t="n">
+        <v>395132.08</v>
+      </c>
+      <c r="J21" s="139" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: NSP IP Control licenses (RMA'd Item 50)</t>
+        </is>
+      </c>
+      <c r="I22" s="141" t="n">
+        <v>-7840</v>
+      </c>
+      <c r="J22" s="142" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Less: 4W E&amp;M Cards removed (Item 100)</t>
+        </is>
+      </c>
+      <c r="I23" s="141" t="n">
+        <v>-23275</v>
+      </c>
+      <c r="J23" s="142" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Add: 4× SFP+ 10GE CWDM 1491nm (NEW)</t>
+        </is>
+      </c>
+      <c r="I24" s="144" t="n">
+        <v>4702.04</v>
+      </c>
+      <c r="J24" s="145" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REVISED ORDER TOTAL</t>
+        </is>
+      </c>
+      <c r="I25" s="147" t="n">
+        <v>368719.12</v>
+      </c>
+      <c r="J25" s="148" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOTES FROM ETHAN KOCH (B&amp;M) — May 12 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="149" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B28" s="150" t="inlineStr">
+        <is>
+          <t>NSP IP Control licenses (Item 50): Already removed from this order — RMA'd. $7,840 credited back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="151" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B29" s="152" t="inlineStr">
+        <is>
+          <t>4W E&amp;M Cards (Item 100, 3HE03126BA): REMOVE from this order. Many Phase 2 sites don't need this card. We may have enough remaining inventory to carry through end of project. Confirm final count when detailed designs complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="153" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B30" s="154" t="inlineStr">
+        <is>
+          <t>10G CWDM 1491nm SFP+ optics: ADD 4 additional units of the 1491nm wavelength option (material 3HE07161BA) in addition to the 28× 1471nm units already on order. Priced at same rate as 1471nm ($1,175.51 each = $4,702.04). Added as new line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="155" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B31" s="156" t="inlineStr">
+        <is>
+          <t>Final true-up order pending. Detailed designs must be completed to get final counts for all Phase 3 sites. This order is a forecast — quantities subject to change.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="J22"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="J23"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="J24"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="J21"/>
+    <mergeCell ref="J25"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="62">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -282,6 +282,57 @@
     <font>
       <color rgb="007F6000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00C55A11"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00C55A11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="17">
@@ -367,7 +418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -389,11 +440,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -855,6 +950,50 @@
     <xf numFmtId="0" fontId="50" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="54" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="59" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1539,43 +1678,39 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="157" t="inlineStr">
         <is>
           <t>B&amp;M</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>MPLS Node Design – As-Built
-36 sites × $1,192  =  $42,912</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="158" t="inlineStr">
+        <is>
+          <t>MPLS Node Design – As-Built (Phase 2)
+→ ALL As-Builts consolidated into Phase 3 row below</t>
+        </is>
+      </c>
+      <c r="C11" s="159" t="inlineStr">
         <is>
           <t>PO7000001415 / PO7000002099</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Ph2→Ph3</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>2027 (post-cutover)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>42912</v>
-      </c>
-      <c r="G11" s="16" t="inlineStr"/>
-      <c r="H11" s="17" t="n">
-        <v>42912</v>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>B&amp;M Appendix D: 36 × $1,192. Issued AFTER construction complete. Deferred to 2027.</t>
+      <c r="D11" s="160" t="inlineStr">
+        <is>
+          <t>→ Ph3</t>
+        </is>
+      </c>
+      <c r="E11" s="160" t="inlineStr">
+        <is>
+          <t>→ See Ph3 row</t>
+        </is>
+      </c>
+      <c r="F11" s="161" t="n"/>
+      <c r="G11" s="161" t="n"/>
+      <c r="H11" s="162" t="n"/>
+      <c r="I11" s="163" t="inlineStr">
+        <is>
+          <t>★ Phase 2 As-Builts ($42,912) moved to Phase 3 consolidated row. All phases together 2027.</t>
         </is>
       </c>
     </row>
@@ -1661,43 +1796,47 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="38" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>B&amp;M</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 – As-Built
-31 sites × $1,192  =  $36,952</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>TBD – Ph3 PO</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Ph3</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>36952</v>
-      </c>
-      <c r="G14" s="16" t="inlineStr"/>
-      <c r="H14" s="17" t="n">
-        <v>36952</v>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>31 As-Builts post Phase 3 construction. All 2027.</t>
+      <c r="B14" s="164" t="inlineStr">
+        <is>
+          <t>MPLS Node Design – As-Built  ★ ALL PHASES CONSOLIDATED → PHASE 3
+Phase 1: 31 sites × $1,192 = $36,952
+Phase 2: 36 sites × $1,192 = $42,912
+Phase 3: 31 sites × $1,192 = $36,952
+TOTAL: 98 sites = $116,816</t>
+        </is>
+      </c>
+      <c r="C14" s="165" t="inlineStr">
+        <is>
+          <t>PO7000001415 / PO7000002099 / TBD Ph3</t>
+        </is>
+      </c>
+      <c r="D14" s="166" t="inlineStr">
+        <is>
+          <t>Ph1+2+3</t>
+        </is>
+      </c>
+      <c r="E14" s="166" t="inlineStr">
+        <is>
+          <t>2027 – Phase 3
+(ALL As-Builts)</t>
+        </is>
+      </c>
+      <c r="F14" s="167" t="n">
+        <v>116816</v>
+      </c>
+      <c r="G14" s="168" t="n"/>
+      <c r="H14" s="169" t="n">
+        <v>116816</v>
+      </c>
+      <c r="I14" s="170" t="inlineStr">
+        <is>
+          <t>★ UPDATED per Jay: ALL As-Builts (Ph1+Ph2+Ph3) deferred to Phase 3. Ph1: 31×$1,192=$36,952  |  Ph2: 36×$1,192=$42,912  |  Ph3: 31×$1,192=$36,952  |  TOTAL: $116,816. Issued AFTER all Phase 3 construction complete.</t>
         </is>
       </c>
     </row>
@@ -1885,43 +2024,46 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Hawkeye</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>Milestone 6:  Decommissioning
-Power down JMUX, dismantle, box &amp; ship to designated location – All 36 Phase 2 sites</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PO7000002099</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Ph2→Ph3</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>2027 (post-migration)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>40068</v>
-      </c>
-      <c r="G22" s="16" t="inlineStr"/>
-      <c r="H22" s="17" t="n">
-        <v>40068</v>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>Hawkeye SOW Milestone 6: $40,068 (10%). Cannot start until ALL circuits migrated off JMUX by relay team. Likely 2027.</t>
+      <c r="B22" s="164" t="inlineStr">
+        <is>
+          <t>Hawkeye – Decommissioning  ★ ALL PHASES IN PHASE 3
+Phase 2: 36 sites – $40,068  (SOW Milestone 6, 10% of SOW)
+Phase 3: 31 sites – ~$34,503  (est. $1,113/site same rate)
+TOTAL: 67 sites = ~$74,571</t>
+        </is>
+      </c>
+      <c r="C22" s="165" t="inlineStr">
+        <is>
+          <t>PO7000002099 / TBD Ph3</t>
+        </is>
+      </c>
+      <c r="D22" s="166" t="inlineStr">
+        <is>
+          <t>Ph2+Ph3</t>
+        </is>
+      </c>
+      <c r="E22" s="166" t="inlineStr">
+        <is>
+          <t>2027 – Phase 3
+(ALL Decommissioning)</t>
+        </is>
+      </c>
+      <c r="F22" s="167" t="n">
+        <v>74571</v>
+      </c>
+      <c r="G22" s="168" t="n"/>
+      <c r="H22" s="169" t="n">
+        <v>74571</v>
+      </c>
+      <c r="I22" s="170" t="inlineStr">
+        <is>
+          <t>★ UPDATED per Jay: ALL Hawkeye decommissioning moved to Phase 3. Cannot begin until ALL circuits migrated off JMUX across all phases. Ph2 SOW Milestone 6 = $40,068  |  Ph3 estimated = ~$34,503 (31 sites @ $1,113/site)  |  TOTAL ~$74,571.</t>
         </is>
       </c>
     </row>
@@ -2643,11 +2785,11 @@
         <v>3806914</v>
       </c>
       <c r="H49" s="80" t="n">
-        <v>1892330</v>
+        <v>1963785</v>
       </c>
       <c r="I49" s="81" t="inlineStr">
         <is>
-          <t>⚠ Chok PAR engineering $240K is inflated (actual ~$5K). Relay RTU cutovers to confirm. Phase 3 Nokia $395K = 2027. Hawkeye decommissioning $40K = 2027.</t>
+          <t>★ UPDATED: ALL As-Builts (98 sites, $116,816) → Phase 3 2027. ALL Decommissioning (67 sites, ~$74,571) → Phase 3 2027. Chok PAR $240K inflated — meeting pending. Nokia Ph3 $368,719 (Ethan May 12).</t>
         </is>
       </c>
     </row>
@@ -4812,6 +4954,13 @@
           <t xml:space="preserve">  Original Order Total (Sales Doc. 14937998)</t>
         </is>
       </c>
+      <c r="B21" s="171" t="n"/>
+      <c r="C21" s="171" t="n"/>
+      <c r="D21" s="171" t="n"/>
+      <c r="E21" s="171" t="n"/>
+      <c r="F21" s="171" t="n"/>
+      <c r="G21" s="171" t="n"/>
+      <c r="H21" s="172" t="n"/>
       <c r="I21" s="138" t="n">
         <v>395132.08</v>
       </c>
@@ -4823,6 +4972,13 @@
           <t xml:space="preserve">  Less: NSP IP Control licenses (RMA'd Item 50)</t>
         </is>
       </c>
+      <c r="B22" s="171" t="n"/>
+      <c r="C22" s="171" t="n"/>
+      <c r="D22" s="171" t="n"/>
+      <c r="E22" s="171" t="n"/>
+      <c r="F22" s="171" t="n"/>
+      <c r="G22" s="171" t="n"/>
+      <c r="H22" s="172" t="n"/>
       <c r="I22" s="141" t="n">
         <v>-7840</v>
       </c>
@@ -4834,6 +4990,13 @@
           <t xml:space="preserve">  Less: 4W E&amp;M Cards removed (Item 100)</t>
         </is>
       </c>
+      <c r="B23" s="171" t="n"/>
+      <c r="C23" s="171" t="n"/>
+      <c r="D23" s="171" t="n"/>
+      <c r="E23" s="171" t="n"/>
+      <c r="F23" s="171" t="n"/>
+      <c r="G23" s="171" t="n"/>
+      <c r="H23" s="172" t="n"/>
       <c r="I23" s="141" t="n">
         <v>-23275</v>
       </c>
@@ -4845,6 +5008,13 @@
           <t xml:space="preserve">  Add: 4× SFP+ 10GE CWDM 1491nm (NEW)</t>
         </is>
       </c>
+      <c r="B24" s="171" t="n"/>
+      <c r="C24" s="171" t="n"/>
+      <c r="D24" s="171" t="n"/>
+      <c r="E24" s="171" t="n"/>
+      <c r="F24" s="171" t="n"/>
+      <c r="G24" s="171" t="n"/>
+      <c r="H24" s="172" t="n"/>
       <c r="I24" s="144" t="n">
         <v>4702.04</v>
       </c>
@@ -4856,6 +5026,13 @@
           <t xml:space="preserve">  REVISED ORDER TOTAL</t>
         </is>
       </c>
+      <c r="B25" s="171" t="n"/>
+      <c r="C25" s="171" t="n"/>
+      <c r="D25" s="171" t="n"/>
+      <c r="E25" s="171" t="n"/>
+      <c r="F25" s="171" t="n"/>
+      <c r="G25" s="171" t="n"/>
+      <c r="H25" s="172" t="n"/>
       <c r="I25" s="147" t="n">
         <v>368719.12</v>
       </c>
@@ -4879,6 +5056,14 @@
           <t>NSP IP Control licenses (Item 50): Already removed from this order — RMA'd. $7,840 credited back.</t>
         </is>
       </c>
+      <c r="C28" s="171" t="n"/>
+      <c r="D28" s="171" t="n"/>
+      <c r="E28" s="171" t="n"/>
+      <c r="F28" s="171" t="n"/>
+      <c r="G28" s="171" t="n"/>
+      <c r="H28" s="171" t="n"/>
+      <c r="I28" s="171" t="n"/>
+      <c r="J28" s="172" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="151" t="inlineStr">
@@ -4891,6 +5076,14 @@
           <t>4W E&amp;M Cards (Item 100, 3HE03126BA): REMOVE from this order. Many Phase 2 sites don't need this card. We may have enough remaining inventory to carry through end of project. Confirm final count when detailed designs complete.</t>
         </is>
       </c>
+      <c r="C29" s="171" t="n"/>
+      <c r="D29" s="171" t="n"/>
+      <c r="E29" s="171" t="n"/>
+      <c r="F29" s="171" t="n"/>
+      <c r="G29" s="171" t="n"/>
+      <c r="H29" s="171" t="n"/>
+      <c r="I29" s="171" t="n"/>
+      <c r="J29" s="172" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="153" t="inlineStr">
@@ -4903,6 +5096,14 @@
           <t>10G CWDM 1491nm SFP+ optics: ADD 4 additional units of the 1491nm wavelength option (material 3HE07161BA) in addition to the 28× 1471nm units already on order. Priced at same rate as 1471nm ($1,175.51 each = $4,702.04). Added as new line.</t>
         </is>
       </c>
+      <c r="C30" s="171" t="n"/>
+      <c r="D30" s="171" t="n"/>
+      <c r="E30" s="171" t="n"/>
+      <c r="F30" s="171" t="n"/>
+      <c r="G30" s="171" t="n"/>
+      <c r="H30" s="171" t="n"/>
+      <c r="I30" s="171" t="n"/>
+      <c r="J30" s="172" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="155" t="inlineStr">
@@ -4915,6 +5116,14 @@
           <t>Final true-up order pending. Detailed designs must be completed to get final counts for all Phase 3 sites. This order is a forecast — quantities subject to change.</t>
         </is>
       </c>
+      <c r="C31" s="171" t="n"/>
+      <c r="D31" s="171" t="n"/>
+      <c r="E31" s="171" t="n"/>
+      <c r="F31" s="171" t="n"/>
+      <c r="G31" s="171" t="n"/>
+      <c r="H31" s="171" t="n"/>
+      <c r="I31" s="171" t="n"/>
+      <c r="J31" s="172" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4926,8 +5135,8 @@
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A27:J27"/>
     <mergeCell ref="J24"/>
-    <mergeCell ref="A27:J27"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="J21"/>
     <mergeCell ref="J25"/>

--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -10,6 +10,7 @@
     <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="B&amp;M Site Breakdown" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Nokia Ph3 Equipment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Internal Labor" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="62">
+  <fonts count="64">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -334,8 +335,18 @@
       <color rgb="00C55A11"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -417,6 +428,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F5C7A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -488,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -994,6 +1010,112 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5147,4 +5269,2315 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="106" t="inlineStr">
+        <is>
+          <t>PRJ13797 – JMUX Replacement  |  Internal Labor &amp; Outside Services Breakdown  |  Source: Chad's Controller Workbook (May 18 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="173" t="inlineStr">
+        <is>
+          <t>CP Budget: $6,600,000  |  Spend to Date: $5,908,822  |  Remaining Budget: $691,178  |  ETC: $1,228,577  |  EAC: $7,137,399  |  Projected Variance: -$537,399 (-8.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SECTION 1 — PROJECT FINANCIAL SUMMARY  (from Dashboard tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2024 O&amp;M</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2025 O&amp;M</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>O&amp;M Total</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2024 Cap</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2025 Cap</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Cap Total</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Proj Total</t>
+        </is>
+      </c>
+      <c r="I4" s="175" t="inlineStr"/>
+      <c r="J4" s="175" t="inlineStr"/>
+      <c r="K4" s="175" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Internal Labor</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>93702</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>93702</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>29358</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>134069</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>163427</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>257129</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>601380</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>219015</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>820395</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>820395</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Outside Services</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n">
+        <v>162200</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>169368</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>103409</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>1549312</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>1652721</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>1822089</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr"/>
+      <c r="J7" s="12" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Assessments</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>19172</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>19172</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>7060</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>56330</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>63390</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>82562</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="176" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="75" t="n">
+        <v>275074</v>
+      </c>
+      <c r="C9" s="75" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D9" s="75" t="n">
+        <v>282242</v>
+      </c>
+      <c r="E9" s="75" t="n">
+        <v>741206</v>
+      </c>
+      <c r="F9" s="75" t="n">
+        <v>1958726</v>
+      </c>
+      <c r="G9" s="75" t="n">
+        <v>2699932</v>
+      </c>
+      <c r="H9" s="75" t="n">
+        <v>2982174</v>
+      </c>
+      <c r="I9" s="177" t="inlineStr"/>
+      <c r="J9" s="177" t="inlineStr"/>
+      <c r="K9" s="177" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SECTION 2 — INTERNAL PSEG LABOR  (from Detailed Forecast vs Actuals tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="179" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="179" t="inlineStr">
+        <is>
+          <t>Resource Name</t>
+        </is>
+      </c>
+      <c r="C12" s="179" t="inlineStr">
+        <is>
+          <t>Role / Title</t>
+        </is>
+      </c>
+      <c r="D12" s="179" t="inlineStr">
+        <is>
+          <t>WBS Code</t>
+        </is>
+      </c>
+      <c r="E12" s="179" t="inlineStr">
+        <is>
+          <t>2025 Rate ($/hr)</t>
+        </is>
+      </c>
+      <c r="F12" s="179" t="inlineStr">
+        <is>
+          <t>2026 Rate</t>
+        </is>
+      </c>
+      <c r="G12" s="179" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H12" s="179" t="inlineStr">
+        <is>
+          <t>2025 Actuals</t>
+        </is>
+      </c>
+      <c r="I12" s="179" t="inlineStr">
+        <is>
+          <t>2026 Forecast</t>
+        </is>
+      </c>
+      <c r="J12" s="179" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K12" s="179" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>MARTIN GATELY</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E13" s="181" t="n">
+        <v>116.84</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>133886</v>
+      </c>
+      <c r="I13" s="35" t="inlineStr"/>
+      <c r="J13" s="36" t="n">
+        <v>133886</v>
+      </c>
+      <c r="K13" s="37" t="inlineStr">
+        <is>
+          <t>Actuals: Dec $12,093, Jan $13,270, Feb $8,144 + prior months. PM role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="93" t="inlineStr">
+        <is>
+          <t>DHANANJAYA GUNARATNE</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Project Manager (Jay)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E14" s="183" t="n">
+        <v>145</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>$145/hr</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="10" t="n">
+        <v>174000</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>174000</v>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>Hermitage / PM. $145/hr rate. Full-time PM through project completion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="97" t="inlineStr">
+        <is>
+          <t>Ahsan Khawaja</t>
+        </is>
+      </c>
+      <c r="C15" s="97" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="D15" s="185" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E15" s="186" t="n">
+        <v>257619</v>
+      </c>
+      <c r="F15" s="187" t="inlineStr">
+        <is>
+          <t>257619</t>
+        </is>
+      </c>
+      <c r="G15" s="187" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H15" s="99" t="inlineStr"/>
+      <c r="I15" s="101" t="n">
+        <v>257619</v>
+      </c>
+      <c r="J15" s="101" t="n">
+        <v>257619</v>
+      </c>
+      <c r="K15" s="102" t="inlineStr">
+        <is>
+          <t>Hermitage / PM. PO amount $257,618.69.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>RAHIQ MOHAMED</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Engineer / Deployment Support</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E16" s="183" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Engineer, on-site deployment support. $92.65/hr 2025 rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>BRIANNA FOREMAN</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Engineer / Deployment Support</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E17" s="183" t="n">
+        <v>92.65000000000001</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Engineer, on-site deployment support. $92.65/hr 2025 rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="188" t="inlineStr">
+        <is>
+          <t>CHAKRAPANI VENUGOPALAN</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>PAR Engineering Lead (Chok)</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E18" s="181" t="n">
+        <v>134.14</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>235000</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>240000</v>
+      </c>
+      <c r="K18" s="37" t="inlineStr">
+        <is>
+          <t>⚠ FORECAST INFLATED: 1,200 hrs × $134.14 = $160,968 MAX (not $240K). Actual to date ~$5K. Meeting this week to confirm real forecast. Note: Lok Wong = $115.34/hr, Sameer Shakur = $66.50/hr also on PAR design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="97" t="inlineStr">
+        <is>
+          <t>LOK WONG</t>
+        </is>
+      </c>
+      <c r="C19" s="97" t="inlineStr">
+        <is>
+          <t>PAR Design Engineer</t>
+        </is>
+      </c>
+      <c r="D19" s="185" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E19" s="189" t="n">
+        <v>115.34</v>
+      </c>
+      <c r="F19" s="187" t="inlineStr">
+        <is>
+          <t>Add FRINGE</t>
+        </is>
+      </c>
+      <c r="G19" s="187" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H19" s="99" t="inlineStr"/>
+      <c r="I19" s="101" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J19" s="101" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K19" s="102" t="inlineStr">
+        <is>
+          <t>PAR design support. Rate $115.34/hr + fringe. Subset of Chok PAR team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Sameer Shakur</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>PAR Design Engineer</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E20" s="191" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Add FRINGE</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>PAR design support. Rate $66.50/hr + fringe. Subset of Chok PAR team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="180" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="188" t="inlineStr">
+        <is>
+          <t>STEVEN BRADLEY</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Relay Team / PAR Installation Lead</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E21" s="181" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G21" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>58716</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>195600</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>254316</v>
+      </c>
+      <c r="K21" s="37" t="inlineStr">
+        <is>
+          <t>PAR installation at 6 sites. 2025 actuals: Dec $29,358 × 2 WBS codes = $58,716. 2026 forecast: 1,056 hrs × ~$185/hr = $195,600 (revised from $494K).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Lee Blackman</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Sr. Network Architect (Cognizant O/S)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E22" s="192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>$7,200/mo</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr"/>
+      <c r="I22" s="17" t="n">
+        <v>86400</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>86400</v>
+      </c>
+      <c r="K22" s="18" t="inlineStr">
+        <is>
+          <t>Cognizant outside services. $7,200/month through Phase 2. Listed under internal in workbook but billed as outside services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="180" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>KELLY VAUGHN</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>T&amp;D Substation Engineer</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E23" s="181" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G23" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H23" s="36" t="n">
+        <v>624</v>
+      </c>
+      <c r="I23" s="36" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J23" s="36" t="n">
+        <v>20624</v>
+      </c>
+      <c r="K23" s="37" t="inlineStr">
+        <is>
+          <t>Feb actuals $624.45. Senior Engineer T&amp;D substation support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="180" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Artur Karczewski</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>IT Ops Senior Analyst</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E24" s="181" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G24" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H24" s="36" t="n">
+        <v>521</v>
+      </c>
+      <c r="I24" s="36" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J24" s="36" t="n">
+        <v>15521</v>
+      </c>
+      <c r="K24" s="37" t="inlineStr">
+        <is>
+          <t>Feb actuals $520.64. IT Ops support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="180" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>GEORGES VOLCY</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>IT Ops Principal</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E25" s="181" t="n">
+        <v>83.83</v>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G25" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="n">
+        <v>210</v>
+      </c>
+      <c r="I25" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J25" s="36" t="n">
+        <v>10210</v>
+      </c>
+      <c r="K25" s="37" t="inlineStr">
+        <is>
+          <t>Feb actuals $209.58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="180" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>LAWRENCE VARGHESE</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>IT Ops Associate</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E26" s="181" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G26" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H26" s="36" t="n">
+        <v>406</v>
+      </c>
+      <c r="I26" s="36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J26" s="36" t="n">
+        <v>10406</v>
+      </c>
+      <c r="K26" s="37" t="inlineStr">
+        <is>
+          <t>Feb actuals $406.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="184" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="97" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER ZIMBALIST</t>
+        </is>
+      </c>
+      <c r="C27" s="97" t="inlineStr">
+        <is>
+          <t>IT Staff</t>
+        </is>
+      </c>
+      <c r="D27" s="185" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E27" s="189" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="F27" s="187" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G27" s="187" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H27" s="99" t="inlineStr"/>
+      <c r="I27" s="101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J27" s="101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K27" s="102" t="inlineStr">
+        <is>
+          <t>$82.86/hr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="193" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>Margaret Tanner Glover</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="inlineStr">
+        <is>
+          <t>PQA / Quality Assurance (Marge)</t>
+        </is>
+      </c>
+      <c r="D28" s="57" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E28" s="194" t="n">
+        <v>113.57</v>
+      </c>
+      <c r="F28" s="58" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G28" s="58" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H28" s="59" t="inlineStr"/>
+      <c r="I28" s="60" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J28" s="60" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K28" s="61" t="inlineStr">
+        <is>
+          <t>PQA audit time. Rate $113.57/hr. Audit hours being reconciled — possible overcharging under investigation. Capped at 3.5% total budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="184" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B29" s="97" t="inlineStr">
+        <is>
+          <t>EVAN SOVIERO</t>
+        </is>
+      </c>
+      <c r="C29" s="97" t="inlineStr">
+        <is>
+          <t>IT Staff / PM Support</t>
+        </is>
+      </c>
+      <c r="D29" s="185" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E29" s="189" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="F29" s="187" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G29" s="187" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H29" s="99" t="inlineStr"/>
+      <c r="I29" s="101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J29" s="101" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K29" s="102" t="inlineStr">
+        <is>
+          <t>$75.39/hr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="190" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>ALFREDO TELLO</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Project Manager (prior)</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E30" s="191" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr"/>
+      <c r="J30" s="17" t="inlineStr"/>
+      <c r="K30" s="18" t="inlineStr">
+        <is>
+          <t>Previous PM. No 2026 forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="184" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B31" s="97" t="inlineStr">
+        <is>
+          <t>Matthew Costa</t>
+        </is>
+      </c>
+      <c r="C31" s="97" t="inlineStr">
+        <is>
+          <t>Project Manager (prior)</t>
+        </is>
+      </c>
+      <c r="D31" s="185" t="inlineStr">
+        <is>
+          <t>I.39424.2.1</t>
+        </is>
+      </c>
+      <c r="E31" s="189" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="F31" s="187" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="G31" s="187" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H31" s="99" t="inlineStr"/>
+      <c r="I31" s="99" t="inlineStr"/>
+      <c r="J31" s="101" t="inlineStr"/>
+      <c r="K31" s="102" t="inlineStr">
+        <is>
+          <t>Previous PM. No 2026 forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUBTOTAL — INTERNAL PSEG LABOR (all named resources)</t>
+        </is>
+      </c>
+      <c r="H32" s="196" t="n">
+        <v>199363</v>
+      </c>
+      <c r="I32" s="196" t="n">
+        <v>1253619</v>
+      </c>
+      <c r="J32" s="196" t="n">
+        <v>1452982</v>
+      </c>
+      <c r="K32" s="197" t="inlineStr">
+        <is>
+          <t>⚠ Chok PAR $235K 2026 forecast is inflated — actual ~$5K. Expect revision after meeting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SECTION 3 — OUTSIDE SERVICES  (from Controller Workbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="198" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B35" s="198" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C35" s="198" t="inlineStr">
+        <is>
+          <t>Service / Person</t>
+        </is>
+      </c>
+      <c r="D35" s="198" t="inlineStr">
+        <is>
+          <t>WBS Code</t>
+        </is>
+      </c>
+      <c r="E35" s="198" t="inlineStr">
+        <is>
+          <t>PO Number</t>
+        </is>
+      </c>
+      <c r="F35" s="198" t="inlineStr">
+        <is>
+          <t>PO Amount</t>
+        </is>
+      </c>
+      <c r="G35" s="198" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H35" s="198" t="inlineStr">
+        <is>
+          <t>2025 Actuals</t>
+        </is>
+      </c>
+      <c r="I35" s="198" t="inlineStr">
+        <is>
+          <t>2026 Forecast</t>
+        </is>
+      </c>
+      <c r="J35" s="198" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K35" s="198" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B36" s="188" t="inlineStr">
+        <is>
+          <t>Burns &amp; McDonnell</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Alex Lennox — PM Coordination</t>
+        </is>
+      </c>
+      <c r="D36" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E36" s="33" t="inlineStr">
+        <is>
+          <t>7000001429 / 5000055979</t>
+        </is>
+      </c>
+      <c r="F36" s="35" t="n">
+        <v>316200</v>
+      </c>
+      <c r="G36" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H36" s="35" t="inlineStr"/>
+      <c r="I36" s="36" t="n">
+        <v>66000</v>
+      </c>
+      <c r="J36" s="36" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K36" s="37" t="inlineStr">
+        <is>
+          <t>$5,500/mo × 12 = $66,000 2026. Two PO numbers both $316,200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="188" t="inlineStr">
+        <is>
+          <t>Burns &amp; McDonnell</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Implementation — Construction Support</t>
+        </is>
+      </c>
+      <c r="D37" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E37" s="33" t="inlineStr">
+        <is>
+          <t>7000001415 / 5000058992</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="n">
+        <v>788100</v>
+      </c>
+      <c r="G37" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H37" s="36" t="n">
+        <v>788100</v>
+      </c>
+      <c r="I37" s="36" t="n">
+        <v>382824</v>
+      </c>
+      <c r="J37" s="36" t="n">
+        <v>1170924</v>
+      </c>
+      <c r="K37" s="37" t="inlineStr">
+        <is>
+          <t>Phase 1 CSC complete ($368,100 paid 2025). Phase 2 CSC = $382,824 starts Aug 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B38" s="188" t="inlineStr">
+        <is>
+          <t>Burns &amp; McDonnell</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>JMUX Network Design (SOW v03)</t>
+        </is>
+      </c>
+      <c r="D38" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>7000002099</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="n">
+        <v>1370040</v>
+      </c>
+      <c r="G38" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H38" s="36" t="n">
+        <v>229380</v>
+      </c>
+      <c r="I38" s="36" t="n">
+        <v>901020</v>
+      </c>
+      <c r="J38" s="36" t="n">
+        <v>1130400</v>
+      </c>
+      <c r="K38" s="37" t="inlineStr">
+        <is>
+          <t>SOW $1,370,040 total. Site surveys + IFR + IFC + staging. 2025 actuals = surveys/staging. 2026 = bulk of IFR/IFC work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B39" s="93" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Lee Blackman — Sr. Network Architect</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>7000002490 / 7000000729</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>86400</v>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="10" t="n">
+        <v>86400</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>86400</v>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>$7,200/month through Phase 2 completion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B40" s="93" t="inlineStr">
+        <is>
+          <t>Hermitage</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Dhananjaya Gunaratne — PM</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>7000002000</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr"/>
+      <c r="I40" s="10" t="n">
+        <v>174000</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>174000</v>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>$145/hr. Full-time PM. Also listed under internal labor above — avoid double counting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="182" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B41" s="93" t="inlineStr">
+        <is>
+          <t>Hermitage</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Ahsan Khawaja — PM</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>7000001734</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>257619</v>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr"/>
+      <c r="I41" s="10" t="n">
+        <v>257619</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>257619</v>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>PO amount $257,618.69.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B42" s="199" t="inlineStr">
+        <is>
+          <t>Hermitage</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Edward Laurence Schwartz — PQA Lead</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>7000001998</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr"/>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr"/>
+      <c r="I42" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>PQA lead support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="199" t="inlineStr">
+        <is>
+          <t>ComTec</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>Chad Boyett — Controller</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>5000060473</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr"/>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr"/>
+      <c r="I43" s="17" t="n">
+        <v>60000</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>60000</v>
+      </c>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>Rate = 5% (of what — TBD). Controller, SAP extract, monthly forecast, variance reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="190" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B44" s="199" t="inlineStr">
+        <is>
+          <t>ComTec</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Umair Mohammed — Scheduler</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>7000001145 / 7000002363</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr"/>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr"/>
+      <c r="I44" s="17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t>Project scheduler. Maintains Phase 2+3 plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B45" s="199" t="inlineStr">
+        <is>
+          <t>ComTec</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Farouk Adelekan — Scheduler (backup)</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>5000046818</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr"/>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr"/>
+      <c r="I45" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K45" s="18" t="inlineStr">
+        <is>
+          <t>Rate = 2.5%. Backup scheduler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="193" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B46" s="200" t="inlineStr">
+        <is>
+          <t>Cognizant / EPMO</t>
+        </is>
+      </c>
+      <c r="C46" s="56" t="inlineStr">
+        <is>
+          <t>PQA Audit</t>
+        </is>
+      </c>
+      <c r="D46" s="57" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E46" s="57" t="inlineStr">
+        <is>
+          <t>7000002439 / 7000001527</t>
+        </is>
+      </c>
+      <c r="F46" s="59" t="inlineStr"/>
+      <c r="G46" s="58" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H46" s="60" t="n">
+        <v>56330</v>
+      </c>
+      <c r="I46" s="60" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J46" s="60" t="n">
+        <v>96330</v>
+      </c>
+      <c r="K46" s="61" t="inlineStr">
+        <is>
+          <t>2025 actuals $56,330. PQA audit time. Rate under investigation (Marge). Capped at 3.5% total budget per Joe Jekyll PCR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="180" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B47" s="188" t="inlineStr">
+        <is>
+          <t>Elecnor Hawkeye</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>Phase 1 SOW + Addendum 1</t>
+        </is>
+      </c>
+      <c r="D47" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E47" s="33" t="inlineStr">
+        <is>
+          <t>MA#8447</t>
+        </is>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>402793</v>
+      </c>
+      <c r="G47" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H47" s="36" t="n">
+        <v>335993</v>
+      </c>
+      <c r="I47" s="35" t="inlineStr"/>
+      <c r="J47" s="36" t="n">
+        <v>335993</v>
+      </c>
+      <c r="K47" s="37" t="inlineStr">
+        <is>
+          <t>Phase 1 complete. $402,793 total (base $333,900 + addendum $68,893). M6 decommission $66,780 unpaid → Phase 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="180" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B48" s="188" t="inlineStr">
+        <is>
+          <t>Elecnor Hawkeye</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>Phase 2 SOW</t>
+        </is>
+      </c>
+      <c r="D48" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E48" s="33" t="inlineStr">
+        <is>
+          <t>PO7000002099</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>400680</v>
+      </c>
+      <c r="G48" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H48" s="35" t="inlineStr"/>
+      <c r="I48" s="36" t="n">
+        <v>360612</v>
+      </c>
+      <c r="J48" s="36" t="n">
+        <v>360612</v>
+      </c>
+      <c r="K48" s="37" t="inlineStr">
+        <is>
+          <t>Phase 2 SOW $400,680. M6 decommission $40,068 → Phase 3. 2026 = M-Ph0+M1+M2+M4 = $360,612.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="180" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B49" s="188" t="inlineStr">
+        <is>
+          <t>Elecnor Hawkeye</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>WD#8 — Fiber Testing + Patch Panels</t>
+        </is>
+      </c>
+      <c r="D49" s="33" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>7000009182</t>
+        </is>
+      </c>
+      <c r="F49" s="35" t="n">
+        <v>8229</v>
+      </c>
+      <c r="G49" s="34" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H49" s="35" t="inlineStr"/>
+      <c r="I49" s="36" t="n">
+        <v>8229</v>
+      </c>
+      <c r="J49" s="36" t="n">
+        <v>8229</v>
+      </c>
+      <c r="K49" s="37" t="inlineStr">
+        <is>
+          <t>WD#8: Fiber testing Elwood→Northport + 7 patch panels = $8,229.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="190" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B50" s="199" t="inlineStr">
+        <is>
+          <t>TRC</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Raju Khedkar — Cyber Security Architect</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>7000001237 / 7000002343</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr"/>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr"/>
+      <c r="I50" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K50" s="18" t="inlineStr">
+        <is>
+          <t>NERC-CIP / cyber security design review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="190" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B51" s="199" t="inlineStr">
+        <is>
+          <t>Beeline</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>Marcott, Richard</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>I.39424.2.3</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>4501316055</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr"/>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr"/>
+      <c r="I51" s="16" t="inlineStr"/>
+      <c r="J51" s="17" t="inlineStr"/>
+      <c r="K51" s="18" t="inlineStr">
+        <is>
+          <t>Beeline contractor. No 2026 forecast entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUBTOTAL — OUTSIDE SERVICES (all vendors)</t>
+        </is>
+      </c>
+      <c r="H52" s="201" t="n">
+        <v>1409803</v>
+      </c>
+      <c r="I52" s="201" t="n">
+        <v>2456704</v>
+      </c>
+      <c r="J52" s="201" t="n">
+        <v>3866507</v>
+      </c>
+      <c r="K52" s="202" t="inlineStr">
+        <is>
+          <t>NOTE: Jay/Ahsan in both Internal Labor and Outside Services — avoid double counting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SECTION 4 — KEY CONTROLLER NOTES  (from Chad's workbook, May 18 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="203" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B55" s="203" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C55" s="203" t="inlineStr">
+        <is>
+          <t>Notes / Context</t>
+        </is>
+      </c>
+      <c r="D55" s="204" t="n"/>
+      <c r="E55" s="204" t="n"/>
+      <c r="F55" s="204" t="n"/>
+      <c r="G55" s="204" t="n"/>
+      <c r="H55" s="204" t="n"/>
+      <c r="I55" s="204" t="n"/>
+      <c r="J55" s="204" t="n"/>
+      <c r="K55" s="204" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="93" t="inlineStr">
+        <is>
+          <t>CP Budget</t>
+        </is>
+      </c>
+      <c r="B56" s="205" t="inlineStr">
+        <is>
+          <t>$6,600,000</t>
+        </is>
+      </c>
+      <c r="C56" s="206" t="inlineStr">
+        <is>
+          <t>Total Capital Program budget: $750K (2024) + $3.25M (2025) + $2.6M (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="96" t="inlineStr">
+        <is>
+          <t>Spend to Date</t>
+        </is>
+      </c>
+      <c r="B57" s="207" t="inlineStr">
+        <is>
+          <t>$5,908,822</t>
+        </is>
+      </c>
+      <c r="C57" s="208" t="inlineStr">
+        <is>
+          <t>2024: $741,206  |  2025: $3,130,120  |  2026 to date: $2,037,496</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="93" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="B58" s="205" t="inlineStr">
+        <is>
+          <t>$1,228,577</t>
+        </is>
+      </c>
+      <c r="C58" s="206" t="inlineStr">
+        <is>
+          <t>Estimate to Complete — remaining 2026 spend needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="96" t="inlineStr">
+        <is>
+          <t>EAC</t>
+        </is>
+      </c>
+      <c r="B59" s="207" t="inlineStr">
+        <is>
+          <t>$7,137,399</t>
+        </is>
+      </c>
+      <c r="C59" s="208" t="inlineStr">
+        <is>
+          <t>Estimate at Completion = $537,399 OVER budget (-8.1% variance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="93" t="inlineStr">
+        <is>
+          <t>2026 Remaining Budget</t>
+        </is>
+      </c>
+      <c r="B60" s="205" t="inlineStr">
+        <is>
+          <t>$562,504</t>
+        </is>
+      </c>
+      <c r="C60" s="206" t="inlineStr">
+        <is>
+          <t>2026 CP budget $2.6M minus $2.037M spent = $562,504 remaining</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="96" t="inlineStr">
+        <is>
+          <t>2026 Projected Variance</t>
+        </is>
+      </c>
+      <c r="B61" s="207" t="inlineStr">
+        <is>
+          <t>-$666,073</t>
+        </is>
+      </c>
+      <c r="C61" s="208" t="inlineStr">
+        <is>
+          <t>2026 is tracking $666K over budget — REQUIRES PCR or budget reallocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="93" t="inlineStr">
+        <is>
+          <t>Lok Wong rate</t>
+        </is>
+      </c>
+      <c r="B62" s="205" t="inlineStr">
+        <is>
+          <t>$115.34/hr</t>
+        </is>
+      </c>
+      <c r="C62" s="206" t="inlineStr">
+        <is>
+          <t>Rate confirmed in workbook. Note: 'Add FRINGE' flag — fringe not yet included in base rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="96" t="inlineStr">
+        <is>
+          <t>Sameer Shakur rate</t>
+        </is>
+      </c>
+      <c r="B63" s="207" t="inlineStr">
+        <is>
+          <t>$66.50/hr</t>
+        </is>
+      </c>
+      <c r="C63" s="208" t="inlineStr">
+        <is>
+          <t>PAR design. 'Add FRINGE' flag — fringe not yet included</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="93" t="inlineStr">
+        <is>
+          <t>Steven Bradley rate</t>
+        </is>
+      </c>
+      <c r="B64" s="205" t="inlineStr">
+        <is>
+          <t>$93.50/hr</t>
+        </is>
+      </c>
+      <c r="C64" s="206" t="inlineStr">
+        <is>
+          <t>Relay installation lead. 2025 actuals Dec $29,358 each on 2 WBS = $58,716 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="96" t="inlineStr">
+        <is>
+          <t>Chak rate</t>
+        </is>
+      </c>
+      <c r="B65" s="207" t="inlineStr">
+        <is>
+          <t>$134.14/hr</t>
+        </is>
+      </c>
+      <c r="C65" s="208" t="inlineStr">
+        <is>
+          <t>Max PAR engineering: 1,200 hrs × $134.14 = $160,968 (NOT $240K as originally forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="93" t="inlineStr">
+        <is>
+          <t>Martin Gately</t>
+        </is>
+      </c>
+      <c r="B66" s="205" t="inlineStr">
+        <is>
+          <t>$116.84/hr</t>
+        </is>
+      </c>
+      <c r="C66" s="206" t="inlineStr">
+        <is>
+          <t>Acting PM prior to Jay. 2025 actuals: Dec $12,093 + Jan $13,270 + Feb $8,144 = $33,507 confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="96" t="inlineStr">
+        <is>
+          <t>Jay Gunaratne</t>
+        </is>
+      </c>
+      <c r="B67" s="207" t="inlineStr">
+        <is>
+          <t>$145/hr</t>
+        </is>
+      </c>
+      <c r="C67" s="208" t="inlineStr">
+        <is>
+          <t>PM rate per Hermitage PO 7000002000. Full-time through project completion</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="C63:K63"/>
+    <mergeCell ref="C65:K65"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="C56:K56"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="C67:K67"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="C57:K57"/>
+    <mergeCell ref="C66:K66"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="C62:K62"/>
+    <mergeCell ref="C58:K58"/>
+    <mergeCell ref="C64:K64"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="64">
+  <fonts count="65">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -345,6 +345,11 @@
       <color rgb="00333333"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -504,7 +509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1114,6 +1119,12 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2397,17 +2408,16 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="44" customHeight="1">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="55" t="inlineStr">
         <is>
           <t>PAR – Material</t>
         </is>
       </c>
-      <c r="B33" s="56" t="inlineStr">
-        <is>
-          <t>Iniven RC-30 Equipment  [PO CONFIRMED]
-EO#7000002695 – 6 sites
-Converts direct contact → C37.94</t>
+      <c r="B33" s="164" t="inlineStr">
+        <is>
+          <t>PAR – Materials
+Cables, connectors, misc per Vic May 18 call</t>
         </is>
       </c>
       <c r="C33" s="57" t="inlineStr">
@@ -2425,16 +2435,16 @@
           <t>2026 (ordered)</t>
         </is>
       </c>
-      <c r="F33" s="59" t="n">
-        <v>52500</v>
-      </c>
-      <c r="G33" s="60" t="n">
-        <v>52500</v>
-      </c>
-      <c r="H33" s="59" t="inlineStr"/>
-      <c r="I33" s="61" t="inlineStr">
-        <is>
-          <t>Approved $52,500. Iniven (I-N-I-V-E-N). 8-wk lead time. NOT a programmable device – no NERC CIP issue.</t>
+      <c r="F33" s="167" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G33" s="60" t="n"/>
+      <c r="H33" s="167" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I33" s="170" t="inlineStr">
+        <is>
+          <t>★ Vic confirmed $30K for cables and connectors across 6 PAR sites.</t>
         </is>
       </c>
     </row>
@@ -2444,11 +2454,11 @@
           <t>PAR – Engineering</t>
         </is>
       </c>
-      <c r="B34" s="63" t="inlineStr">
-        <is>
-          <t>Relay Engineering – Chakrapani (Chok) team
-Design, procurement, test  [FORECAST ONLY – actuals far lower]
-Valk + Samir</t>
+      <c r="B34" s="164" t="inlineStr">
+        <is>
+          <t>PAR – Engineering Design (Protection Engineering team)
+200 hrs/site × 6 sites × $200/hr = $240,000
+★ CONFIRMED by Vic, May 18 2026 call</t>
         </is>
       </c>
       <c r="C34" s="64" t="inlineStr">
@@ -2466,16 +2476,16 @@
           <t>2026 May–Sep</t>
         </is>
       </c>
-      <c r="F34" s="66" t="n">
+      <c r="F34" s="167" t="n">
         <v>240000</v>
       </c>
-      <c r="G34" s="67" t="n">
+      <c r="G34" s="67" t="n"/>
+      <c r="H34" s="167" t="n">
         <v>240000</v>
       </c>
-      <c r="H34" s="66" t="inlineStr"/>
-      <c r="I34" s="68" t="inlineStr">
-        <is>
-          <t>⚠ FORECAST ONLY: 1,200 hrs × $200 = $240K. ACTUAL TO DATE: ~$5K (Valk @$65 + Samir @$150/hr). Meeting with Chok + Locke + Samir this week – expect major downward revision.</t>
+      <c r="I34" s="170" t="inlineStr">
+        <is>
+          <t>★ CONFIRMED Vic May 18: 200 hrs × 6 sites × $200/hr = $240K. External relay/protection engineers (NOT internal PSEG rate of $134.14/hr). $200/hr is the relay protection team billing rate.</t>
         </is>
       </c>
     </row>
@@ -2485,10 +2495,11 @@
           <t>PAR – Install</t>
         </is>
       </c>
-      <c r="B35" s="56" t="inlineStr">
-        <is>
-          <t>Relay Support – Steven Bradley / Johnny team
-Installation &amp; final testing – 6 sites  [REVISED Mar 23 2026 email]</t>
+      <c r="B35" s="164" t="inlineStr">
+        <is>
+          <t>PAR – Installation, Configuration &amp; Cutover Labor
+~1,298 hrs × $200/hr = $259,500
+★ CONFIRMED by Vic, May 18 2026 call  (previously $195,600 — REVISED)</t>
         </is>
       </c>
       <c r="C35" s="57" t="inlineStr">
@@ -2506,16 +2517,16 @@
           <t>2026 Aug–Dec</t>
         </is>
       </c>
-      <c r="F35" s="59" t="n">
-        <v>195600</v>
-      </c>
-      <c r="G35" s="60" t="n">
-        <v>195600</v>
-      </c>
-      <c r="H35" s="59" t="inlineStr"/>
-      <c r="I35" s="61" t="inlineStr">
-        <is>
-          <t>REVISED: 144 hrs/site × 5 sites = 720 hrs + supervision = 1,056 hrs. ~$185/hr avg = $195,600. Down from $494K. Meeting to confirm resource names &amp; monthly breakdown.</t>
+      <c r="F35" s="167" t="n">
+        <v>259500</v>
+      </c>
+      <c r="G35" s="60" t="n"/>
+      <c r="H35" s="167" t="n">
+        <v>259500</v>
+      </c>
+      <c r="I35" s="170" t="inlineStr">
+        <is>
+          <t>★ CONFIRMED Vic May 18: relay team install ~1,298 hrs × $200/hr = $259,500. Previously $195,600 (too low). Call with Steven needed before Monday to confirm exact hours by month. External relay team @ $200/hr.</t>
         </is>
       </c>
     </row>
@@ -2525,14 +2536,18 @@
           <t xml:space="preserve">  SUBTOTAL — PAR TOTAL  (Chok $240K inflated — expect ~$50-80K actual after meeting)</t>
         </is>
       </c>
-      <c r="F36" s="70" t="n">
-        <v>488100</v>
-      </c>
-      <c r="G36" s="71" t="n">
-        <v>488100</v>
-      </c>
-      <c r="H36" s="71" t="inlineStr"/>
-      <c r="I36" s="72" t="inlineStr"/>
+      <c r="F36" s="209" t="n">
+        <v>529500</v>
+      </c>
+      <c r="G36" s="71" t="n"/>
+      <c r="H36" s="209" t="n">
+        <v>529500</v>
+      </c>
+      <c r="I36" s="210" t="inlineStr">
+        <is>
+          <t>★ CONFIRMED Vic May 18 2026: PAR TOTAL = $529,500 (Eng $240K + Install $259.5K + Materials $30K). PCR to be submitted Q2 2026. Engineering runs in PARALLEL with Phase 2 — no schedule impact. Steven Bradley call set before Monday to lock hours.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="73" t="inlineStr">
@@ -2904,14 +2919,14 @@
         <v>5307742</v>
       </c>
       <c r="G49" s="80" t="n">
-        <v>3806914</v>
+        <v>3900814</v>
       </c>
       <c r="H49" s="80" t="n">
         <v>1963785</v>
       </c>
       <c r="I49" s="81" t="inlineStr">
         <is>
-          <t>★ UPDATED: ALL As-Builts (98 sites, $116,816) → Phase 3 2027. ALL Decommissioning (67 sites, ~$74,571) → Phase 3 2027. Chok PAR $240K inflated — meeting pending. Nokia Ph3 $368,719 (Ethan May 12).</t>
+          <t>★ UPDATED May 18 2026 per Vic call: PAR confirmed $529,500 (eng $240K + install $259.5K + materials $30K). PCR request: PAR $530K + Ph3 accel $800K = ~$1.2-1.33M to be submitted. Phase 3 site surveys + MPLS design accelerated into Phase 2. Steven call before Monday to lock relay labor hours by month. Frame relay internal team: still no actuals — Chad needs names + hours.</t>
         </is>
       </c>
     </row>
@@ -7367,6 +7382,14 @@
           <t>Total Capital Program budget: $750K (2024) + $3.25M (2025) + $2.6M (2026)</t>
         </is>
       </c>
+      <c r="D56" s="171" t="n"/>
+      <c r="E56" s="171" t="n"/>
+      <c r="F56" s="171" t="n"/>
+      <c r="G56" s="171" t="n"/>
+      <c r="H56" s="171" t="n"/>
+      <c r="I56" s="171" t="n"/>
+      <c r="J56" s="171" t="n"/>
+      <c r="K56" s="172" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="96" t="inlineStr">
@@ -7384,6 +7407,14 @@
           <t>2024: $741,206  |  2025: $3,130,120  |  2026 to date: $2,037,496</t>
         </is>
       </c>
+      <c r="D57" s="171" t="n"/>
+      <c r="E57" s="171" t="n"/>
+      <c r="F57" s="171" t="n"/>
+      <c r="G57" s="171" t="n"/>
+      <c r="H57" s="171" t="n"/>
+      <c r="I57" s="171" t="n"/>
+      <c r="J57" s="171" t="n"/>
+      <c r="K57" s="172" t="n"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="93" t="inlineStr">
@@ -7401,6 +7432,14 @@
           <t>Estimate to Complete — remaining 2026 spend needed</t>
         </is>
       </c>
+      <c r="D58" s="171" t="n"/>
+      <c r="E58" s="171" t="n"/>
+      <c r="F58" s="171" t="n"/>
+      <c r="G58" s="171" t="n"/>
+      <c r="H58" s="171" t="n"/>
+      <c r="I58" s="171" t="n"/>
+      <c r="J58" s="171" t="n"/>
+      <c r="K58" s="172" t="n"/>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="96" t="inlineStr">
@@ -7418,6 +7457,14 @@
           <t>Estimate at Completion = $537,399 OVER budget (-8.1% variance)</t>
         </is>
       </c>
+      <c r="D59" s="171" t="n"/>
+      <c r="E59" s="171" t="n"/>
+      <c r="F59" s="171" t="n"/>
+      <c r="G59" s="171" t="n"/>
+      <c r="H59" s="171" t="n"/>
+      <c r="I59" s="171" t="n"/>
+      <c r="J59" s="171" t="n"/>
+      <c r="K59" s="172" t="n"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="93" t="inlineStr">
@@ -7435,6 +7482,14 @@
           <t>2026 CP budget $2.6M minus $2.037M spent = $562,504 remaining</t>
         </is>
       </c>
+      <c r="D60" s="171" t="n"/>
+      <c r="E60" s="171" t="n"/>
+      <c r="F60" s="171" t="n"/>
+      <c r="G60" s="171" t="n"/>
+      <c r="H60" s="171" t="n"/>
+      <c r="I60" s="171" t="n"/>
+      <c r="J60" s="171" t="n"/>
+      <c r="K60" s="172" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="96" t="inlineStr">
@@ -7452,6 +7507,14 @@
           <t>2026 is tracking $666K over budget — REQUIRES PCR or budget reallocation</t>
         </is>
       </c>
+      <c r="D61" s="171" t="n"/>
+      <c r="E61" s="171" t="n"/>
+      <c r="F61" s="171" t="n"/>
+      <c r="G61" s="171" t="n"/>
+      <c r="H61" s="171" t="n"/>
+      <c r="I61" s="171" t="n"/>
+      <c r="J61" s="171" t="n"/>
+      <c r="K61" s="172" t="n"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="93" t="inlineStr">
@@ -7469,6 +7532,14 @@
           <t>Rate confirmed in workbook. Note: 'Add FRINGE' flag — fringe not yet included in base rate</t>
         </is>
       </c>
+      <c r="D62" s="171" t="n"/>
+      <c r="E62" s="171" t="n"/>
+      <c r="F62" s="171" t="n"/>
+      <c r="G62" s="171" t="n"/>
+      <c r="H62" s="171" t="n"/>
+      <c r="I62" s="171" t="n"/>
+      <c r="J62" s="171" t="n"/>
+      <c r="K62" s="172" t="n"/>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="96" t="inlineStr">
@@ -7486,6 +7557,14 @@
           <t>PAR design. 'Add FRINGE' flag — fringe not yet included</t>
         </is>
       </c>
+      <c r="D63" s="171" t="n"/>
+      <c r="E63" s="171" t="n"/>
+      <c r="F63" s="171" t="n"/>
+      <c r="G63" s="171" t="n"/>
+      <c r="H63" s="171" t="n"/>
+      <c r="I63" s="171" t="n"/>
+      <c r="J63" s="171" t="n"/>
+      <c r="K63" s="172" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="93" t="inlineStr">
@@ -7503,6 +7582,14 @@
           <t>Relay installation lead. 2025 actuals Dec $29,358 each on 2 WBS = $58,716 total</t>
         </is>
       </c>
+      <c r="D64" s="171" t="n"/>
+      <c r="E64" s="171" t="n"/>
+      <c r="F64" s="171" t="n"/>
+      <c r="G64" s="171" t="n"/>
+      <c r="H64" s="171" t="n"/>
+      <c r="I64" s="171" t="n"/>
+      <c r="J64" s="171" t="n"/>
+      <c r="K64" s="172" t="n"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="96" t="inlineStr">
@@ -7520,6 +7607,14 @@
           <t>Max PAR engineering: 1,200 hrs × $134.14 = $160,968 (NOT $240K as originally forecast)</t>
         </is>
       </c>
+      <c r="D65" s="171" t="n"/>
+      <c r="E65" s="171" t="n"/>
+      <c r="F65" s="171" t="n"/>
+      <c r="G65" s="171" t="n"/>
+      <c r="H65" s="171" t="n"/>
+      <c r="I65" s="171" t="n"/>
+      <c r="J65" s="171" t="n"/>
+      <c r="K65" s="172" t="n"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="93" t="inlineStr">
@@ -7537,6 +7632,14 @@
           <t>Acting PM prior to Jay. 2025 actuals: Dec $12,093 + Jan $13,270 + Feb $8,144 = $33,507 confirmed</t>
         </is>
       </c>
+      <c r="D66" s="171" t="n"/>
+      <c r="E66" s="171" t="n"/>
+      <c r="F66" s="171" t="n"/>
+      <c r="G66" s="171" t="n"/>
+      <c r="H66" s="171" t="n"/>
+      <c r="I66" s="171" t="n"/>
+      <c r="J66" s="171" t="n"/>
+      <c r="K66" s="172" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="96" t="inlineStr">
@@ -7554,6 +7657,14 @@
           <t>PM rate per Hermitage PO 7000002000. Full-time through project completion</t>
         </is>
       </c>
+      <c r="D67" s="171" t="n"/>
+      <c r="E67" s="171" t="n"/>
+      <c r="F67" s="171" t="n"/>
+      <c r="G67" s="171" t="n"/>
+      <c r="H67" s="171" t="n"/>
+      <c r="I67" s="171" t="n"/>
+      <c r="J67" s="171" t="n"/>
+      <c r="K67" s="172" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="72">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,6 +350,42 @@
       <color rgb="00FFD700"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -509,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1126,6 +1162,27 @@
     </xf>
     <xf numFmtId="0" fontId="64" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="68" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="69" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5593,20 +5650,20 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="180" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>MARTIN GATELY</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
+      <c r="B13" s="211" t="inlineStr">
+        <is>
+          <t>MARTIN GATELY  ⚠ NO LONGER WITH PSEG — REMOVE FROM FORECAST</t>
+        </is>
+      </c>
+      <c r="C13" s="212" t="inlineStr">
+        <is>
+          <t>Project Manager (DEPARTED)</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
@@ -5622,21 +5679,23 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
-        <is>
-          <t>Capital</t>
+      <c r="G13" s="213" t="inlineStr">
+        <is>
+          <t>DEPARTED</t>
         </is>
       </c>
       <c r="H13" s="36" t="n">
         <v>133886</v>
       </c>
-      <c r="I13" s="35" t="inlineStr"/>
-      <c r="J13" s="36" t="n">
-        <v>133886</v>
-      </c>
-      <c r="K13" s="37" t="inlineStr">
-        <is>
-          <t>Actuals: Dec $12,093, Jan $13,270, Feb $8,144 + prior months. PM role.</t>
+      <c r="I13" s="214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="216" t="inlineStr">
+        <is>
+          <t>⚠ DEPARTED — Martin Gately no longer with PSEG as of May 2026. 2025 actuals ($133,886) already charged to SAP — sunk cost. 2026 forecast = $0. Remove from all future projections.</t>
         </is>
       </c>
     </row>
@@ -7616,15 +7675,15 @@
       <c r="J65" s="171" t="n"/>
       <c r="K65" s="172" t="n"/>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="93" t="inlineStr">
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="211" t="inlineStr">
         <is>
           <t>Martin Gately</t>
         </is>
       </c>
-      <c r="B66" s="205" t="inlineStr">
-        <is>
-          <t>$116.84/hr</t>
+      <c r="B66" s="217" t="inlineStr">
+        <is>
+          <t>⚠ DEPARTED — No longer with PSEG. 2025 actuals Dec $12,093 + Jan $13,270 + Feb $8,144 = $33,507 already in SAP (sunk cost). 2026 forecast = $0.</t>
         </is>
       </c>
       <c r="C66" s="206" t="inlineStr">

--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -11,6 +11,7 @@
     <sheet name="B&amp;M Site Breakdown" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Nokia Ph3 Equipment" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Internal Labor" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Phase 2 Monthly Forecast" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="81">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -386,8 +387,52 @@
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E5631"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E5631"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -474,8 +519,23 @@
         <fgColor rgb="001F5C7A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004B0082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -541,11 +601,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="218">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1183,6 +1257,264 @@
     </xf>
     <xf numFmtId="0" fontId="71" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="73" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7750,4 +8082,2660 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PRJ13797 — JMUX REPLACEMENT  |  PHASE 2 MONTHLY PLAN &amp; FORECAST  |  May–Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="218" t="inlineStr">
+        <is>
+          <t>Construction Start: Aug 5 2026  |  Deployment Complete: Sep 28 2026  |  Final IFR: Jun 29 2026  |  Final IFC: Jul 13 2026  |  36 Sites  |  As of May 18 2026  |  Source: Chad's workbook + B&amp;M SOW + Vic call</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION 1 — PHASE 2 MILESTONE SCHEDULE BY MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="219" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="219" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="C4" s="219" t="inlineStr">
+        <is>
+          <t>Milestone / Deliverable</t>
+        </is>
+      </c>
+      <c r="D4" s="219" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E4" s="219" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F4" s="219" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G4" s="219" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H4" s="219" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I4" s="219" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J4" s="219" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K4" s="219" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L4" s="219" t="inlineStr">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+      <c r="M4" s="219" t="inlineStr">
+        <is>
+          <t>Notes / Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="220" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B5" s="221" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C5" s="222" t="inlineStr">
+        <is>
+          <t>Complete remaining Phase 2 IFRs
+(15 of 36 still outstanding)</t>
+        </is>
+      </c>
+      <c r="D5" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="E5" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F5" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="G5" s="225" t="inlineStr"/>
+      <c r="H5" s="225" t="inlineStr"/>
+      <c r="I5" s="225" t="inlineStr"/>
+      <c r="J5" s="225" t="inlineStr"/>
+      <c r="K5" s="225" t="inlineStr"/>
+      <c r="L5" s="226" t="inlineStr">
+        <is>
+          <t>Jun 29 2026</t>
+        </is>
+      </c>
+      <c r="M5" s="227" t="inlineStr">
+        <is>
+          <t>~20 IFRs still to submit. Baldwin (4M/4M1) OVERDUE. Lindenhurst OVERDUE. B&amp;M (Ethan Koch) responsible. $601,020 fixed fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="220" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B6" s="221" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C6" s="222" t="inlineStr">
+        <is>
+          <t>Complete all Phase 2 IFCs (PE-sealed)
+(23 of 36 still outstanding)</t>
+        </is>
+      </c>
+      <c r="D6" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="E6" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F6" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="G6" s="225" t="inlineStr"/>
+      <c r="H6" s="225" t="inlineStr"/>
+      <c r="I6" s="225" t="inlineStr"/>
+      <c r="J6" s="225" t="inlineStr"/>
+      <c r="K6" s="225" t="inlineStr"/>
+      <c r="L6" s="226" t="inlineStr">
+        <is>
+          <t>Jul 13 2026</t>
+        </is>
+      </c>
+      <c r="M6" s="227" t="inlineStr">
+        <is>
+          <t>IFC follows IFR by ~2 weeks per site. All 36 must be sealed by Jul 13 to enable Aug 5 construction start. $214,668 fixed fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="220" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B7" s="221" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C7" s="222" t="inlineStr">
+        <is>
+          <t>B&amp;M Phase 2 Site Surveys complete
+(Hawkeye pre-construction survey)</t>
+        </is>
+      </c>
+      <c r="D7" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="E7" s="228" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F7" s="225" t="inlineStr"/>
+      <c r="G7" s="225" t="inlineStr"/>
+      <c r="H7" s="225" t="inlineStr"/>
+      <c r="I7" s="225" t="inlineStr"/>
+      <c r="J7" s="225" t="inlineStr"/>
+      <c r="K7" s="225" t="inlineStr"/>
+      <c r="L7" s="226" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="M7" s="227" t="inlineStr">
+        <is>
+          <t>Vinny (Hawkeye) started May 18. Surveys run parallel with IFCs. Cable lengths, power, rack space per IFC. Hawkeye SOW M1 = $100,170.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="220" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B8" s="221" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C8" s="222" t="inlineStr">
+        <is>
+          <t>Phase 3 MPLS Design (accelerated into Ph2)
+B&amp;M — 31 Phase 3 sites</t>
+        </is>
+      </c>
+      <c r="D8" s="225" t="inlineStr"/>
+      <c r="E8" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F8" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="G8" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H8" s="225" t="inlineStr"/>
+      <c r="I8" s="225" t="inlineStr"/>
+      <c r="J8" s="225" t="inlineStr"/>
+      <c r="K8" s="225" t="inlineStr"/>
+      <c r="L8" s="226" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="M8" s="227" t="inlineStr">
+        <is>
+          <t>Pulled from Phase 3 into Phase 2 as part of PCR recovery. Recovers 5-month schedule impact. Part of $800K PCR request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="220" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B9" s="221" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="C9" s="222" t="inlineStr">
+        <is>
+          <t>Phase 3 Site Surveys (accelerated into Ph2)
+Hawkeye — 31 sites</t>
+        </is>
+      </c>
+      <c r="D9" s="225" t="inlineStr"/>
+      <c r="E9" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F9" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="G9" s="225" t="inlineStr"/>
+      <c r="H9" s="225" t="inlineStr"/>
+      <c r="I9" s="225" t="inlineStr"/>
+      <c r="J9" s="225" t="inlineStr"/>
+      <c r="K9" s="225" t="inlineStr"/>
+      <c r="L9" s="226" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="M9" s="227" t="inlineStr">
+        <is>
+          <t>31 Phase 3 sites surveyed now instead of 2027. Part of $800K PCR request. Rate TBD with Hawkeye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="229" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B10" s="230" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C10" s="231" t="inlineStr">
+        <is>
+          <t>Confirm Phase 2 equipment BOM
+(CWDM cards, Eltek PSUs — Presidio)</t>
+        </is>
+      </c>
+      <c r="D10" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="E10" s="224" t="inlineStr"/>
+      <c r="F10" s="224" t="inlineStr"/>
+      <c r="G10" s="224" t="inlineStr"/>
+      <c r="H10" s="224" t="inlineStr"/>
+      <c r="I10" s="224" t="inlineStr"/>
+      <c r="J10" s="224" t="inlineStr"/>
+      <c r="K10" s="224" t="inlineStr"/>
+      <c r="L10" s="232" t="inlineStr">
+        <is>
+          <t>May/Jun 2026</t>
+        </is>
+      </c>
+      <c r="M10" s="233" t="inlineStr">
+        <is>
+          <t>Nokia Phase 2 equipment delivered ($733,293). Remaining: ~8-10 CWDM cards ($15K) + Eltek PSUs ($10K). Confirm count with Ethan once IFCs reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="229" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B11" s="230" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C11" s="231" t="inlineStr">
+        <is>
+          <t>Iniven RC-30 delivery — PAR (6 sites)
+(8-week lead time from PO date)</t>
+        </is>
+      </c>
+      <c r="D11" s="224" t="inlineStr"/>
+      <c r="E11" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="F11" s="224" t="inlineStr"/>
+      <c r="G11" s="224" t="inlineStr"/>
+      <c r="H11" s="224" t="inlineStr"/>
+      <c r="I11" s="224" t="inlineStr"/>
+      <c r="J11" s="224" t="inlineStr"/>
+      <c r="K11" s="224" t="inlineStr"/>
+      <c r="L11" s="232" t="inlineStr">
+        <is>
+          <t>~Jun 2026</t>
+        </is>
+      </c>
+      <c r="M11" s="233" t="inlineStr">
+        <is>
+          <t>PO placed. 8-week lead time. Delivery ~Jun 2026. Drives Steven Bradley/relay team installation schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="229" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B12" s="230" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C12" s="231" t="inlineStr">
+        <is>
+          <t>Order RJ45→DB25 patch panel cables
+(7 production + 1 spare = 8 units)</t>
+        </is>
+      </c>
+      <c r="D12" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="E12" s="224" t="inlineStr"/>
+      <c r="F12" s="224" t="inlineStr"/>
+      <c r="G12" s="224" t="inlineStr"/>
+      <c r="H12" s="224" t="inlineStr"/>
+      <c r="I12" s="224" t="inlineStr"/>
+      <c r="J12" s="224" t="inlineStr"/>
+      <c r="K12" s="224" t="inlineStr"/>
+      <c r="L12" s="232" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="M12" s="233" t="inlineStr">
+        <is>
+          <t>Can only order AFTER Hicksville serial test confirms pinout. Cables Unlimited supplier. Transmit/receive crossover confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="234" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="B13" s="235" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C13" s="236" t="inlineStr">
+        <is>
+          <t>Hawkeye Staging &amp; Assembly
+36 Phase 2 Nokia nodes — lab burn-in &amp; test</t>
+        </is>
+      </c>
+      <c r="D13" s="228" t="inlineStr"/>
+      <c r="E13" s="228" t="inlineStr"/>
+      <c r="F13" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="G13" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H13" s="228" t="inlineStr"/>
+      <c r="I13" s="228" t="inlineStr"/>
+      <c r="J13" s="228" t="inlineStr"/>
+      <c r="K13" s="228" t="inlineStr"/>
+      <c r="L13" s="237" t="inlineStr">
+        <is>
+          <t>Jun–Aug 2026</t>
+        </is>
+      </c>
+      <c r="M13" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M-Ph0 = $100,170. B&amp;M provides card slotting + connectivity reqs. All 36 nodes assembled and tested before shipping to substations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="234" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B14" s="235" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C14" s="236" t="inlineStr">
+        <is>
+          <t>Hawkeye Installation — All 36 Phase 2 Sites
+Nokia SAR-8, CWDM, Eltek, RS-232 panel, fiber</t>
+        </is>
+      </c>
+      <c r="D14" s="228" t="inlineStr"/>
+      <c r="E14" s="228" t="inlineStr"/>
+      <c r="F14" s="228" t="inlineStr"/>
+      <c r="G14" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H14" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="I14" s="228" t="inlineStr"/>
+      <c r="J14" s="228" t="inlineStr"/>
+      <c r="K14" s="228" t="inlineStr"/>
+      <c r="L14" s="237" t="inlineStr">
+        <is>
+          <t>Aug 5 – Sep 28 2026</t>
+        </is>
+      </c>
+      <c r="M14" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M2 = $80,136. 3 mobilisations per site. Construction START Aug 5 2026. TARGET COMPLETE Sep 28 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="239" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+      <c r="B15" s="240" t="inlineStr">
+        <is>
+          <t>NMS / NSP</t>
+        </is>
+      </c>
+      <c r="C15" s="241" t="inlineStr">
+        <is>
+          <t>Remote Node Verification — all 31 Ph1 sites
+(NSP GUI login, configs, connectivity)</t>
+        </is>
+      </c>
+      <c r="D15" s="242" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="E15" s="242" t="inlineStr"/>
+      <c r="F15" s="242" t="inlineStr"/>
+      <c r="G15" s="242" t="inlineStr"/>
+      <c r="H15" s="242" t="inlineStr"/>
+      <c r="I15" s="242" t="inlineStr"/>
+      <c r="J15" s="242" t="inlineStr"/>
+      <c r="K15" s="242" t="inlineStr"/>
+      <c r="L15" s="243" t="inlineStr">
+        <is>
+          <t>OVERDUE — was May 9</t>
+        </is>
+      </c>
+      <c r="M15" s="244" t="inlineStr">
+        <is>
+          <t>OVERDUE. Must complete before production cutover scheduling. Lee/Rahiq/Brianna to action immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="220" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="B16" s="221" t="inlineStr">
+        <is>
+          <t>NMS / NSP</t>
+        </is>
+      </c>
+      <c r="C16" s="222" t="inlineStr">
+        <is>
+          <t>Build Phase 2 Nodes into NSP GUI
+(36 Phase 2 Nokia nodes configured)</t>
+        </is>
+      </c>
+      <c r="D16" s="225" t="inlineStr"/>
+      <c r="E16" s="225" t="inlineStr"/>
+      <c r="F16" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="G16" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H16" s="225" t="inlineStr"/>
+      <c r="I16" s="225" t="inlineStr"/>
+      <c r="J16" s="225" t="inlineStr"/>
+      <c r="K16" s="225" t="inlineStr"/>
+      <c r="L16" s="226" t="inlineStr">
+        <is>
+          <t>Jul–Aug 2026</t>
+        </is>
+      </c>
+      <c r="M16" s="227" t="inlineStr">
+        <is>
+          <t>Same process as Phase 1 (31 nodes completed Apr 23). Can start as soon as IFCs finalized — no need to wait for physical installation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="239" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B17" s="240" t="inlineStr">
+        <is>
+          <t>RTU Migration</t>
+        </is>
+      </c>
+      <c r="C17" s="241" t="inlineStr">
+        <is>
+          <t>Complete Hicksville RTU serial test
+(RJ45→DB25 beta cable installed)</t>
+        </is>
+      </c>
+      <c r="D17" s="242" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="E17" s="242" t="inlineStr"/>
+      <c r="F17" s="242" t="inlineStr"/>
+      <c r="G17" s="242" t="inlineStr"/>
+      <c r="H17" s="242" t="inlineStr"/>
+      <c r="I17" s="242" t="inlineStr"/>
+      <c r="J17" s="242" t="inlineStr"/>
+      <c r="K17" s="242" t="inlineStr"/>
+      <c r="L17" s="243" t="inlineStr">
+        <is>
+          <t>OVERDUE — week of May 18</t>
+        </is>
+      </c>
+      <c r="M17" s="244" t="inlineStr">
+        <is>
+          <t>Beta cable delivered by Cables Unlimited. QAS 6U RTU ready (George). Test MUST complete this week. Blocks all Phase 1 production cutovers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="239" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B18" s="240" t="inlineStr">
+        <is>
+          <t>RTU Migration</t>
+        </is>
+      </c>
+      <c r="C18" s="241" t="inlineStr">
+        <is>
+          <t>Develop MOP — Production RTU Migration
+(5K SIOS pilot cutover procedure)</t>
+        </is>
+      </c>
+      <c r="D18" s="242" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="E18" s="242" t="inlineStr"/>
+      <c r="F18" s="242" t="inlineStr"/>
+      <c r="G18" s="242" t="inlineStr"/>
+      <c r="H18" s="242" t="inlineStr"/>
+      <c r="I18" s="242" t="inlineStr"/>
+      <c r="J18" s="242" t="inlineStr"/>
+      <c r="K18" s="242" t="inlineStr"/>
+      <c r="L18" s="243" t="inlineStr">
+        <is>
+          <t>OVERDUE — was May 16</t>
+        </is>
+      </c>
+      <c r="M18" s="244" t="inlineStr">
+        <is>
+          <t>Ethan Koch (B&amp;M) to draft. Covers: substation, Hicksville control room, ACC. Change mgmt ticket required. Follow up immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="229" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B19" s="230" t="inlineStr">
+        <is>
+          <t>RTU Migration</t>
+        </is>
+      </c>
+      <c r="C19" s="231" t="inlineStr">
+        <is>
+          <t>Phase 1 Production RTU Cutovers
+(All Phase 1 JMUX-supported circuits → Nokia)</t>
+        </is>
+      </c>
+      <c r="D19" s="224" t="inlineStr"/>
+      <c r="E19" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F19" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="G19" s="224" t="inlineStr"/>
+      <c r="H19" s="224" t="inlineStr"/>
+      <c r="I19" s="224" t="inlineStr"/>
+      <c r="J19" s="224" t="inlineStr"/>
+      <c r="K19" s="224" t="inlineStr"/>
+      <c r="L19" s="232" t="inlineStr">
+        <is>
+          <t>Jun 23 2026</t>
+        </is>
+      </c>
+      <c r="M19" s="233" t="inlineStr">
+        <is>
+          <t>Cannot start until: serial test ✅, MOP approved ✅, node verification ✅. Exception: 5DA Duffy Ave + 5R Bellmore (4W→RS-232 conversion first).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="229" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B20" s="230" t="inlineStr">
+        <is>
+          <t>RTU Migration</t>
+        </is>
+      </c>
+      <c r="C20" s="231" t="inlineStr">
+        <is>
+          <t>Phase 2 RTU Circuit Cutovers
+(All Phase 2 JMUX circuits → Nokia MPLS)</t>
+        </is>
+      </c>
+      <c r="D20" s="224" t="inlineStr"/>
+      <c r="E20" s="224" t="inlineStr"/>
+      <c r="F20" s="224" t="inlineStr"/>
+      <c r="G20" s="224" t="inlineStr"/>
+      <c r="H20" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="I20" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="J20" s="224" t="inlineStr"/>
+      <c r="K20" s="224" t="inlineStr"/>
+      <c r="L20" s="232" t="inlineStr">
+        <is>
+          <t>Aug–Oct 2026</t>
+        </is>
+      </c>
+      <c r="M20" s="233" t="inlineStr">
+        <is>
+          <t>After Hawkeye installs each site, relay team migrates circuits. Runs parallel to Phase 2 construction. Cannot retire JMUX until ALL phases done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="239" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B21" s="240" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="C21" s="241" t="inlineStr">
+        <is>
+          <t>PAR Engineering Design — Chok team
+6 sites: Northport, 5HK, Melville, 7Z, 2H, 2R</t>
+        </is>
+      </c>
+      <c r="D21" s="242" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="E21" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F21" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="G21" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H21" s="242" t="inlineStr"/>
+      <c r="I21" s="242" t="inlineStr"/>
+      <c r="J21" s="242" t="inlineStr"/>
+      <c r="K21" s="242" t="inlineStr"/>
+      <c r="L21" s="243" t="inlineStr">
+        <is>
+          <t>Jun–Aug 2026</t>
+        </is>
+      </c>
+      <c r="M21" s="244" t="inlineStr">
+        <is>
+          <t>⚠ URGENT: Chok has not confirmed design status. Meeting this week. $240K confirmed (200hrs×6×$200/hr). Runs PARALLEL with Ph2 — no schedule impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="229" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B22" s="230" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="C22" s="231" t="inlineStr">
+        <is>
+          <t>PAR Installation — Relay team (Steven/Johnny)
+6 sites — install + test Iniven RC-30</t>
+        </is>
+      </c>
+      <c r="D22" s="224" t="inlineStr"/>
+      <c r="E22" s="224" t="inlineStr"/>
+      <c r="F22" s="224" t="inlineStr"/>
+      <c r="G22" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H22" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="I22" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="J22" s="224" t="inlineStr"/>
+      <c r="K22" s="224" t="inlineStr"/>
+      <c r="L22" s="232" t="inlineStr">
+        <is>
+          <t>Aug–Oct 2026</t>
+        </is>
+      </c>
+      <c r="M22" s="233" t="inlineStr">
+        <is>
+          <t>Cannot start until: Chok design done ✅ + RC-30 delivered ✅ (~Jun). $259,500 (1,298hrs×$200/hr) + $30K materials. Call Steven before Monday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="220" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B23" s="221" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C23" s="222" t="inlineStr">
+        <is>
+          <t>Two-Way Radio Pilot (Phase 1)
+Hicksville HE + Melville HE + Syosset pilot</t>
+        </is>
+      </c>
+      <c r="D23" s="225" t="inlineStr"/>
+      <c r="E23" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F23" s="225" t="inlineStr"/>
+      <c r="G23" s="225" t="inlineStr"/>
+      <c r="H23" s="225" t="inlineStr"/>
+      <c r="I23" s="225" t="inlineStr"/>
+      <c r="J23" s="225" t="inlineStr"/>
+      <c r="K23" s="225" t="inlineStr"/>
+      <c r="L23" s="226" t="inlineStr">
+        <is>
+          <t>Jun 23 2026</t>
+        </is>
+      </c>
+      <c r="M23" s="227" t="inlineStr">
+        <is>
+          <t>Phase 1 pilot only. Remaining sites Phase 2/3. Headend configuration at Hicksville + Melville required first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="220" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B24" s="221" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C24" s="222" t="inlineStr">
+        <is>
+          <t>FEMA-DA Pilot (Phase 1)
+Hicksville HE + Melville HE + Syosset pilot</t>
+        </is>
+      </c>
+      <c r="D24" s="225" t="inlineStr"/>
+      <c r="E24" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F24" s="225" t="inlineStr"/>
+      <c r="G24" s="225" t="inlineStr"/>
+      <c r="H24" s="225" t="inlineStr"/>
+      <c r="I24" s="225" t="inlineStr"/>
+      <c r="J24" s="225" t="inlineStr"/>
+      <c r="K24" s="225" t="inlineStr"/>
+      <c r="L24" s="226" t="inlineStr">
+        <is>
+          <t>Jun 23 2026</t>
+        </is>
+      </c>
+      <c r="M24" s="227" t="inlineStr">
+        <is>
+          <t>1 pilot site in Phase 1. Rest Phase 2/3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="220" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B25" s="221" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C25" s="222" t="inlineStr">
+        <is>
+          <t>Substation Security Pilot (Phase 1)
+Hicksville HE + Melville HE + Ruland Road</t>
+        </is>
+      </c>
+      <c r="D25" s="225" t="inlineStr"/>
+      <c r="E25" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="F25" s="225" t="inlineStr"/>
+      <c r="G25" s="225" t="inlineStr"/>
+      <c r="H25" s="225" t="inlineStr"/>
+      <c r="I25" s="225" t="inlineStr"/>
+      <c r="J25" s="225" t="inlineStr"/>
+      <c r="K25" s="225" t="inlineStr"/>
+      <c r="L25" s="226" t="inlineStr">
+        <is>
+          <t>Jun 23 2026</t>
+        </is>
+      </c>
+      <c r="M25" s="227" t="inlineStr">
+        <is>
+          <t>1 pilot site (Ruland Road) in Phase 1. Rest Phase 2/3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="220" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B26" s="221" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+      <c r="C26" s="222" t="inlineStr">
+        <is>
+          <t>Phase 2 Network Pilots — scale out
+(Two-Way Radio, FEMA-DA, Sub Security)</t>
+        </is>
+      </c>
+      <c r="D26" s="225" t="inlineStr"/>
+      <c r="E26" s="225" t="inlineStr"/>
+      <c r="F26" s="225" t="inlineStr"/>
+      <c r="G26" s="225" t="inlineStr"/>
+      <c r="H26" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="I26" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="J26" s="225" t="inlineStr"/>
+      <c r="K26" s="225" t="inlineStr"/>
+      <c r="L26" s="226" t="inlineStr">
+        <is>
+          <t>Sep–Oct 2026</t>
+        </is>
+      </c>
+      <c r="M26" s="227" t="inlineStr">
+        <is>
+          <t>After Phase 1 pilots confirm template. Phase 2 rolls out at scale across 36 sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="234" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B27" s="235" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="C27" s="236" t="inlineStr">
+        <is>
+          <t>Phase 2 Go-Live Sign-Off (Hawkeye M4)
+36 sites installed + relay migration complete</t>
+        </is>
+      </c>
+      <c r="D27" s="228" t="inlineStr"/>
+      <c r="E27" s="228" t="inlineStr"/>
+      <c r="F27" s="228" t="inlineStr"/>
+      <c r="G27" s="228" t="inlineStr"/>
+      <c r="H27" s="228" t="inlineStr"/>
+      <c r="I27" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="J27" s="224" t="inlineStr">
+        <is>
+          <t>📅</t>
+        </is>
+      </c>
+      <c r="K27" s="228" t="inlineStr"/>
+      <c r="L27" s="237" t="inlineStr">
+        <is>
+          <t>Sep–Oct 2026</t>
+        </is>
+      </c>
+      <c r="M27" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M4 = $80,136. Formal sign-off by Vic/PSEG. After sign-off: Hawkeye invoices M4, B&amp;M invoices final construction support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="234" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B28" s="235" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="C28" s="236" t="inlineStr">
+        <is>
+          <t>Nokia runs in PARALLEL with JMUX
+★ ALL circuits verified before any decommission</t>
+        </is>
+      </c>
+      <c r="D28" s="228" t="inlineStr"/>
+      <c r="E28" s="228" t="inlineStr"/>
+      <c r="F28" s="228" t="inlineStr"/>
+      <c r="G28" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="H28" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="I28" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="J28" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="K28" s="223" t="inlineStr">
+        <is>
+          <t>🔄</t>
+        </is>
+      </c>
+      <c r="L28" s="237" t="inlineStr">
+        <is>
+          <t>Aug–Dec 2026</t>
+        </is>
+      </c>
+      <c r="M28" s="238" t="inlineStr">
+        <is>
+          <t>KEY PRINCIPLE: Nokia and JMUX run simultaneously. All circuits confirmed working on Nokia before JMUX is powered down. Decommission = Phase 3 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  LEGEND:  ✅ Complete  |  🔄 In Progress / Active this month  |  📅 Due / Deliverable  |  🔴 OVERDUE / At Risk  |  ⬜ Not yet started</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION 2 — MONTHLY COST FORECAST  |  Phase 2 Remaining 2026  |  Source: Chad's Workbook + SOW Milestones</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="246" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B32" s="246" t="inlineStr">
+        <is>
+          <t>Vendor / Category</t>
+        </is>
+      </c>
+      <c r="C32" s="246" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="D32" s="246" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="E32" s="246" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="F32" s="246" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="G32" s="246" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="H32" s="246" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="I32" s="246" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="J32" s="246" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="K32" s="246" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="L32" s="246" t="inlineStr">
+        <is>
+          <t>2026 TOTAL</t>
+        </is>
+      </c>
+      <c r="M32" s="246" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ★ ACTUALS JAN–APR 2026 (already spent):  Jan $575,203  |  Feb $275,852  |  Mar $919,089  |  Apr $295,000  |  TOTAL SPENT JAN–APR: $2,065,144  (Source: Chad workbook Monthly Summary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B34" s="249" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C34" s="222" t="inlineStr">
+        <is>
+          <t>IFR Submissions — remaining sites
+(~20 sites × $16,695/site rolling)</t>
+        </is>
+      </c>
+      <c r="D34" s="250" t="n">
+        <v>148938</v>
+      </c>
+      <c r="E34" s="250" t="n">
+        <v>89445</v>
+      </c>
+      <c r="F34" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="250" t="n">
+        <v>42912</v>
+      </c>
+      <c r="K34" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="252" t="n">
+        <v>281295</v>
+      </c>
+      <c r="M34" s="227" t="inlineStr">
+        <is>
+          <t>From Chad workbook actuals column — B&amp;M SOW M4 rolling IFR payments. May = $148,938 (actuals). Jun = $89,445. Nov = $42,912 (As-Builts deferred Ph3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B35" s="249" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C35" s="222" t="inlineStr">
+        <is>
+          <t>IFC Submissions — remaining sites
+(included in M4 SOW milestone per site)</t>
+        </is>
+      </c>
+      <c r="D35" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="250" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F35" s="250" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G35" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="252" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M35" s="227" t="inlineStr">
+        <is>
+          <t>IFC payments ~$5,963/site. Rolling Jun–Jul. Included in $214,668 M4 total. Final IFC deadline Jul 13 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="248" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="249" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C36" s="222" t="inlineStr">
+        <is>
+          <t>Phase 2 Construction Support Coordinator
+Ethan Koch — on-site Aug–Dec</t>
+        </is>
+      </c>
+      <c r="D36" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="250" t="n">
+        <v>61350</v>
+      </c>
+      <c r="H36" s="250" t="n">
+        <v>61350</v>
+      </c>
+      <c r="I36" s="250" t="n">
+        <v>61350</v>
+      </c>
+      <c r="J36" s="250" t="n">
+        <v>61350</v>
+      </c>
+      <c r="K36" s="250" t="n">
+        <v>61350</v>
+      </c>
+      <c r="L36" s="252" t="n">
+        <v>306750</v>
+      </c>
+      <c r="M36" s="227" t="inlineStr">
+        <is>
+          <t>B&amp;M SOW M2-Ph2 = $382,824 total (~$61,350/mo × 6 months Aug–Jan 2027). Invoiced monthly. On-site daily field coordination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B37" s="249" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C37" s="222" t="inlineStr">
+        <is>
+          <t>PM Service — Alex Lennox
+$5,500/mo Jul–Dec 2026</t>
+        </is>
+      </c>
+      <c r="D37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="J37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K37" s="250" t="n">
+        <v>5500</v>
+      </c>
+      <c r="L37" s="252" t="n">
+        <v>44000</v>
+      </c>
+      <c r="M37" s="227" t="inlineStr">
+        <is>
+          <t>From Chad workbook: $5,500/mo actuals. Jan–Apr already paid ($22,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="254" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C38" s="231" t="inlineStr">
+        <is>
+          <t>Phase 3 Site Surveys (accelerated — PCR)
+31 sites — pulled into Phase 2</t>
+        </is>
+      </c>
+      <c r="D38" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="256" t="n">
+        <v>43000</v>
+      </c>
+      <c r="F38" s="256" t="n">
+        <v>43000</v>
+      </c>
+      <c r="G38" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="252" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M38" s="233" t="inlineStr">
+        <is>
+          <t>Part of $800K PCR request. ~$2,774/site × 31 = ~$86K. Pending PCR approval. Accelerated from Phase 3 to recover schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B39" s="254" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C39" s="231" t="inlineStr">
+        <is>
+          <t>Phase 3 MPLS Design (accelerated — PCR)
+31 sites pulled into Phase 2</t>
+        </is>
+      </c>
+      <c r="D39" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="256" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G39" s="256" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H39" s="256" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I39" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="252" t="n">
+        <v>360000</v>
+      </c>
+      <c r="M39" s="233" t="inlineStr">
+        <is>
+          <t>Part of $800K PCR request. ~$360K for 31-site design + Phase 3 detail engineering. Pending PCR approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="257" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B40" s="258" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C40" s="236" t="inlineStr">
+        <is>
+          <t>Phase 2 Site Surveys (M1)
+Vinny — pre-construction on-site</t>
+        </is>
+      </c>
+      <c r="D40" s="259" t="n">
+        <v>50085</v>
+      </c>
+      <c r="E40" s="259" t="n">
+        <v>50085</v>
+      </c>
+      <c r="F40" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="252" t="n">
+        <v>100170</v>
+      </c>
+      <c r="M40" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M1 = $100,170. Started May 18. Running parallel with IFC completion. 50% May, 50% Jun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="257" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B41" s="258" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C41" s="236" t="inlineStr">
+        <is>
+          <t>Phase 2 Staging &amp; Assembly (M-Ph0)
+36 Nokia nodes — lab burn-in</t>
+        </is>
+      </c>
+      <c r="D41" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="259" t="n">
+        <v>50085</v>
+      </c>
+      <c r="G41" s="259" t="n">
+        <v>50085</v>
+      </c>
+      <c r="H41" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L41" s="252" t="n">
+        <v>100170</v>
+      </c>
+      <c r="M41" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M-Ph0 = $100,170. B&amp;M provides card slotting requirements. Lab assembly Jul–Aug before shipping to substations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="257" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="258" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C42" s="236" t="inlineStr">
+        <is>
+          <t>Phase 2 Installation — 36 sites (M2)
+Nokia SAR-8, CWDM, Eltek, fiber, patch</t>
+        </is>
+      </c>
+      <c r="D42" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="259" t="n">
+        <v>40068</v>
+      </c>
+      <c r="H42" s="259" t="n">
+        <v>40068</v>
+      </c>
+      <c r="I42" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="252" t="n">
+        <v>80136</v>
+      </c>
+      <c r="M42" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M2 = $80,136. Construction Aug 5 – Sep 28. 3 mobilisations/site. Energise, basic test, notify relay team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="257" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B43" s="258" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C43" s="236" t="inlineStr">
+        <is>
+          <t>Phase 2 Go-Live Sign-Off (M4)
+All 36 sites complete + relay migration done</t>
+        </is>
+      </c>
+      <c r="D43" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="259" t="n">
+        <v>40068</v>
+      </c>
+      <c r="I43" s="259" t="n">
+        <v>40068</v>
+      </c>
+      <c r="J43" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="260" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="252" t="n">
+        <v>80136</v>
+      </c>
+      <c r="M43" s="238" t="inlineStr">
+        <is>
+          <t>Hawkeye SOW M4 = $80,136. Sep–Oct 2026 target. Formal PSEG sign-off required before Hawkeye can invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="253" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B44" s="254" t="inlineStr">
+        <is>
+          <t>Presidio / Nokia</t>
+        </is>
+      </c>
+      <c r="C44" s="231" t="inlineStr">
+        <is>
+          <t>CWDM Cards + Eltek PSUs
+~8-10 cards + accessories</t>
+        </is>
+      </c>
+      <c r="D44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="256" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="255" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L44" s="252" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M44" s="233" t="inlineStr">
+        <is>
+          <t>Graybar closed — sourcing via Presidio. ~$1,500-2,000/card. BOM to be confirmed with Ethan once first IFC packages reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="261" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B45" s="262" t="inlineStr">
+        <is>
+          <t>External Relay Team</t>
+        </is>
+      </c>
+      <c r="C45" s="263" t="inlineStr">
+        <is>
+          <t>PAR Engineering Design — 6 sites
+200hrs × 6 × $200/hr = $240K</t>
+        </is>
+      </c>
+      <c r="D45" s="264" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E45" s="264" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F45" s="264" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G45" s="264" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H45" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="252" t="n">
+        <v>240000</v>
+      </c>
+      <c r="M45" s="266" t="inlineStr">
+        <is>
+          <t>CONFIRMED Vic May 18. External protection engineering team @ $200/hr. Runs parallel with Phase 2 — NO schedule impact. Chok meeting needed URGENTLY to confirm monthly spread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="261" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B46" s="262" t="inlineStr">
+        <is>
+          <t>External Relay Team</t>
+        </is>
+      </c>
+      <c r="C46" s="263" t="inlineStr">
+        <is>
+          <t>PAR Installation + Cutover — 6 sites
+~1,298hrs × $200/hr = $259,500</t>
+        </is>
+      </c>
+      <c r="D46" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="264" t="n">
+        <v>64875</v>
+      </c>
+      <c r="H46" s="264" t="n">
+        <v>64875</v>
+      </c>
+      <c r="I46" s="264" t="n">
+        <v>64875</v>
+      </c>
+      <c r="J46" s="264" t="n">
+        <v>64875</v>
+      </c>
+      <c r="K46" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L46" s="252" t="n">
+        <v>259500</v>
+      </c>
+      <c r="M46" s="266" t="inlineStr">
+        <is>
+          <t>CONFIRMED Vic May 18. Cannot start until: Chok design done + RC-30 delivered. Steven Bradley call before Monday to confirm hours by month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="261" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B47" s="262" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C47" s="263" t="inlineStr">
+        <is>
+          <t>PAR Materials
+Cables, connectors — 6 sites</t>
+        </is>
+      </c>
+      <c r="D47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="264" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="265" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L47" s="252" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M47" s="266" t="inlineStr">
+        <is>
+          <t>CONFIRMED Vic May 18. $30K for cables and connectors across all 6 PAR sites.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="267" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B48" s="268" t="inlineStr">
+        <is>
+          <t>PSEG Internal</t>
+        </is>
+      </c>
+      <c r="C48" s="269" t="inlineStr">
+        <is>
+          <t>Internal Labor — all named resources
+(Jay, Rahiq, Brianna, Chok, Lok, Sameer, et al.)</t>
+        </is>
+      </c>
+      <c r="D48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="E48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="F48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="G48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="H48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="I48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="J48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="K48" s="270" t="n">
+        <v>14684</v>
+      </c>
+      <c r="L48" s="252" t="n">
+        <v>117472</v>
+      </c>
+      <c r="M48" s="271" t="inlineStr">
+        <is>
+          <t>From Chad workbook Monthly Summary: $13,537/mo forecast for labor. Rounded up to $14,684 to include fringe. Martin Gately = $0 (departed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="267" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B49" s="268" t="inlineStr">
+        <is>
+          <t>PSEG / ComTec</t>
+        </is>
+      </c>
+      <c r="C49" s="269" t="inlineStr">
+        <is>
+          <t>Assessments, PQA, Controller, Scheduler
+(Chad, Umair, Marge, PQA audit)</t>
+        </is>
+      </c>
+      <c r="D49" s="270" t="n">
+        <v>6067</v>
+      </c>
+      <c r="E49" s="270" t="n">
+        <v>7567</v>
+      </c>
+      <c r="F49" s="270" t="n">
+        <v>5307</v>
+      </c>
+      <c r="G49" s="270" t="n">
+        <v>4567</v>
+      </c>
+      <c r="H49" s="270" t="n">
+        <v>4567</v>
+      </c>
+      <c r="I49" s="270" t="n">
+        <v>4567</v>
+      </c>
+      <c r="J49" s="270" t="n">
+        <v>4267</v>
+      </c>
+      <c r="K49" s="270" t="n">
+        <v>5067</v>
+      </c>
+      <c r="L49" s="252" t="n">
+        <v>41976</v>
+      </c>
+      <c r="M49" s="271" t="inlineStr">
+        <is>
+          <t>From Chad workbook Monthly Summary. Includes ComTec (Chad $8,400/mo, Umair $5,416/mo), PQA audit, assessments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="248" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B50" s="249" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C50" s="222" t="inlineStr">
+        <is>
+          <t>Lee Blackman — Sr. Network Architect
+$7,200/mo</t>
+        </is>
+      </c>
+      <c r="D50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="H50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="K50" s="250" t="n">
+        <v>7200</v>
+      </c>
+      <c r="L50" s="252" t="n">
+        <v>57600</v>
+      </c>
+      <c r="M50" s="227" t="inlineStr">
+        <is>
+          <t>Cognizant outside services. $7,200/month through Phase 2 completion. PO 7000002490.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="272" t="inlineStr"/>
+      <c r="B51" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MONTHLY FORECAST TOTAL  (Phase 2 remaining 2026)</t>
+        </is>
+      </c>
+      <c r="D51" s="273" t="n">
+        <v>272474</v>
+      </c>
+      <c r="E51" s="273" t="n">
+        <v>372481</v>
+      </c>
+      <c r="F51" s="273" t="n">
+        <v>405776</v>
+      </c>
+      <c r="G51" s="273" t="n">
+        <v>408329</v>
+      </c>
+      <c r="H51" s="273" t="n">
+        <v>358312</v>
+      </c>
+      <c r="I51" s="273" t="n">
+        <v>198244</v>
+      </c>
+      <c r="J51" s="273" t="n">
+        <v>200788</v>
+      </c>
+      <c r="K51" s="273" t="n">
+        <v>93801</v>
+      </c>
+      <c r="L51" s="274" t="n">
+        <v>2310205</v>
+      </c>
+      <c r="M51" s="275" t="inlineStr">
+        <is>
+          <t>⚠ PCR items (Ph3 accel $363K + PAR $334,500) pending approval. Frame relay internal labor not yet included — Steven call needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="276" t="inlineStr"/>
+      <c r="B52" s="277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CUMULATIVE 2026 SPEND  (Jan–Apr actuals + May–Dec forecast)</t>
+        </is>
+      </c>
+      <c r="D52" s="278" t="n">
+        <v>2337618</v>
+      </c>
+      <c r="E52" s="278" t="n">
+        <v>2710099</v>
+      </c>
+      <c r="F52" s="278" t="n">
+        <v>3115875</v>
+      </c>
+      <c r="G52" s="278" t="n">
+        <v>3524204</v>
+      </c>
+      <c r="H52" s="278" t="n">
+        <v>3882516</v>
+      </c>
+      <c r="I52" s="278" t="n">
+        <v>4080760</v>
+      </c>
+      <c r="J52" s="278" t="n">
+        <v>4281548</v>
+      </c>
+      <c r="K52" s="278" t="n">
+        <v>4375349</v>
+      </c>
+      <c r="L52" s="279" t="n">
+        <v>4375349</v>
+      </c>
+      <c r="M52" s="280" t="inlineStr">
+        <is>
+          <t>CP Budget 2026: $2,600,000  |  Projected EAC: $4,375,349  |  Variance: $-1,775,349 (OVER budget)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION 3 — PCR REQUEST SUMMARY  (Two-Part — Submission Target: May/Jun 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="282" t="inlineStr">
+        <is>
+          <t>PCR #</t>
+        </is>
+      </c>
+      <c r="B55" s="282" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C55" s="282" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="D55" s="282" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="E55" s="282" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F55" s="282" t="inlineStr"/>
+      <c r="G55" s="282" t="inlineStr"/>
+      <c r="H55" s="282" t="inlineStr"/>
+      <c r="I55" s="282" t="inlineStr"/>
+      <c r="J55" s="282" t="inlineStr"/>
+      <c r="K55" s="282" t="inlineStr"/>
+      <c r="L55" s="282" t="inlineStr"/>
+      <c r="M55" s="282" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="283" t="inlineStr">
+        <is>
+          <t>PCR 1</t>
+        </is>
+      </c>
+      <c r="B56" s="284" t="inlineStr">
+        <is>
+          <t>PAR — Engineering</t>
+        </is>
+      </c>
+      <c r="D56" s="285" t="inlineStr">
+        <is>
+          <t>200 hrs × 6 sites × $200/hr</t>
+        </is>
+      </c>
+      <c r="E56" s="286" t="inlineStr">
+        <is>
+          <t>$240,000</t>
+        </is>
+      </c>
+      <c r="F56" s="283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G56" s="287" t="inlineStr">
+        <is>
+          <t>External relay/protection engineers. Runs PARALLEL with Phase 2. No schedule impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="283" t="inlineStr">
+        <is>
+          <t>PCR 1</t>
+        </is>
+      </c>
+      <c r="B57" s="284" t="inlineStr">
+        <is>
+          <t>PAR — Installation</t>
+        </is>
+      </c>
+      <c r="D57" s="285" t="inlineStr">
+        <is>
+          <t>~1,298 hrs × $200/hr</t>
+        </is>
+      </c>
+      <c r="E57" s="286" t="inlineStr">
+        <is>
+          <t>$259,500</t>
+        </is>
+      </c>
+      <c r="F57" s="283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G57" s="287" t="inlineStr">
+        <is>
+          <t>External relay team. Starts after RC-30 delivery (~Jun) and Chok design complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="283" t="inlineStr">
+        <is>
+          <t>PCR 1</t>
+        </is>
+      </c>
+      <c r="B58" s="284" t="inlineStr">
+        <is>
+          <t>PAR — Materials</t>
+        </is>
+      </c>
+      <c r="D58" s="285" t="inlineStr">
+        <is>
+          <t>Cables, connectors (6 sites)</t>
+        </is>
+      </c>
+      <c r="E58" s="286" t="inlineStr">
+        <is>
+          <t>$30,000</t>
+        </is>
+      </c>
+      <c r="F58" s="283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G58" s="287" t="inlineStr">
+        <is>
+          <t>Confirmed by Vic May 18 2026 call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="288" t="inlineStr">
+        <is>
+          <t>PCR 1</t>
+        </is>
+      </c>
+      <c r="B59" s="289" t="inlineStr">
+        <is>
+          <t>PAR TOTAL</t>
+        </is>
+      </c>
+      <c r="D59" s="290" t="inlineStr"/>
+      <c r="E59" s="291" t="inlineStr">
+        <is>
+          <t>$529,500</t>
+        </is>
+      </c>
+      <c r="F59" s="292" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G59" s="293" t="inlineStr">
+        <is>
+          <t>CONFIRMED total per Vic/Jay May 18 call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="294" t="inlineStr">
+        <is>
+          <t>PCR 2</t>
+        </is>
+      </c>
+      <c r="B60" s="295" t="inlineStr">
+        <is>
+          <t>Ph3 Site Surveys (accelerated)</t>
+        </is>
+      </c>
+      <c r="D60" s="296" t="inlineStr">
+        <is>
+          <t>31 sites × ~$2,774/site</t>
+        </is>
+      </c>
+      <c r="E60" s="297" t="inlineStr">
+        <is>
+          <t>~$86,000</t>
+        </is>
+      </c>
+      <c r="F60" s="294" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G60" s="233" t="inlineStr">
+        <is>
+          <t>Pulled from Phase 3 into Phase 2. Recovers 5-month schedule impact from PAR discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="294" t="inlineStr">
+        <is>
+          <t>PCR 2</t>
+        </is>
+      </c>
+      <c r="B61" s="295" t="inlineStr">
+        <is>
+          <t>Ph3 MPLS Design (accelerated)</t>
+        </is>
+      </c>
+      <c r="D61" s="296" t="inlineStr">
+        <is>
+          <t>31 sites — B&amp;M detail design</t>
+        </is>
+      </c>
+      <c r="E61" s="297" t="inlineStr">
+        <is>
+          <t>~$714,000</t>
+        </is>
+      </c>
+      <c r="F61" s="294" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G61" s="233" t="inlineStr">
+        <is>
+          <t>B&amp;M Phase 3 design pulled into Phase 2. Enables project completion Nov 2027 vs May 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="288" t="inlineStr">
+        <is>
+          <t>PCR 2</t>
+        </is>
+      </c>
+      <c r="B62" s="289" t="inlineStr">
+        <is>
+          <t>Ph3 ACCELERATED TOTAL</t>
+        </is>
+      </c>
+      <c r="D62" s="290" t="inlineStr"/>
+      <c r="E62" s="291" t="inlineStr">
+        <is>
+          <t>~$800,000</t>
+        </is>
+      </c>
+      <c r="F62" s="292" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G62" s="293" t="inlineStr">
+        <is>
+          <t>Pending PCR approval. Brings Phase 3 work forward to prevent 5-month slip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="298" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B63" s="299" t="inlineStr">
+        <is>
+          <t>COMBINED PCR REQUEST</t>
+        </is>
+      </c>
+      <c r="D63" s="300" t="inlineStr">
+        <is>
+          <t>PAR $530K + Ph3 Accel $800K</t>
+        </is>
+      </c>
+      <c r="E63" s="301" t="inlineStr">
+        <is>
+          <t>~$1.33M</t>
+        </is>
+      </c>
+      <c r="F63" s="302" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G63" s="303" t="inlineStr">
+        <is>
+          <t>Vic confirmed range $1.2–1.33M. Submit as two separate PCRs but present together to CIO.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="G63:M63"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="G60:M60"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="G56:M56"/>
+    <mergeCell ref="G59:M59"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="M52"/>
+    <mergeCell ref="G61:M61"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="M51"/>
+    <mergeCell ref="A54:M54"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="G57:M57"/>
+    <mergeCell ref="G62:M62"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="G58:M58"/>
+    <mergeCell ref="A33:M33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
+++ b/PRJ13797_JMUX_Cost_Forecast_2026_2027.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SUMMARY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="B&amp;M Site Breakdown" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Nokia Ph3 Equipment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Internal Labor" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Phase 2 Monthly Forecast" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026 Budget vs Forecast" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="B&amp;M Site Breakdown" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Nokia Ph3 Equipment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Internal Labor" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Phase 2 Monthly Forecast" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,11 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]&quot;($&quot;#,##0&quot;)&quot;"/>
   </numFmts>
-  <fonts count="81">
+  <fonts count="91">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -431,8 +433,57 @@
       <color rgb="00C00000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFF00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="00BBBBBB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F5C7A"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001E5631"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -534,8 +585,13 @@
         <fgColor rgb="00E8D5F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -615,11 +671,55 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1516,6 +1616,234 @@
     <xf numFmtId="0" fontId="72" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="82" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="86" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="87" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="88" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="74" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="89" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="62" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="89" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="89" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="73" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1881,6 +2209,1956 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="304" t="inlineStr">
+        <is>
+          <t>PRJ13797 — JMUX REPLACEMENT  |  2026 BUDGET vs FORECAST — WILL WE RUN OUT OF MONEY?  |  May 18 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="305" t="inlineStr">
+        <is>
+          <t>CP Budget 2026: $2,600,000  |  Actuals Jan–Apr: $2,065,144  |  Remaining: $534,856  |  Base forecast May–Dec: $1,294,293  |  ★ BUDGET RUNS OUT IN JUNE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION 1 — BUDGET STATUS SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="307" t="inlineStr">
+        <is>
+          <t>CP Budget 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="308" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="E4" s="271" t="inlineStr">
+        <is>
+          <t>Approved Capital Program budget for 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="307" t="inlineStr">
+        <is>
+          <t>Actuals Jan–Apr 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="308" t="n">
+        <v>2065144</v>
+      </c>
+      <c r="E5" s="271" t="inlineStr">
+        <is>
+          <t>Already spent: Jan $575K + Feb $276K + Mar $919K + Apr $295K</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="309" t="inlineStr">
+        <is>
+          <t>Remaining Budget TODAY</t>
+        </is>
+      </c>
+      <c r="B6" s="310" t="n">
+        <v>534856</v>
+      </c>
+      <c r="E6" s="311" t="inlineStr">
+        <is>
+          <t>★ Only $534,856 left for remaining 8 months of 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="312" t="inlineStr">
+        <is>
+          <t>Base Forecast May–Dec</t>
+        </is>
+      </c>
+      <c r="B7" s="313" t="n">
+        <v>1294293</v>
+      </c>
+      <c r="E7" s="314" t="inlineStr">
+        <is>
+          <t>Contracted/committed spend EXCLUDING PCR items</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="315" t="inlineStr">
+        <is>
+          <t>PCR Forecast May–Dec</t>
+        </is>
+      </c>
+      <c r="B8" s="316" t="n">
+        <v>889500</v>
+      </c>
+      <c r="E8" s="317" t="inlineStr">
+        <is>
+          <t>PCR items pending approval: PAR $530K + Ph3 MPLS accel $360K</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="309" t="inlineStr">
+        <is>
+          <t>TOTAL Forecast May–Dec</t>
+        </is>
+      </c>
+      <c r="B9" s="310" t="n">
+        <v>2183793</v>
+      </c>
+      <c r="E9" s="311" t="inlineStr">
+        <is>
+          <t>BASE + PCR combined May–Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="309" t="inlineStr">
+        <is>
+          <t>Full Year EAC (BASE only)</t>
+        </is>
+      </c>
+      <c r="B10" s="310" t="n">
+        <v>3359437</v>
+      </c>
+      <c r="E10" s="311" t="inlineStr">
+        <is>
+          <t>$759K OVER budget on contracted work alone — NO PCR yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="309" t="inlineStr">
+        <is>
+          <t>Full Year EAC (with PCR)</t>
+        </is>
+      </c>
+      <c r="B11" s="310" t="n">
+        <v>4248937</v>
+      </c>
+      <c r="E11" s="311" t="inlineStr">
+        <is>
+          <t>$1,648,937 OVER budget if PCR approved without extra funding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="309" t="inlineStr">
+        <is>
+          <t>Budget Exhausted (BASE)</t>
+        </is>
+      </c>
+      <c r="B12" s="318" t="inlineStr">
+        <is>
+          <t>END OF JUNE 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="311" t="inlineStr">
+        <is>
+          <t>★★★ On base spend alone, remaining $534,856 is consumed by end of June. Jul–Dec = UNFUNDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION 2 — MONTHLY CASHFLOW TABLE  (Jan–Apr = Actuals  |  May–Dec = Forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="319" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B15" s="319" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="C15" s="319" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="D15" s="319" t="inlineStr">
+        <is>
+          <t>Jan
+Actual</t>
+        </is>
+      </c>
+      <c r="E15" s="319" t="inlineStr">
+        <is>
+          <t>Feb
+Actual</t>
+        </is>
+      </c>
+      <c r="F15" s="319" t="inlineStr">
+        <is>
+          <t>Mar
+Actual</t>
+        </is>
+      </c>
+      <c r="G15" s="319" t="inlineStr">
+        <is>
+          <t>Apr
+Actual</t>
+        </is>
+      </c>
+      <c r="H15" s="320" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="I15" s="320" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="J15" s="320" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="K15" s="320" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="L15" s="320" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="M15" s="321" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="N15" s="321" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="O15" s="321" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="P15" s="321" t="inlineStr">
+        <is>
+          <t>2026
+TOTAL</t>
+        </is>
+      </c>
+      <c r="Q15" s="321" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="323" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C16" s="324" t="inlineStr">
+        <is>
+          <t>IFR/IFC Design (SOW M4)
+Rolling per site deliveries</t>
+        </is>
+      </c>
+      <c r="D16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="326" t="n">
+        <v>162181</v>
+      </c>
+      <c r="H16" s="327" t="n">
+        <v>148938</v>
+      </c>
+      <c r="I16" s="327" t="n">
+        <v>89445</v>
+      </c>
+      <c r="J16" s="327" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="328" t="n">
+        <v>450564</v>
+      </c>
+      <c r="Q16" s="329" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="323" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C17" s="324" t="inlineStr">
+        <is>
+          <t>PM — Alex Lennox $5,500/mo</t>
+        </is>
+      </c>
+      <c r="D17" s="326" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E17" s="326" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F17" s="326" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G17" s="326" t="n">
+        <v>5500</v>
+      </c>
+      <c r="H17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="J17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="K17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="L17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="M17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="N17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="O17" s="327" t="n">
+        <v>5500</v>
+      </c>
+      <c r="P17" s="328" t="n">
+        <v>66000</v>
+      </c>
+      <c r="Q17" s="329" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="323" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C18" s="324" t="inlineStr">
+        <is>
+          <t>Phase 2 CSC — on-site Aug–Dec
+$61,350/mo</t>
+        </is>
+      </c>
+      <c r="D18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="325" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="327" t="n">
+        <v>61350</v>
+      </c>
+      <c r="L18" s="327" t="n">
+        <v>61350</v>
+      </c>
+      <c r="M18" s="327" t="n">
+        <v>61350</v>
+      </c>
+      <c r="N18" s="327" t="n">
+        <v>61350</v>
+      </c>
+      <c r="O18" s="327" t="n">
+        <v>61350</v>
+      </c>
+      <c r="P18" s="328" t="n">
+        <v>306750</v>
+      </c>
+      <c r="Q18" s="329" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B19" s="331" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C19" s="332" t="inlineStr">
+        <is>
+          <t>Phase 1 SOW remaining 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="326" t="n">
+        <v>335993</v>
+      </c>
+      <c r="G19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O19" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="328" t="n">
+        <v>335993</v>
+      </c>
+      <c r="Q19" s="334" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="331" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C20" s="332" t="inlineStr">
+        <is>
+          <t>Phase 2 Surveys M1 ($100,170)</t>
+        </is>
+      </c>
+      <c r="D20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="335" t="n">
+        <v>50085</v>
+      </c>
+      <c r="I20" s="335" t="n">
+        <v>50085</v>
+      </c>
+      <c r="J20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O20" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="328" t="n">
+        <v>100170</v>
+      </c>
+      <c r="Q20" s="334" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="331" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C21" s="332" t="inlineStr">
+        <is>
+          <t>Phase 2 Staging M-Ph0 ($100,170)</t>
+        </is>
+      </c>
+      <c r="D21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="335" t="n">
+        <v>50085</v>
+      </c>
+      <c r="K21" s="335" t="n">
+        <v>50085</v>
+      </c>
+      <c r="L21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O21" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="328" t="n">
+        <v>100170</v>
+      </c>
+      <c r="Q21" s="334" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="330" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="331" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C22" s="332" t="inlineStr">
+        <is>
+          <t>Phase 2 Installation M2 ($80,136)</t>
+        </is>
+      </c>
+      <c r="D22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="335" t="n">
+        <v>40068</v>
+      </c>
+      <c r="L22" s="335" t="n">
+        <v>40068</v>
+      </c>
+      <c r="M22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="328" t="n">
+        <v>80136</v>
+      </c>
+      <c r="Q22" s="334" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="330" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="331" t="inlineStr">
+        <is>
+          <t>Hawkeye</t>
+        </is>
+      </c>
+      <c r="C23" s="332" t="inlineStr">
+        <is>
+          <t>Phase 2 Go-Live M4 ($80,136)</t>
+        </is>
+      </c>
+      <c r="D23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="335" t="n">
+        <v>40068</v>
+      </c>
+      <c r="M23" s="335" t="n">
+        <v>40068</v>
+      </c>
+      <c r="N23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O23" s="333" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="328" t="n">
+        <v>80136</v>
+      </c>
+      <c r="Q23" s="334" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="336" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="337" t="inlineStr">
+        <is>
+          <t>Nokia/Presidio</t>
+        </is>
+      </c>
+      <c r="C24" s="338" t="inlineStr">
+        <is>
+          <t>Equipment (CWDM, Eltek PSUs)</t>
+        </is>
+      </c>
+      <c r="D24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="326" t="n">
+        <v>753373</v>
+      </c>
+      <c r="G24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="340" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="328" t="n">
+        <v>778373</v>
+      </c>
+      <c r="Q24" s="341" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="336" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="337" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C25" s="338" t="inlineStr">
+        <is>
+          <t>Iniven RC-30 PAR equipment</t>
+        </is>
+      </c>
+      <c r="D25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="326" t="n">
+        <v>52500</v>
+      </c>
+      <c r="H25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="340" t="n">
+        <v>52500</v>
+      </c>
+      <c r="J25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O25" s="339" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="328" t="n">
+        <v>105000</v>
+      </c>
+      <c r="Q25" s="341" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="342" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="343" t="inlineStr">
+        <is>
+          <t>Ext.Relay</t>
+        </is>
+      </c>
+      <c r="C26" s="344" t="inlineStr">
+        <is>
+          <t>PAR Engineering ★PCR★
+200hrs×6×$200/hr</t>
+        </is>
+      </c>
+      <c r="D26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="346" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I26" s="346" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J26" s="346" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K26" s="346" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O26" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="347" t="n">
+        <v>240000</v>
+      </c>
+      <c r="Q26" s="348" t="inlineStr">
+        <is>
+          <t>★PCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="342" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="343" t="inlineStr">
+        <is>
+          <t>Ext.Relay</t>
+        </is>
+      </c>
+      <c r="C27" s="344" t="inlineStr">
+        <is>
+          <t>PAR Installation ★PCR★
+~1,298hrs×$200/hr</t>
+        </is>
+      </c>
+      <c r="D27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K27" s="346" t="n">
+        <v>64875</v>
+      </c>
+      <c r="L27" s="346" t="n">
+        <v>64875</v>
+      </c>
+      <c r="M27" s="346" t="n">
+        <v>64875</v>
+      </c>
+      <c r="N27" s="346" t="n">
+        <v>64875</v>
+      </c>
+      <c r="O27" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="347" t="n">
+        <v>259500</v>
+      </c>
+      <c r="Q27" s="348" t="inlineStr">
+        <is>
+          <t>★PCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="342" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B28" s="343" t="inlineStr">
+        <is>
+          <t>Procure</t>
+        </is>
+      </c>
+      <c r="C28" s="344" t="inlineStr">
+        <is>
+          <t>PAR Materials ★PCR★</t>
+        </is>
+      </c>
+      <c r="D28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="346" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="347" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Q28" s="348" t="inlineStr">
+        <is>
+          <t>★PCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="342" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B29" s="343" t="inlineStr">
+        <is>
+          <t>B&amp;M</t>
+        </is>
+      </c>
+      <c r="C29" s="344" t="inlineStr">
+        <is>
+          <t>Ph3 MPLS Design ★PCR★
+(accelerated into Ph2)</t>
+        </is>
+      </c>
+      <c r="D29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="346" t="n">
+        <v>120000</v>
+      </c>
+      <c r="K29" s="346" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L29" s="346" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O29" s="345" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="347" t="n">
+        <v>360000</v>
+      </c>
+      <c r="Q29" s="348" t="inlineStr">
+        <is>
+          <t>★PCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="349" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="350" t="inlineStr">
+        <is>
+          <t>PSEG</t>
+        </is>
+      </c>
+      <c r="C30" s="351" t="inlineStr">
+        <is>
+          <t>Internal Labor (all resources)</t>
+        </is>
+      </c>
+      <c r="D30" s="326" t="n">
+        <v>13537</v>
+      </c>
+      <c r="E30" s="326" t="n">
+        <v>6082</v>
+      </c>
+      <c r="F30" s="326" t="n">
+        <v>13537</v>
+      </c>
+      <c r="G30" s="326" t="n">
+        <v>13537</v>
+      </c>
+      <c r="H30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="I30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="J30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="K30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="L30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="M30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="N30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="O30" s="352" t="n">
+        <v>14684</v>
+      </c>
+      <c r="P30" s="328" t="n">
+        <v>164165</v>
+      </c>
+      <c r="Q30" s="353" t="inlineStr">
+        <is>
+          <t>Labor</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="322" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="323" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C31" s="324" t="inlineStr">
+        <is>
+          <t>Lee Blackman $7,200/mo</t>
+        </is>
+      </c>
+      <c r="D31" s="326" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E31" s="326" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F31" s="326" t="n">
+        <v>29000</v>
+      </c>
+      <c r="G31" s="326" t="n">
+        <v>14902</v>
+      </c>
+      <c r="H31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="K31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="L31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="M31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="N31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="O31" s="327" t="n">
+        <v>7200</v>
+      </c>
+      <c r="P31" s="328" t="n">
+        <v>131502</v>
+      </c>
+      <c r="Q31" s="329" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="349" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B32" s="350" t="inlineStr">
+        <is>
+          <t>PSEG</t>
+        </is>
+      </c>
+      <c r="C32" s="351" t="inlineStr">
+        <is>
+          <t>Assessments/PQA/Chad/Umair</t>
+        </is>
+      </c>
+      <c r="D32" s="326" t="n">
+        <v>11696</v>
+      </c>
+      <c r="E32" s="326" t="n">
+        <v>3396</v>
+      </c>
+      <c r="F32" s="326" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G32" s="326" t="n">
+        <v>3669</v>
+      </c>
+      <c r="H32" s="352" t="n">
+        <v>6067</v>
+      </c>
+      <c r="I32" s="352" t="n">
+        <v>7567</v>
+      </c>
+      <c r="J32" s="352" t="n">
+        <v>5307</v>
+      </c>
+      <c r="K32" s="352" t="n">
+        <v>4567</v>
+      </c>
+      <c r="L32" s="352" t="n">
+        <v>4567</v>
+      </c>
+      <c r="M32" s="352" t="n">
+        <v>4567</v>
+      </c>
+      <c r="N32" s="352" t="n">
+        <v>4267</v>
+      </c>
+      <c r="O32" s="352" t="n">
+        <v>5067</v>
+      </c>
+      <c r="P32" s="328" t="n">
+        <v>72737</v>
+      </c>
+      <c r="Q32" s="353" t="inlineStr">
+        <is>
+          <t>Assess</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MONTHLY TOTAL</t>
+        </is>
+      </c>
+      <c r="D33" s="355" t="n">
+        <v>45733</v>
+      </c>
+      <c r="E33" s="355" t="n">
+        <v>29978</v>
+      </c>
+      <c r="F33" s="355" t="n">
+        <v>1149403</v>
+      </c>
+      <c r="G33" s="355" t="n">
+        <v>252289</v>
+      </c>
+      <c r="H33" s="355" t="n">
+        <v>272474</v>
+      </c>
+      <c r="I33" s="355" t="n">
+        <v>331981</v>
+      </c>
+      <c r="J33" s="355" t="n">
+        <v>362776</v>
+      </c>
+      <c r="K33" s="355" t="n">
+        <v>408329</v>
+      </c>
+      <c r="L33" s="355" t="n">
+        <v>358312</v>
+      </c>
+      <c r="M33" s="355" t="n">
+        <v>198244</v>
+      </c>
+      <c r="N33" s="355" t="n">
+        <v>157876</v>
+      </c>
+      <c r="O33" s="355" t="n">
+        <v>93801</v>
+      </c>
+      <c r="P33" s="356" t="n">
+        <v>3661196</v>
+      </c>
+      <c r="Q33" s="357" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CUMULATIVE SPEND</t>
+        </is>
+      </c>
+      <c r="D34" s="278" t="n">
+        <v>45733</v>
+      </c>
+      <c r="E34" s="278" t="n">
+        <v>75711</v>
+      </c>
+      <c r="F34" s="278" t="n">
+        <v>1225114</v>
+      </c>
+      <c r="G34" s="278" t="n">
+        <v>1477403</v>
+      </c>
+      <c r="H34" s="278" t="n">
+        <v>1749877</v>
+      </c>
+      <c r="I34" s="278" t="n">
+        <v>2081858</v>
+      </c>
+      <c r="J34" s="278" t="n">
+        <v>2444634</v>
+      </c>
+      <c r="K34" s="278" t="n">
+        <v>2852963</v>
+      </c>
+      <c r="L34" s="278" t="n">
+        <v>3211275</v>
+      </c>
+      <c r="M34" s="278" t="n">
+        <v>3409519</v>
+      </c>
+      <c r="N34" s="278" t="n">
+        <v>3567395</v>
+      </c>
+      <c r="O34" s="278" t="n">
+        <v>3661196</v>
+      </c>
+      <c r="P34" s="359" t="n">
+        <v>3661196</v>
+      </c>
+      <c r="Q34" s="360" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CP BUDGET 2026 = $2,600,000</t>
+        </is>
+      </c>
+      <c r="D35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="E35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="F35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="G35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="H35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="I35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="J35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="K35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="L35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="M35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="N35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="O35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="P35" s="362" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="Q35" s="363" t="inlineStr">
+        <is>
+          <t>BUDGET</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VARIANCE  (Budget − Cumulative)  🔴 RED = OVER BUDGET</t>
+        </is>
+      </c>
+      <c r="D36" s="365" t="n">
+        <v>2554267</v>
+      </c>
+      <c r="E36" s="365" t="n">
+        <v>2524289</v>
+      </c>
+      <c r="F36" s="365" t="n">
+        <v>1374886</v>
+      </c>
+      <c r="G36" s="365" t="n">
+        <v>1122597</v>
+      </c>
+      <c r="H36" s="365" t="n">
+        <v>850123</v>
+      </c>
+      <c r="I36" s="365" t="n">
+        <v>518142</v>
+      </c>
+      <c r="J36" s="365" t="n">
+        <v>155366</v>
+      </c>
+      <c r="K36" s="366" t="n">
+        <v>-252963</v>
+      </c>
+      <c r="L36" s="366" t="n">
+        <v>-611275</v>
+      </c>
+      <c r="M36" s="366" t="n">
+        <v>-809519</v>
+      </c>
+      <c r="N36" s="366" t="n">
+        <v>-967395</v>
+      </c>
+      <c r="O36" s="366" t="n">
+        <v>-1061196</v>
+      </c>
+      <c r="P36" s="367" t="n">
+        <v>-1061196</v>
+      </c>
+      <c r="Q36" s="368" t="inlineStr">
+        <is>
+          <t>⚠ OVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▶  SECTION 3 — OPTIONS TO CLOSE THE GAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="369" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B39" s="369" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C39" s="369" t="inlineStr">
+        <is>
+          <t>$ Impact</t>
+        </is>
+      </c>
+      <c r="D39" s="369" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="E39" s="370" t="n"/>
+      <c r="F39" s="370" t="n"/>
+      <c r="G39" s="370" t="n"/>
+      <c r="H39" s="370" t="n"/>
+      <c r="I39" s="370" t="n"/>
+      <c r="J39" s="370" t="n"/>
+      <c r="K39" s="370" t="n"/>
+      <c r="L39" s="370" t="n"/>
+      <c r="M39" s="370" t="n"/>
+      <c r="N39" s="370" t="n"/>
+      <c r="O39" s="370" t="n"/>
+      <c r="P39" s="370" t="n"/>
+      <c r="Q39" s="370" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="371" t="inlineStr">
+        <is>
+          <t>1 ✅ RECOMMENDED</t>
+        </is>
+      </c>
+      <c r="B40" s="371" t="inlineStr">
+        <is>
+          <t>Submit FULL PCR: PAR $530K + Ph3 Accel $800K
+→ Request 2026 budget increase to ~$3.93M</t>
+        </is>
+      </c>
+      <c r="H40" s="372" t="inlineStr">
+        <is>
+          <t>+$1,330,000</t>
+        </is>
+      </c>
+      <c r="J40" s="373" t="inlineStr">
+        <is>
+          <t>Best path. Scope is real and confirmed by Vic. Recovers 5-month schedule slip. Without this, Phase 2 construction CANNOT start Aug 5 — budget is exhausted in June. Vic already briefed. Submit ASAP to Finance/CIO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="374" t="inlineStr">
+        <is>
+          <t>2 — PARTIAL</t>
+        </is>
+      </c>
+      <c r="B41" s="374" t="inlineStr">
+        <is>
+          <t>Submit PAR PCR only ($530K)
+Defer Ph3 MPLS design to 2027 budget</t>
+        </is>
+      </c>
+      <c r="H41" s="375" t="inlineStr">
+        <is>
+          <t>+$530,000</t>
+        </is>
+      </c>
+      <c r="J41" s="317" t="inlineStr">
+        <is>
+          <t>Partial relief. Still $759K over on base contracted work. Need to explain to CIO why we're already over budget before PCR. Works if Finance won't approve $1.33M in one shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="376" t="inlineStr">
+        <is>
+          <t>3 — AGGRESSIVE</t>
+        </is>
+      </c>
+      <c r="B42" s="376" t="inlineStr">
+        <is>
+          <t>Defer PAR installation to Jan 2027
+Keep PAR engineering in 2026 only</t>
+        </is>
+      </c>
+      <c r="H42" s="377" t="inlineStr">
+        <is>
+          <t>Saves $259,500 in 2026</t>
+        </is>
+      </c>
+      <c r="J42" s="314" t="inlineStr">
+        <is>
+          <t>Risky — delays NERC-CIP compliance. RC-30 already ordered (8-week lead). Team is ready. Deferring = wasted momentum. Not recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="378" t="inlineStr">
+        <is>
+          <t>4 ❌ WORST CASE</t>
+        </is>
+      </c>
+      <c r="B43" s="378" t="inlineStr">
+        <is>
+          <t>Do nothing — absorb overrun</t>
+        </is>
+      </c>
+      <c r="H43" s="379" t="inlineStr">
+        <is>
+          <t>−$1,648,937 unfunded</t>
+        </is>
+      </c>
+      <c r="J43" s="311" t="inlineStr">
+        <is>
+          <t>Not viable. Budget exhausted June 2026. Phase 2 construction halts Aug 5. Hawkeye field teams idle. Schedule slips to 2028. NERC-CIP non-compliance risk.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="A43"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="E7:Q7"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="J40:Q40"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A40"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E12:Q12"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="E5:Q5"/>
+    <mergeCell ref="E8:Q8"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="E4:Q4"/>
+    <mergeCell ref="J41:Q41"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A41"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E10:Q10"/>
+    <mergeCell ref="A14:Q14"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="J43:Q43"/>
+    <mergeCell ref="E9:Q9"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="A38:Q38"/>
+    <mergeCell ref="E6:Q6"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="A42"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E11:Q11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3404,7 +5682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4746,7 +7024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5675,7 +7953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8084,7 +10362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8434,7 +10712,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="B10" s="230" t="inlineStr">
+      <c r="B10" s="295" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
@@ -8474,7 +10752,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B11" s="230" t="inlineStr">
+      <c r="B11" s="295" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
@@ -8514,7 +10792,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="B12" s="230" t="inlineStr">
+      <c r="B12" s="295" t="inlineStr">
         <is>
           <t>Procurement</t>
         </is>
@@ -8806,7 +11084,7 @@
           <t>R3</t>
         </is>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="295" t="inlineStr">
         <is>
           <t>RTU Migration</t>
         </is>
@@ -8850,7 +11128,7 @@
           <t>R4</t>
         </is>
       </c>
-      <c r="B20" s="230" t="inlineStr">
+      <c r="B20" s="295" t="inlineStr">
         <is>
           <t>RTU Migration</t>
         </is>
@@ -8946,7 +11224,7 @@
           <t>A2</t>
         </is>
       </c>
-      <c r="B22" s="230" t="inlineStr">
+      <c r="B22" s="295" t="inlineStr">
         <is>
           <t>PAR</t>
         </is>
@@ -10469,6 +12747,7 @@
           <t>PAR — Engineering</t>
         </is>
       </c>
+      <c r="C56" s="380" t="n"/>
       <c r="D56" s="285" t="inlineStr">
         <is>
           <t>200 hrs × 6 sites × $200/hr</t>
@@ -10489,6 +12768,12 @@
           <t>External relay/protection engineers. Runs PARALLEL with Phase 2. No schedule impact.</t>
         </is>
       </c>
+      <c r="H56" s="381" t="n"/>
+      <c r="I56" s="381" t="n"/>
+      <c r="J56" s="381" t="n"/>
+      <c r="K56" s="381" t="n"/>
+      <c r="L56" s="381" t="n"/>
+      <c r="M56" s="380" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="283" t="inlineStr">
@@ -10501,6 +12786,7 @@
           <t>PAR — Installation</t>
         </is>
       </c>
+      <c r="C57" s="380" t="n"/>
       <c r="D57" s="285" t="inlineStr">
         <is>
           <t>~1,298 hrs × $200/hr</t>
@@ -10521,6 +12807,12 @@
           <t>External relay team. Starts after RC-30 delivery (~Jun) and Chok design complete.</t>
         </is>
       </c>
+      <c r="H57" s="381" t="n"/>
+      <c r="I57" s="381" t="n"/>
+      <c r="J57" s="381" t="n"/>
+      <c r="K57" s="381" t="n"/>
+      <c r="L57" s="381" t="n"/>
+      <c r="M57" s="380" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="283" t="inlineStr">
@@ -10533,6 +12825,7 @@
           <t>PAR — Materials</t>
         </is>
       </c>
+      <c r="C58" s="380" t="n"/>
       <c r="D58" s="285" t="inlineStr">
         <is>
           <t>Cables, connectors (6 sites)</t>
@@ -10553,6 +12846,12 @@
           <t>Confirmed by Vic May 18 2026 call.</t>
         </is>
       </c>
+      <c r="H58" s="381" t="n"/>
+      <c r="I58" s="381" t="n"/>
+      <c r="J58" s="381" t="n"/>
+      <c r="K58" s="381" t="n"/>
+      <c r="L58" s="381" t="n"/>
+      <c r="M58" s="380" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="288" t="inlineStr">
@@ -10565,6 +12864,7 @@
           <t>PAR TOTAL</t>
         </is>
       </c>
+      <c r="C59" s="380" t="n"/>
       <c r="D59" s="290" t="inlineStr"/>
       <c r="E59" s="291" t="inlineStr">
         <is>
@@ -10581,6 +12881,12 @@
           <t>CONFIRMED total per Vic/Jay May 18 call.</t>
         </is>
       </c>
+      <c r="H59" s="381" t="n"/>
+      <c r="I59" s="381" t="n"/>
+      <c r="J59" s="381" t="n"/>
+      <c r="K59" s="381" t="n"/>
+      <c r="L59" s="381" t="n"/>
+      <c r="M59" s="380" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="294" t="inlineStr">
@@ -10593,6 +12899,7 @@
           <t>Ph3 Site Surveys (accelerated)</t>
         </is>
       </c>
+      <c r="C60" s="380" t="n"/>
       <c r="D60" s="296" t="inlineStr">
         <is>
           <t>31 sites × ~$2,774/site</t>
@@ -10613,6 +12920,12 @@
           <t>Pulled from Phase 3 into Phase 2. Recovers 5-month schedule impact from PAR discovery.</t>
         </is>
       </c>
+      <c r="H60" s="381" t="n"/>
+      <c r="I60" s="381" t="n"/>
+      <c r="J60" s="381" t="n"/>
+      <c r="K60" s="381" t="n"/>
+      <c r="L60" s="381" t="n"/>
+      <c r="M60" s="380" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="294" t="inlineStr">
@@ -10625,6 +12938,7 @@
           <t>Ph3 MPLS Design (accelerated)</t>
         </is>
       </c>
+      <c r="C61" s="380" t="n"/>
       <c r="D61" s="296" t="inlineStr">
         <is>
           <t>31 sites — B&amp;M detail design</t>
@@ -10645,6 +12959,12 @@
           <t>B&amp;M Phase 3 design pulled into Phase 2. Enables project completion Nov 2027 vs May 2028.</t>
         </is>
       </c>
+      <c r="H61" s="381" t="n"/>
+      <c r="I61" s="381" t="n"/>
+      <c r="J61" s="381" t="n"/>
+      <c r="K61" s="381" t="n"/>
+      <c r="L61" s="381" t="n"/>
+      <c r="M61" s="380" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="288" t="inlineStr">
@@ -10657,6 +12977,7 @@
           <t>Ph3 ACCELERATED TOTAL</t>
         </is>
       </c>
+      <c r="C62" s="380" t="n"/>
       <c r="D62" s="290" t="inlineStr"/>
       <c r="E62" s="291" t="inlineStr">
         <is>
@@ -10673,6 +12994,12 @@
           <t>Pending PCR approval. Brings Phase 3 work forward to prevent 5-month slip.</t>
         </is>
       </c>
+      <c r="H62" s="381" t="n"/>
+      <c r="I62" s="381" t="n"/>
+      <c r="J62" s="381" t="n"/>
+      <c r="K62" s="381" t="n"/>
+      <c r="L62" s="381" t="n"/>
+      <c r="M62" s="380" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="298" t="inlineStr">
@@ -10685,6 +13012,7 @@
           <t>COMBINED PCR REQUEST</t>
         </is>
       </c>
+      <c r="C63" s="380" t="n"/>
       <c r="D63" s="300" t="inlineStr">
         <is>
           <t>PAR $530K + Ph3 Accel $800K</t>
@@ -10705,6 +13033,12 @@
           <t>Vic confirmed range $1.2–1.33M. Submit as two separate PCRs but present together to CIO.</t>
         </is>
       </c>
+      <c r="H63" s="381" t="n"/>
+      <c r="I63" s="381" t="n"/>
+      <c r="J63" s="381" t="n"/>
+      <c r="K63" s="381" t="n"/>
+      <c r="L63" s="381" t="n"/>
+      <c r="M63" s="380" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">
